--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B86059-CFF5-4E1B-A676-843ADFFF2351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2AB537A-A0DF-4577-88B0-B14C29199C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="184">
   <si>
     <t>记录类型</t>
   </si>
@@ -202,15 +202,9 @@
     <t>日用&amp;家用</t>
   </si>
   <si>
-    <t>应收款项</t>
-  </si>
-  <si>
     <t>居家</t>
   </si>
   <si>
-    <t>代付</t>
-  </si>
-  <si>
     <t>理发</t>
   </si>
   <si>
@@ -248,9 +242,6 @@
     <t>个人</t>
   </si>
   <si>
-    <t>报账</t>
-  </si>
-  <si>
     <t>电费</t>
   </si>
   <si>
@@ -303,10 +294,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>跑腿客户</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>馋不二</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -323,26 +310,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>湖北省高速公路联网收费中心</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>天之逸</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>停车</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>高速过路费</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>停车费</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>铁路12306</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -367,10 +334,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>武南综合服务商店陈忠</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>闪送</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -379,10 +342,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>湖北工业大学</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>卢亮</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -700,6 +659,10 @@
   </si>
   <si>
     <t>饮料</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>零食很忙</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -892,7 +855,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1076,12 +1039,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor theme="9" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
     <fill>
@@ -1388,7 +1345,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1409,16 +1366,13 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="42" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1780,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.1640625" customWidth="1"/>
@@ -1799,13 +1753,13 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1817,13 +1771,13 @@
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>3</v>
@@ -1832,10 +1786,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>5</v>
@@ -1855,16 +1809,16 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="K2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1875,10 +1829,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K3" t="s">
         <v>18</v>
@@ -1892,10 +1846,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K4" t="s">
         <v>16</v>
@@ -1909,10 +1863,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -1923,16 +1877,16 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -1940,13 +1894,13 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K7" t="s">
         <v>29</v>
@@ -1957,16 +1911,16 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K8" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -1974,16 +1928,16 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K9" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -1991,16 +1945,16 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K10" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2008,16 +1962,16 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K11" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2025,16 +1979,16 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K12" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2042,19 +1996,16 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
-      </c>
-      <c r="J13" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="K13" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2062,22 +2013,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>170</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
+        <v>159</v>
+      </c>
+      <c r="J14" t="s">
+        <v>182</v>
       </c>
       <c r="K14" t="s">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -2085,13 +2033,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -2100,7 +2048,7 @@
         <v>12</v>
       </c>
       <c r="K15" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2108,13 +2056,13 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -2122,11 +2070,8 @@
       <c r="F16" t="s">
         <v>12</v>
       </c>
-      <c r="J16" t="s">
-        <v>19</v>
-      </c>
       <c r="K16" t="s">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -2134,13 +2079,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
@@ -2148,8 +2093,11 @@
       <c r="F17" t="s">
         <v>12</v>
       </c>
+      <c r="J17" t="s">
+        <v>19</v>
+      </c>
       <c r="K17" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -2157,16 +2105,22 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>170</v>
+        <v>159</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
       </c>
       <c r="K18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -2174,16 +2128,16 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K19" t="s">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -2191,19 +2145,16 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>170</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
       <c r="K20" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -2211,27 +2162,30 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
       </c>
       <c r="K21" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -2239,48 +2193,45 @@
       <c r="E22" t="s">
         <v>11</v>
       </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J22" t="s">
-        <v>176</v>
-      </c>
       <c r="K22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" t="s">
         <v>165</v>
       </c>
-      <c r="C23" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" t="s">
-        <v>10</v>
-      </c>
       <c r="K23" t="s">
-        <v>27</v>
-      </c>
-      <c r="R23">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
       </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
       <c r="K24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -2288,16 +2239,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
       </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
       <c r="K25" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -2305,30 +2259,27 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
       </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
       <c r="K26" t="s">
-        <v>31</v>
+        <v>147</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -2336,39 +2287,39 @@
       <c r="E27" t="s">
         <v>11</v>
       </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
       <c r="K27" t="s">
-        <v>33</v>
-      </c>
-      <c r="O27" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
       </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
       <c r="K28" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O28" t="s">
-        <v>40</v>
-      </c>
-      <c r="R28">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -2377,7 +2328,7 @@
         <v>41</v>
       </c>
       <c r="O29" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -2385,10 +2336,10 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -2397,15 +2348,18 @@
         <v>41</v>
       </c>
       <c r="O30" t="s">
-        <v>87</v>
+        <v>83</v>
+      </c>
+      <c r="R30">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -2414,18 +2368,15 @@
         <v>41</v>
       </c>
       <c r="O31" t="s">
-        <v>87</v>
-      </c>
-      <c r="R31">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2434,7 +2385,7 @@
         <v>41</v>
       </c>
       <c r="O32" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="R32">
         <v>1</v>
@@ -2442,10 +2393,10 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -2454,7 +2405,7 @@
         <v>41</v>
       </c>
       <c r="O33" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -2462,10 +2413,10 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -2474,7 +2425,7 @@
         <v>41</v>
       </c>
       <c r="O34" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -2482,10 +2433,10 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -2494,7 +2445,7 @@
         <v>41</v>
       </c>
       <c r="O35" t="s">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -2502,61 +2453,64 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
       </c>
       <c r="K36" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="O36" t="s">
+        <v>140</v>
+      </c>
+      <c r="R36">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
       </c>
       <c r="K37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
       </c>
       <c r="K38" t="s">
-        <v>48</v>
-      </c>
-      <c r="R38">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
       </c>
       <c r="K39" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -2564,25 +2518,16 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>183</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>184</v>
-      </c>
       <c r="K40" t="s">
-        <v>185</v>
-      </c>
-      <c r="N40" s="4" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -2590,56 +2535,59 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="N41" t="s">
-        <v>85</v>
-      </c>
-      <c r="O41" t="s">
-        <v>105</v>
+        <v>173</v>
+      </c>
+      <c r="K41" t="s">
+        <v>174</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C42" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" t="s">
-        <v>35</v>
-      </c>
-      <c r="F42" t="s">
-        <v>72</v>
-      </c>
-      <c r="K42" t="s">
-        <v>93</v>
-      </c>
       <c r="N42" t="s">
+        <v>81</v>
+      </c>
+      <c r="O42" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -2648,74 +2596,70 @@
         <v>35</v>
       </c>
       <c r="F43" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="K43" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="N43" t="s">
-        <v>94</v>
-      </c>
-      <c r="O43" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>163</v>
-      </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
         <v>35</v>
       </c>
-      <c r="F44" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="L44" s="10"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="R44">
-        <v>1</v>
+      <c r="F44" t="s">
+        <v>88</v>
+      </c>
+      <c r="K44" t="s">
+        <v>87</v>
+      </c>
+      <c r="N44" t="s">
+        <v>85</v>
+      </c>
+      <c r="O44" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>159</v>
-      </c>
-      <c r="C45" t="s">
-        <v>65</v>
-      </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F45" t="s">
-        <v>160</v>
-      </c>
-      <c r="K45" t="s">
-        <v>161</v>
-      </c>
-      <c r="N45" t="s">
-        <v>150</v>
+      <c r="F45" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L45" s="9"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="8" t="s">
+        <v>139</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -2723,10 +2667,10 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="C46" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -2735,24 +2679,24 @@
         <v>35</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
-      </c>
-      <c r="J46" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="K46" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="N46" t="s">
-        <v>74</v>
+        <v>139</v>
+      </c>
+      <c r="R46">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C47" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -2767,18 +2711,18 @@
         <v>37</v>
       </c>
       <c r="K47" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="N47" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="C48" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -2793,18 +2737,18 @@
         <v>37</v>
       </c>
       <c r="K48" t="s">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="N48" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -2816,24 +2760,21 @@
         <v>36</v>
       </c>
       <c r="J49" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="K49" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="N49" t="s">
-        <v>150</v>
-      </c>
-      <c r="R49">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C50" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -2845,13 +2786,13 @@
         <v>36</v>
       </c>
       <c r="J50" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="K50" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="N50" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -2859,83 +2800,83 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="C51" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
       </c>
       <c r="E51" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="F51" t="s">
-        <v>69</v>
+        <v>36</v>
+      </c>
+      <c r="J51" t="s">
+        <v>153</v>
       </c>
       <c r="K51" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="N51" t="s">
-        <v>50</v>
-      </c>
-      <c r="O51" s="12" t="s">
-        <v>51</v>
+        <v>139</v>
+      </c>
+      <c r="R51">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="C52" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F52" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="K52" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="N52" t="s">
-        <v>150</v>
-      </c>
-      <c r="O52">
-        <v>13297968006</v>
-      </c>
-      <c r="R52">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="O52" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C53" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F53" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="K53" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="N53" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="O53">
-        <v>13638658298</v>
+        <v>13297968006</v>
       </c>
       <c r="R53">
         <v>1</v>
@@ -2943,22 +2884,28 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
       </c>
       <c r="E54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>138</v>
+      </c>
+      <c r="K54" t="s">
+        <v>137</v>
       </c>
       <c r="N54" t="s">
-        <v>52</v>
+        <v>139</v>
+      </c>
+      <c r="O54">
+        <v>13638658298</v>
       </c>
       <c r="R54">
         <v>1</v>
@@ -2966,60 +2913,51 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>152</v>
+        <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c r="F55" t="s">
-        <v>156</v>
-      </c>
-      <c r="K55" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="N55" t="s">
         <v>52</v>
       </c>
-      <c r="O55" t="s">
-        <v>151</v>
-      </c>
       <c r="R55">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="F56" t="s">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="K56" t="s">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="N56" t="s">
-        <v>39</v>
-      </c>
-      <c r="P56" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>66</v>
+        <v>52</v>
+      </c>
+      <c r="O56" t="s">
+        <v>140</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -3027,101 +2965,58 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="C57" t="s">
+        <v>63</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s">
         <v>65</v>
       </c>
-      <c r="D57" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>67</v>
       </c>
-      <c r="F57" t="s">
-        <v>70</v>
+      <c r="K57" t="s">
+        <v>68</v>
       </c>
       <c r="N57" t="s">
         <v>39</v>
       </c>
+      <c r="P57" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>64</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D58" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F58" t="s">
-        <v>55</v>
-      </c>
-      <c r="O58" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" t="s">
-        <v>65</v>
-      </c>
-      <c r="D59" t="s">
-        <v>53</v>
-      </c>
-      <c r="E59" t="s">
-        <v>53</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="J59" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>89</v>
-      </c>
-      <c r="R59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60" t="s">
-        <v>65</v>
-      </c>
-      <c r="D60" t="s">
-        <v>53</v>
-      </c>
-      <c r="E60" t="s">
-        <v>53</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="J60" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>89</v>
-      </c>
-      <c r="R60">
-        <v>1</v>
+        <v>67</v>
+      </c>
+      <c r="N58" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R61" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
+  <autoFilter ref="A1:R59" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3138,162 +3033,162 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2AB537A-A0DF-4577-88B0-B14C29199C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16FC458-6BF6-4CEA-A660-46EA1835B04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="186">
   <si>
     <t>记录类型</t>
   </si>
@@ -663,6 +663,14 @@
   </si>
   <si>
     <t>零食很忙</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>午餐</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>斯迪姆幼儿园-柏思思</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1345,7 +1353,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1377,6 +1385,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1734,7 +1748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:R58"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.1640625" customWidth="1"/>
@@ -1814,9 +1828,6 @@
       <c r="C2" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
       <c r="K2" t="s">
         <v>75</v>
       </c>
@@ -1831,9 +1842,6 @@
       <c r="C3" t="s">
         <v>79</v>
       </c>
-      <c r="D3" t="s">
-        <v>159</v>
-      </c>
       <c r="K3" t="s">
         <v>18</v>
       </c>
@@ -1848,9 +1856,6 @@
       <c r="C4" t="s">
         <v>79</v>
       </c>
-      <c r="D4" t="s">
-        <v>159</v>
-      </c>
       <c r="K4" t="s">
         <v>16</v>
       </c>
@@ -1865,9 +1870,6 @@
       <c r="C5" t="s">
         <v>79</v>
       </c>
-      <c r="D5" t="s">
-        <v>159</v>
-      </c>
       <c r="K5" t="s">
         <v>17</v>
       </c>
@@ -1882,9 +1884,6 @@
       <c r="C6" t="s">
         <v>79</v>
       </c>
-      <c r="D6" t="s">
-        <v>159</v>
-      </c>
       <c r="K6" t="s">
         <v>76</v>
       </c>
@@ -1899,9 +1898,6 @@
       <c r="C7" t="s">
         <v>79</v>
       </c>
-      <c r="D7" t="s">
-        <v>159</v>
-      </c>
       <c r="K7" t="s">
         <v>29</v>
       </c>
@@ -1916,9 +1912,6 @@
       <c r="C8" t="s">
         <v>79</v>
       </c>
-      <c r="D8" t="s">
-        <v>159</v>
-      </c>
       <c r="K8" t="s">
         <v>155</v>
       </c>
@@ -1933,9 +1926,6 @@
       <c r="C9" t="s">
         <v>79</v>
       </c>
-      <c r="D9" t="s">
-        <v>159</v>
-      </c>
       <c r="K9" t="s">
         <v>183</v>
       </c>
@@ -1950,9 +1940,6 @@
       <c r="C10" t="s">
         <v>79</v>
       </c>
-      <c r="D10" t="s">
-        <v>159</v>
-      </c>
       <c r="K10" t="s">
         <v>158</v>
       </c>
@@ -1967,9 +1954,6 @@
       <c r="C11" t="s">
         <v>79</v>
       </c>
-      <c r="D11" t="s">
-        <v>159</v>
-      </c>
       <c r="K11" t="s">
         <v>169</v>
       </c>
@@ -1984,9 +1968,6 @@
       <c r="C12" t="s">
         <v>79</v>
       </c>
-      <c r="D12" t="s">
-        <v>159</v>
-      </c>
       <c r="K12" t="s">
         <v>176</v>
       </c>
@@ -2001,9 +1982,6 @@
       <c r="C13" t="s">
         <v>79</v>
       </c>
-      <c r="D13" t="s">
-        <v>159</v>
-      </c>
       <c r="K13" t="s">
         <v>177</v>
       </c>
@@ -2018,9 +1996,6 @@
       <c r="C14" t="s">
         <v>79</v>
       </c>
-      <c r="D14" t="s">
-        <v>159</v>
-      </c>
       <c r="J14" t="s">
         <v>182</v>
       </c>
@@ -2033,30 +2008,29 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>185</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="K15" t="s">
-        <v>14</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="L15" s="12"/>
+      <c r="M15" s="13"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>79</v>
@@ -2071,7 +2045,7 @@
         <v>12</v>
       </c>
       <c r="K16" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -2079,7 +2053,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
         <v>79</v>
@@ -2093,11 +2067,8 @@
       <c r="F17" t="s">
         <v>12</v>
       </c>
-      <c r="J17" t="s">
-        <v>19</v>
-      </c>
       <c r="K17" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -2105,7 +2076,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" t="s">
         <v>79</v>
@@ -2119,8 +2090,11 @@
       <c r="F18" t="s">
         <v>12</v>
       </c>
+      <c r="J18" t="s">
+        <v>19</v>
+      </c>
       <c r="K18" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -2128,7 +2102,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C19" t="s">
         <v>79</v>
@@ -2136,8 +2110,14 @@
       <c r="D19" t="s">
         <v>159</v>
       </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
       <c r="K19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -2145,7 +2125,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
         <v>79</v>
@@ -2154,7 +2134,7 @@
         <v>159</v>
       </c>
       <c r="K20" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -2162,7 +2142,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
         <v>79</v>
@@ -2170,11 +2150,8 @@
       <c r="D21" t="s">
         <v>159</v>
       </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
       <c r="K21" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -2182,24 +2159,27 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
         <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
       </c>
       <c r="K22" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
         <v>79</v>
@@ -2210,19 +2190,13 @@
       <c r="E23" t="s">
         <v>11</v>
       </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="J23" t="s">
-        <v>165</v>
-      </c>
       <c r="K23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
         <v>79</v>
@@ -2230,16 +2204,22 @@
       <c r="D24" t="s">
         <v>10</v>
       </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" t="s">
+        <v>165</v>
+      </c>
       <c r="K24" t="s">
-        <v>27</v>
-      </c>
-      <c r="R24">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C25" t="s">
         <v>79</v>
@@ -2247,11 +2227,8 @@
       <c r="D25" t="s">
         <v>10</v>
       </c>
-      <c r="E25" t="s">
-        <v>11</v>
-      </c>
       <c r="K25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -2259,7 +2236,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C26" t="s">
         <v>79</v>
@@ -2267,8 +2244,11 @@
       <c r="D26" t="s">
         <v>10</v>
       </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
       <c r="K26" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="R26">
         <v>1</v>
@@ -2276,7 +2256,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
         <v>79</v>
@@ -2284,19 +2264,16 @@
       <c r="D27" t="s">
         <v>10</v>
       </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
       <c r="K27" t="s">
-        <v>31</v>
+        <v>147</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
         <v>79</v>
@@ -2307,16 +2284,16 @@
       <c r="E28" t="s">
         <v>11</v>
       </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
       <c r="K28" t="s">
-        <v>33</v>
-      </c>
-      <c r="O28" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
         <v>79</v>
@@ -2324,31 +2301,28 @@
       <c r="D29" t="s">
         <v>10</v>
       </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
       <c r="K29" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O29" t="s">
-        <v>40</v>
-      </c>
-      <c r="R29">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
         <v>79</v>
-      </c>
-      <c r="D30" t="s">
-        <v>10</v>
       </c>
       <c r="K30" t="s">
         <v>41</v>
       </c>
       <c r="O30" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -2356,13 +2330,10 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
         <v>79</v>
-      </c>
-      <c r="D31" t="s">
-        <v>10</v>
       </c>
       <c r="K31" t="s">
         <v>41</v>
@@ -2370,16 +2341,16 @@
       <c r="O31" t="s">
         <v>83</v>
       </c>
+      <c r="R31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
         <v>79</v>
-      </c>
-      <c r="D32" t="s">
-        <v>10</v>
       </c>
       <c r="K32" t="s">
         <v>41</v>
@@ -2387,25 +2358,19 @@
       <c r="O32" t="s">
         <v>83</v>
       </c>
-      <c r="R32">
-        <v>1</v>
-      </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
         <v>79</v>
-      </c>
-      <c r="D33" t="s">
-        <v>10</v>
       </c>
       <c r="K33" t="s">
         <v>41</v>
       </c>
       <c r="O33" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -2413,19 +2378,16 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
         <v>79</v>
-      </c>
-      <c r="D34" t="s">
-        <v>10</v>
       </c>
       <c r="K34" t="s">
         <v>41</v>
       </c>
       <c r="O34" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -2433,19 +2395,16 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
         <v>79</v>
-      </c>
-      <c r="D35" t="s">
-        <v>10</v>
       </c>
       <c r="K35" t="s">
         <v>41</v>
       </c>
       <c r="O35" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -2453,19 +2412,16 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
         <v>79</v>
-      </c>
-      <c r="D36" t="s">
-        <v>10</v>
       </c>
       <c r="K36" t="s">
         <v>41</v>
       </c>
       <c r="O36" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -2473,61 +2429,52 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
         <v>79</v>
       </c>
-      <c r="D37" t="s">
-        <v>10</v>
-      </c>
       <c r="K37" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="O37" t="s">
+        <v>140</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
         <v>79</v>
       </c>
-      <c r="D38" t="s">
-        <v>10</v>
-      </c>
       <c r="K38" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
         <v>79</v>
       </c>
-      <c r="D39" t="s">
-        <v>10</v>
-      </c>
       <c r="K39" t="s">
-        <v>48</v>
-      </c>
-      <c r="R39">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
         <v>79</v>
       </c>
-      <c r="D40" t="s">
-        <v>10</v>
-      </c>
       <c r="K40" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -2535,25 +2482,13 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
       </c>
-      <c r="D41" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>173</v>
-      </c>
       <c r="K41" t="s">
-        <v>174</v>
-      </c>
-      <c r="N41" s="4" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -2561,7 +2496,7 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="C42" t="s">
         <v>79</v>
@@ -2573,18 +2508,21 @@
         <v>53</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N42" t="s">
-        <v>81</v>
-      </c>
-      <c r="O42" t="s">
-        <v>94</v>
+        <v>173</v>
+      </c>
+      <c r="K42" t="s">
+        <v>174</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R42">
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
         <v>79</v>
@@ -2592,22 +2530,22 @@
       <c r="D43" t="s">
         <v>10</v>
       </c>
-      <c r="E43" t="s">
-        <v>35</v>
-      </c>
-      <c r="F43" t="s">
-        <v>69</v>
-      </c>
-      <c r="K43" t="s">
-        <v>84</v>
+      <c r="E43" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="N43" t="s">
-        <v>85</v>
+        <v>81</v>
+      </c>
+      <c r="O43" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
         <v>79</v>
@@ -2619,72 +2557,69 @@
         <v>35</v>
       </c>
       <c r="F44" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="K44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N44" t="s">
         <v>85</v>
       </c>
-      <c r="O44" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>152</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D45" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" t="s">
         <v>35</v>
       </c>
-      <c r="F45" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="L45" s="9"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="R45">
-        <v>1</v>
+      <c r="F45" t="s">
+        <v>88</v>
+      </c>
+      <c r="K45" t="s">
+        <v>87</v>
+      </c>
+      <c r="N45" t="s">
+        <v>85</v>
+      </c>
+      <c r="O45" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>148</v>
-      </c>
-      <c r="C46" t="s">
+        <v>152</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="K46" t="s">
-        <v>150</v>
-      </c>
-      <c r="N46" t="s">
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L46" s="9"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="8" t="s">
         <v>139</v>
       </c>
       <c r="R46">
@@ -2693,10 +2628,10 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -2705,21 +2640,21 @@
         <v>35</v>
       </c>
       <c r="F47" t="s">
-        <v>36</v>
-      </c>
-      <c r="J47" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="K47" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="N47" t="s">
-        <v>71</v>
+        <v>139</v>
+      </c>
+      <c r="R47">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C48" t="s">
         <v>79</v>
@@ -2737,7 +2672,7 @@
         <v>37</v>
       </c>
       <c r="K48" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N48" t="s">
         <v>71</v>
@@ -2745,7 +2680,7 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="C49" t="s">
         <v>79</v>
@@ -2763,7 +2698,7 @@
         <v>37</v>
       </c>
       <c r="K49" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="N49" t="s">
         <v>71</v>
@@ -2771,7 +2706,7 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C50" t="s">
         <v>79</v>
@@ -2786,21 +2721,18 @@
         <v>36</v>
       </c>
       <c r="J50" t="s">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="K50" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="N50" t="s">
-        <v>139</v>
-      </c>
-      <c r="R50">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C51" t="s">
         <v>79</v>
@@ -2818,7 +2750,7 @@
         <v>153</v>
       </c>
       <c r="K51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N51" t="s">
         <v>139</v>
@@ -2829,7 +2761,7 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="C52" t="s">
         <v>79</v>
@@ -2838,24 +2770,27 @@
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F52" t="s">
-        <v>66</v>
+        <v>36</v>
+      </c>
+      <c r="J52" t="s">
+        <v>153</v>
       </c>
       <c r="K52" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="N52" t="s">
-        <v>50</v>
-      </c>
-      <c r="O52" s="11" t="s">
-        <v>51</v>
+        <v>139</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="C53" t="s">
         <v>79</v>
@@ -2867,24 +2802,21 @@
         <v>53</v>
       </c>
       <c r="F53" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="K53" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="N53" t="s">
-        <v>139</v>
-      </c>
-      <c r="O53">
-        <v>13297968006</v>
-      </c>
-      <c r="R53">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="O53" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C54" t="s">
         <v>79</v>
@@ -2899,13 +2831,13 @@
         <v>138</v>
       </c>
       <c r="K54" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N54" t="s">
         <v>139</v>
       </c>
       <c r="O54">
-        <v>13638658298</v>
+        <v>13297968006</v>
       </c>
       <c r="R54">
         <v>1</v>
@@ -2913,7 +2845,7 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="C55" t="s">
         <v>79</v>
@@ -2925,10 +2857,16 @@
         <v>53</v>
       </c>
       <c r="F55" t="s">
-        <v>54</v>
+        <v>138</v>
+      </c>
+      <c r="K55" t="s">
+        <v>137</v>
       </c>
       <c r="N55" t="s">
-        <v>52</v>
+        <v>139</v>
+      </c>
+      <c r="O55">
+        <v>13638658298</v>
       </c>
       <c r="R55">
         <v>1</v>
@@ -2936,7 +2874,7 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C56" t="s">
         <v>79</v>
@@ -2945,51 +2883,42 @@
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="F56" t="s">
-        <v>145</v>
-      </c>
-      <c r="K56" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="N56" t="s">
         <v>52</v>
       </c>
-      <c r="O56" t="s">
-        <v>140</v>
-      </c>
       <c r="R56">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="C57" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="E57" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="F57" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="K57" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="N57" t="s">
-        <v>39</v>
-      </c>
-      <c r="P57" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>64</v>
+        <v>52</v>
+      </c>
+      <c r="O57" t="s">
+        <v>140</v>
       </c>
       <c r="R57">
         <v>1</v>
@@ -2997,7 +2926,7 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
         <v>63</v>
@@ -3011,12 +2940,44 @@
       <c r="F58" t="s">
         <v>67</v>
       </c>
+      <c r="K58" t="s">
+        <v>68</v>
+      </c>
       <c r="N58" t="s">
         <v>39</v>
       </c>
+      <c r="P58" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>64</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s">
+        <v>65</v>
+      </c>
+      <c r="F59" t="s">
+        <v>67</v>
+      </c>
+      <c r="N59" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R59" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
+  <autoFilter ref="A1:R60" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16FC458-6BF6-4CEA-A660-46EA1835B04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213F76CC-ECD3-4480-B896-93CE1BDB5D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="190">
   <si>
     <t>记录类型</t>
   </si>
@@ -671,6 +671,22 @@
   </si>
   <si>
     <t>斯迪姆幼儿园-柏思思</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>支出</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>饮食</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>食材</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>食</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1828,8 +1844,20 @@
       <c r="C2" t="s">
         <v>79</v>
       </c>
+      <c r="D2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" t="s">
+        <v>188</v>
+      </c>
       <c r="K2" t="s">
         <v>75</v>
+      </c>
+      <c r="N2" t="s">
+        <v>189</v>
       </c>
       <c r="R2">
         <v>1</v>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213F76CC-ECD3-4480-B896-93CE1BDB5D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83518C39-594D-494A-A428-4E6915CE0594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="186">
   <si>
     <t>记录类型</t>
   </si>
@@ -671,22 +671,6 @@
   </si>
   <si>
     <t>斯迪姆幼儿园-柏思思</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>支出</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>饮食</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>食材</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>食</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1844,20 +1828,8 @@
       <c r="C2" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" t="s">
-        <v>188</v>
-      </c>
       <c r="K2" t="s">
         <v>75</v>
-      </c>
-      <c r="N2" t="s">
-        <v>189</v>
       </c>
       <c r="R2">
         <v>1</v>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83518C39-594D-494A-A428-4E6915CE0594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3CEEB1-838B-4187-9484-970371865787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="190">
   <si>
     <t>记录类型</t>
   </si>
@@ -671,6 +671,21 @@
   </si>
   <si>
     <t>斯迪姆幼儿园-柏思思</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>李李</t>
+  </si>
+  <si>
+    <t>支出</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>正餐</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>小饭馆</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1353,7 +1368,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1392,6 +1407,7 @@
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1748,7 +1764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.1640625" customWidth="1"/>
@@ -2006,54 +2022,48 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>185</v>
+    <row r="15" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>186</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>184</v>
-      </c>
-      <c r="K15" t="s">
-        <v>185</v>
-      </c>
-      <c r="L15" s="12"/>
-      <c r="M15" s="13"/>
+        <v>79</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="R15" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>185</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="K16" t="s">
-        <v>14</v>
-      </c>
-      <c r="R16">
-        <v>1</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" s="13"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>79</v>
@@ -2068,7 +2078,7 @@
         <v>12</v>
       </c>
       <c r="K17" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -2076,7 +2086,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
         <v>79</v>
@@ -2090,11 +2100,8 @@
       <c r="F18" t="s">
         <v>12</v>
       </c>
-      <c r="J18" t="s">
-        <v>19</v>
-      </c>
       <c r="K18" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -2102,7 +2109,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" t="s">
         <v>79</v>
@@ -2116,8 +2123,11 @@
       <c r="F19" t="s">
         <v>12</v>
       </c>
+      <c r="J19" t="s">
+        <v>19</v>
+      </c>
       <c r="K19" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -2125,7 +2135,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
         <v>79</v>
@@ -2133,8 +2143,14 @@
       <c r="D20" t="s">
         <v>159</v>
       </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
       <c r="K20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -2142,7 +2158,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C21" t="s">
         <v>79</v>
@@ -2151,7 +2167,7 @@
         <v>159</v>
       </c>
       <c r="K21" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -2159,7 +2175,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
         <v>79</v>
@@ -2167,11 +2183,8 @@
       <c r="D22" t="s">
         <v>159</v>
       </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
       <c r="K22" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -2179,24 +2192,27 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="C23" t="s">
         <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
       </c>
       <c r="K23" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
         <v>79</v>
@@ -2207,19 +2223,13 @@
       <c r="E24" t="s">
         <v>11</v>
       </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="J24" t="s">
-        <v>165</v>
-      </c>
       <c r="K24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
         <v>79</v>
@@ -2227,16 +2237,22 @@
       <c r="D25" t="s">
         <v>10</v>
       </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25" t="s">
+        <v>165</v>
+      </c>
       <c r="K25" t="s">
-        <v>27</v>
-      </c>
-      <c r="R25">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C26" t="s">
         <v>79</v>
@@ -2244,11 +2260,8 @@
       <c r="D26" t="s">
         <v>10</v>
       </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
       <c r="K26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R26">
         <v>1</v>
@@ -2256,7 +2269,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C27" t="s">
         <v>79</v>
@@ -2264,8 +2277,11 @@
       <c r="D27" t="s">
         <v>10</v>
       </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
       <c r="K27" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -2273,7 +2289,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
         <v>79</v>
@@ -2281,19 +2297,16 @@
       <c r="D28" t="s">
         <v>10</v>
       </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
       <c r="K28" t="s">
-        <v>31</v>
+        <v>147</v>
+      </c>
+      <c r="R28">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
         <v>79</v>
@@ -2304,33 +2317,36 @@
       <c r="E29" t="s">
         <v>11</v>
       </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
       <c r="K29" t="s">
-        <v>33</v>
-      </c>
-      <c r="O29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
         <v>79</v>
       </c>
+      <c r="D30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
       <c r="K30" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O30" t="s">
-        <v>40</v>
-      </c>
-      <c r="R30">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
         <v>79</v>
@@ -2339,7 +2355,7 @@
         <v>41</v>
       </c>
       <c r="O31" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -2347,7 +2363,7 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
         <v>79</v>
@@ -2358,10 +2374,13 @@
       <c r="O32" t="s">
         <v>83</v>
       </c>
+      <c r="R32">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
         <v>79</v>
@@ -2372,13 +2391,10 @@
       <c r="O33" t="s">
         <v>83</v>
       </c>
-      <c r="R33">
-        <v>1</v>
-      </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
         <v>79</v>
@@ -2387,7 +2403,7 @@
         <v>41</v>
       </c>
       <c r="O34" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -2395,7 +2411,7 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
         <v>79</v>
@@ -2404,7 +2420,7 @@
         <v>41</v>
       </c>
       <c r="O35" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -2412,7 +2428,7 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
         <v>79</v>
@@ -2421,7 +2437,7 @@
         <v>41</v>
       </c>
       <c r="O36" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -2429,7 +2445,7 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
         <v>79</v>
@@ -2438,7 +2454,7 @@
         <v>41</v>
       </c>
       <c r="O37" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -2446,49 +2462,52 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="C38" t="s">
         <v>79</v>
       </c>
       <c r="K38" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="O38" t="s">
+        <v>140</v>
+      </c>
+      <c r="R38">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
         <v>79</v>
       </c>
       <c r="K39" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
         <v>79</v>
       </c>
       <c r="K40" t="s">
-        <v>48</v>
-      </c>
-      <c r="R40">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
       </c>
       <c r="K41" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -2496,25 +2515,13 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s">
         <v>79</v>
       </c>
-      <c r="D42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>173</v>
-      </c>
       <c r="K42" t="s">
-        <v>174</v>
-      </c>
-      <c r="N42" s="4" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="R42">
         <v>1</v>
@@ -2522,7 +2529,7 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="C43" t="s">
         <v>79</v>
@@ -2534,18 +2541,21 @@
         <v>53</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N43" t="s">
-        <v>81</v>
-      </c>
-      <c r="O43" t="s">
-        <v>94</v>
+        <v>173</v>
+      </c>
+      <c r="K43" t="s">
+        <v>174</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R43">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
         <v>79</v>
@@ -2553,22 +2563,22 @@
       <c r="D44" t="s">
         <v>10</v>
       </c>
-      <c r="E44" t="s">
-        <v>35</v>
-      </c>
-      <c r="F44" t="s">
-        <v>69</v>
-      </c>
-      <c r="K44" t="s">
-        <v>84</v>
+      <c r="E44" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="N44" t="s">
-        <v>85</v>
+        <v>81</v>
+      </c>
+      <c r="O44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C45" t="s">
         <v>79</v>
@@ -2580,72 +2590,69 @@
         <v>35</v>
       </c>
       <c r="F45" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="K45" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N45" t="s">
         <v>85</v>
       </c>
-      <c r="O45" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>152</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D46" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" t="s">
         <v>10</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" t="s">
         <v>35</v>
       </c>
-      <c r="F46" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="L46" s="9"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="R46">
-        <v>1</v>
+      <c r="F46" t="s">
+        <v>88</v>
+      </c>
+      <c r="K46" t="s">
+        <v>87</v>
+      </c>
+      <c r="N46" t="s">
+        <v>85</v>
+      </c>
+      <c r="O46" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>148</v>
-      </c>
-      <c r="C47" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="K47" t="s">
-        <v>150</v>
-      </c>
-      <c r="N47" t="s">
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L47" s="9"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="8" t="s">
         <v>139</v>
       </c>
       <c r="R47">
@@ -2654,10 +2661,10 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -2666,21 +2673,21 @@
         <v>35</v>
       </c>
       <c r="F48" t="s">
-        <v>36</v>
-      </c>
-      <c r="J48" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="K48" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="N48" t="s">
-        <v>71</v>
+        <v>139</v>
+      </c>
+      <c r="R48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C49" t="s">
         <v>79</v>
@@ -2698,7 +2705,7 @@
         <v>37</v>
       </c>
       <c r="K49" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N49" t="s">
         <v>71</v>
@@ -2706,7 +2713,7 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="C50" t="s">
         <v>79</v>
@@ -2724,7 +2731,7 @@
         <v>37</v>
       </c>
       <c r="K50" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="N50" t="s">
         <v>71</v>
@@ -2732,7 +2739,7 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C51" t="s">
         <v>79</v>
@@ -2747,21 +2754,18 @@
         <v>36</v>
       </c>
       <c r="J51" t="s">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="K51" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="N51" t="s">
-        <v>139</v>
-      </c>
-      <c r="R51">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C52" t="s">
         <v>79</v>
@@ -2779,7 +2783,7 @@
         <v>153</v>
       </c>
       <c r="K52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N52" t="s">
         <v>139</v>
@@ -2790,7 +2794,7 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="C53" t="s">
         <v>79</v>
@@ -2799,24 +2803,27 @@
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F53" t="s">
-        <v>66</v>
+        <v>36</v>
+      </c>
+      <c r="J53" t="s">
+        <v>153</v>
       </c>
       <c r="K53" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="N53" t="s">
-        <v>50</v>
-      </c>
-      <c r="O53" s="11" t="s">
-        <v>51</v>
+        <v>139</v>
+      </c>
+      <c r="R53">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="C54" t="s">
         <v>79</v>
@@ -2828,24 +2835,21 @@
         <v>53</v>
       </c>
       <c r="F54" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="K54" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="N54" t="s">
-        <v>139</v>
-      </c>
-      <c r="O54">
-        <v>13297968006</v>
-      </c>
-      <c r="R54">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="O54" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C55" t="s">
         <v>79</v>
@@ -2860,13 +2864,13 @@
         <v>138</v>
       </c>
       <c r="K55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N55" t="s">
         <v>139</v>
       </c>
       <c r="O55">
-        <v>13638658298</v>
+        <v>13297968006</v>
       </c>
       <c r="R55">
         <v>1</v>
@@ -2874,7 +2878,7 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s">
         <v>79</v>
@@ -2886,10 +2890,16 @@
         <v>53</v>
       </c>
       <c r="F56" t="s">
-        <v>54</v>
+        <v>138</v>
+      </c>
+      <c r="K56" t="s">
+        <v>137</v>
       </c>
       <c r="N56" t="s">
-        <v>52</v>
+        <v>139</v>
+      </c>
+      <c r="O56">
+        <v>13638658298</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -2897,7 +2907,7 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C57" t="s">
         <v>79</v>
@@ -2906,51 +2916,42 @@
         <v>10</v>
       </c>
       <c r="E57" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="F57" t="s">
-        <v>145</v>
-      </c>
-      <c r="K57" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="N57" t="s">
         <v>52</v>
       </c>
-      <c r="O57" t="s">
-        <v>140</v>
-      </c>
       <c r="R57">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="F58" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="K58" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="N58" t="s">
-        <v>39</v>
-      </c>
-      <c r="P58" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>64</v>
+        <v>52</v>
+      </c>
+      <c r="O58" t="s">
+        <v>140</v>
       </c>
       <c r="R58">
         <v>1</v>
@@ -2958,7 +2959,7 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
         <v>63</v>
@@ -2972,12 +2973,44 @@
       <c r="F59" t="s">
         <v>67</v>
       </c>
+      <c r="K59" t="s">
+        <v>68</v>
+      </c>
       <c r="N59" t="s">
         <v>39</v>
       </c>
+      <c r="P59" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>64</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" t="s">
+        <v>63</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" t="s">
+        <v>65</v>
+      </c>
+      <c r="F60" t="s">
+        <v>67</v>
+      </c>
+      <c r="N60" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R60" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
+  <autoFilter ref="A1:R61" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TZY_YX\工作\2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3CEEB1-838B-4187-9484-970371865787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6367B0E6-A218-4865-99CA-53B26ADF3DDE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="25815" windowHeight="15495" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Moze Dict" sheetId="1" r:id="rId1"/>
     <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="192">
   <si>
     <t>记录类型</t>
   </si>
@@ -686,6 +686,14 @@
   </si>
   <si>
     <t>小饭馆</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈望云</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔬菜</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1764,24 +1772,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:R60"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R61"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="46.1640625" customWidth="1"/>
-    <col min="2" max="2" width="2.58203125" customWidth="1"/>
+    <col min="1" max="1" width="46.125" customWidth="1"/>
+    <col min="2" max="2" width="2.625" customWidth="1"/>
     <col min="7" max="7" width="2.25" customWidth="1"/>
-    <col min="8" max="8" width="2.83203125" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.08203125" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" customWidth="1"/>
-    <col min="13" max="13" width="3.08203125" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" customWidth="1"/>
-    <col min="15" max="15" width="16.08203125" customWidth="1"/>
+    <col min="8" max="8" width="2.875" customWidth="1"/>
+    <col min="9" max="9" width="4.375" customWidth="1"/>
+    <col min="10" max="10" width="10.875" customWidth="1"/>
+    <col min="11" max="11" width="16.125" customWidth="1"/>
+    <col min="12" max="12" width="11.875" customWidth="1"/>
+    <col min="13" max="13" width="3.125" customWidth="1"/>
+    <col min="14" max="14" width="12.375" customWidth="1"/>
+    <col min="15" max="15" width="16.125" customWidth="1"/>
     <col min="16" max="16" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>74</v>
       </c>
@@ -1837,7 +1845,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -1851,7 +1859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1865,7 +1873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1879,7 +1887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1893,7 +1901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>157</v>
       </c>
@@ -1907,7 +1915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -1921,7 +1929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>155</v>
       </c>
@@ -1935,7 +1943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>183</v>
       </c>
@@ -1949,7 +1957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>158</v>
       </c>
@@ -1963,7 +1971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>168</v>
       </c>
@@ -1977,7 +1985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>175</v>
       </c>
@@ -1991,7 +1999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>178</v>
       </c>
@@ -2005,7 +2013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>181</v>
       </c>
@@ -2022,71 +2030,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" t="s">
+        <v>191</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="K15" s="14" t="s">
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="O15" s="14" t="s">
+      <c r="O16" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="R15" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="R16" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>185</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>63</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>187</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>184</v>
-      </c>
-      <c r="K16" t="s">
-        <v>185</v>
-      </c>
-      <c r="L16" s="12"/>
-      <c r="M16" s="13"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>159</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="K17" t="s">
-        <v>14</v>
-      </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
         <v>79</v>
@@ -2101,15 +2100,15 @@
         <v>12</v>
       </c>
       <c r="K18" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="R18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>79</v>
@@ -2123,19 +2122,16 @@
       <c r="F19" t="s">
         <v>12</v>
       </c>
-      <c r="J19" t="s">
-        <v>19</v>
-      </c>
       <c r="K19" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="R19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C20" t="s">
         <v>79</v>
@@ -2149,16 +2145,19 @@
       <c r="F20" t="s">
         <v>12</v>
       </c>
+      <c r="J20" t="s">
+        <v>19</v>
+      </c>
       <c r="K20" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="R20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
         <v>79</v>
@@ -2166,16 +2165,22 @@
       <c r="D21" t="s">
         <v>159</v>
       </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
       <c r="K21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C22" t="s">
         <v>79</v>
@@ -2184,15 +2189,15 @@
         <v>159</v>
       </c>
       <c r="K22" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>156</v>
-      </c>
-      <c r="R22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>164</v>
       </c>
       <c r="C23" t="s">
         <v>79</v>
@@ -2200,36 +2205,36 @@
       <c r="D23" t="s">
         <v>159</v>
       </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
       <c r="K23" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="R23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
         <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
       </c>
       <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>26</v>
       </c>
       <c r="C25" t="s">
         <v>79</v>
@@ -2240,19 +2245,13 @@
       <c r="E25" t="s">
         <v>11</v>
       </c>
-      <c r="F25" t="s">
-        <v>12</v>
-      </c>
-      <c r="J25" t="s">
-        <v>165</v>
-      </c>
       <c r="K25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>154</v>
       </c>
       <c r="C26" t="s">
         <v>79</v>
@@ -2260,16 +2259,22 @@
       <c r="D26" t="s">
         <v>10</v>
       </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" t="s">
+        <v>165</v>
+      </c>
       <c r="K26" t="s">
-        <v>27</v>
-      </c>
-      <c r="R26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C27" t="s">
         <v>79</v>
@@ -2277,19 +2282,16 @@
       <c r="D27" t="s">
         <v>10</v>
       </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
       <c r="K27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C28" t="s">
         <v>79</v>
@@ -2297,16 +2299,19 @@
       <c r="D28" t="s">
         <v>10</v>
       </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
       <c r="K28" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="R28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
         <v>79</v>
@@ -2314,19 +2319,16 @@
       <c r="D29" t="s">
         <v>10</v>
       </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
       <c r="K29" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
         <v>79</v>
@@ -2337,33 +2339,36 @@
       <c r="E30" t="s">
         <v>11</v>
       </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
       <c r="K30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="K31" t="s">
         <v>33</v>
       </c>
-      <c r="O30" t="s">
+      <c r="O31" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>40</v>
-      </c>
-      <c r="C31" t="s">
-        <v>79</v>
-      </c>
-      <c r="K31" t="s">
-        <v>41</v>
-      </c>
-      <c r="O31" t="s">
-        <v>40</v>
-      </c>
-      <c r="R31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>70</v>
       </c>
       <c r="C32" t="s">
         <v>79</v>
@@ -2372,15 +2377,15 @@
         <v>41</v>
       </c>
       <c r="O32" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="R32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
         <v>79</v>
@@ -2391,10 +2396,13 @@
       <c r="O33" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
         <v>79</v>
@@ -2405,13 +2413,10 @@
       <c r="O34" t="s">
         <v>83</v>
       </c>
-      <c r="R34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
         <v>79</v>
@@ -2420,15 +2425,15 @@
         <v>41</v>
       </c>
       <c r="O35" t="s">
+        <v>83</v>
+      </c>
+      <c r="R35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>42</v>
-      </c>
-      <c r="R35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>15</v>
       </c>
       <c r="C36" t="s">
         <v>79</v>
@@ -2437,15 +2442,15 @@
         <v>41</v>
       </c>
       <c r="O36" t="s">
+        <v>42</v>
+      </c>
+      <c r="R36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>15</v>
-      </c>
-      <c r="R36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>43</v>
       </c>
       <c r="C37" t="s">
         <v>79</v>
@@ -2454,15 +2459,15 @@
         <v>41</v>
       </c>
       <c r="O37" t="s">
+        <v>15</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>43</v>
-      </c>
-      <c r="R37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>140</v>
       </c>
       <c r="C38" t="s">
         <v>79</v>
@@ -2471,91 +2476,82 @@
         <v>41</v>
       </c>
       <c r="O38" t="s">
+        <v>43</v>
+      </c>
+      <c r="R38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>140</v>
       </c>
-      <c r="R38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="C39" t="s">
+        <v>79</v>
+      </c>
+      <c r="K39" t="s">
+        <v>41</v>
+      </c>
+      <c r="O39" t="s">
+        <v>140</v>
+      </c>
+      <c r="R39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>44</v>
       </c>
-      <c r="C39" t="s">
-        <v>79</v>
-      </c>
-      <c r="K39" t="s">
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+      <c r="K40" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>46</v>
       </c>
-      <c r="C40" t="s">
-        <v>79</v>
-      </c>
-      <c r="K40" t="s">
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+      <c r="K41" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>48</v>
       </c>
-      <c r="C41" t="s">
-        <v>79</v>
-      </c>
-      <c r="K41" t="s">
+      <c r="C42" t="s">
+        <v>79</v>
+      </c>
+      <c r="K42" t="s">
         <v>48</v>
       </c>
-      <c r="R41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="R42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>91</v>
       </c>
-      <c r="C42" t="s">
-        <v>79</v>
-      </c>
-      <c r="K42" t="s">
+      <c r="C43" t="s">
+        <v>79</v>
+      </c>
+      <c r="K43" t="s">
         <v>91</v>
       </c>
-      <c r="R42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="R43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>172</v>
-      </c>
-      <c r="C43" t="s">
-        <v>79</v>
-      </c>
-      <c r="D43" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="K43" t="s">
-        <v>174</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="R43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>92</v>
       </c>
       <c r="C44" t="s">
         <v>79</v>
@@ -2567,18 +2563,21 @@
         <v>53</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N44" t="s">
-        <v>81</v>
-      </c>
-      <c r="O44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+      <c r="K44" t="s">
+        <v>174</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
         <v>79</v>
@@ -2586,22 +2585,22 @@
       <c r="D45" t="s">
         <v>10</v>
       </c>
-      <c r="E45" t="s">
-        <v>35</v>
-      </c>
-      <c r="F45" t="s">
-        <v>69</v>
-      </c>
-      <c r="K45" t="s">
+      <c r="E45" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="N45" t="s">
+        <v>81</v>
+      </c>
+      <c r="O45" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>84</v>
-      </c>
-      <c r="N45" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>86</v>
       </c>
       <c r="C46" t="s">
         <v>79</v>
@@ -2613,84 +2612,81 @@
         <v>35</v>
       </c>
       <c r="F46" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="K46" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N46" t="s">
         <v>85</v>
       </c>
-      <c r="O46" t="s">
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" t="s">
+        <v>88</v>
+      </c>
+      <c r="K47" t="s">
+        <v>87</v>
+      </c>
+      <c r="N47" t="s">
+        <v>85</v>
+      </c>
+      <c r="O47" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D48" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E48" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F48" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8" t="s">
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="K47" s="8" t="s">
+      <c r="K48" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="L47" s="9"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="8" t="s">
+      <c r="L48" s="9"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="R47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="R48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>148</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>63</v>
-      </c>
-      <c r="D48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
-        <v>35</v>
-      </c>
-      <c r="F48" t="s">
-        <v>149</v>
-      </c>
-      <c r="K48" t="s">
-        <v>150</v>
-      </c>
-      <c r="N48" t="s">
-        <v>139</v>
-      </c>
-      <c r="R48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" t="s">
-        <v>79</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -2699,21 +2695,21 @@
         <v>35</v>
       </c>
       <c r="F49" t="s">
-        <v>36</v>
-      </c>
-      <c r="J49" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="K49" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="N49" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+      <c r="R49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
         <v>79</v>
@@ -2731,15 +2727,15 @@
         <v>37</v>
       </c>
       <c r="K50" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N50" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="C51" t="s">
         <v>79</v>
@@ -2757,15 +2753,15 @@
         <v>37</v>
       </c>
       <c r="K51" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="N51" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C52" t="s">
         <v>79</v>
@@ -2780,21 +2776,18 @@
         <v>36</v>
       </c>
       <c r="J52" t="s">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="K52" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="N52" t="s">
-        <v>139</v>
-      </c>
-      <c r="R52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C53" t="s">
         <v>79</v>
@@ -2812,7 +2805,7 @@
         <v>153</v>
       </c>
       <c r="K53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N53" t="s">
         <v>139</v>
@@ -2821,9 +2814,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="C54" t="s">
         <v>79</v>
@@ -2832,24 +2825,27 @@
         <v>10</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F54" t="s">
-        <v>66</v>
+        <v>36</v>
+      </c>
+      <c r="J54" t="s">
+        <v>153</v>
       </c>
       <c r="K54" t="s">
+        <v>170</v>
+      </c>
+      <c r="N54" t="s">
+        <v>139</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>49</v>
-      </c>
-      <c r="N54" t="s">
-        <v>50</v>
-      </c>
-      <c r="O54" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>136</v>
       </c>
       <c r="C55" t="s">
         <v>79</v>
@@ -2861,24 +2857,21 @@
         <v>53</v>
       </c>
       <c r="F55" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="K55" t="s">
+        <v>49</v>
+      </c>
+      <c r="N55" t="s">
+        <v>50</v>
+      </c>
+      <c r="O55" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>136</v>
-      </c>
-      <c r="N55" t="s">
-        <v>139</v>
-      </c>
-      <c r="O55">
-        <v>13297968006</v>
-      </c>
-      <c r="R55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>137</v>
       </c>
       <c r="C56" t="s">
         <v>79</v>
@@ -2893,21 +2886,21 @@
         <v>138</v>
       </c>
       <c r="K56" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N56" t="s">
         <v>139</v>
       </c>
       <c r="O56">
-        <v>13638658298</v>
+        <v>13297968006</v>
       </c>
       <c r="R56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
         <v>79</v>
@@ -2919,18 +2912,24 @@
         <v>53</v>
       </c>
       <c r="F57" t="s">
-        <v>54</v>
+        <v>138</v>
+      </c>
+      <c r="K57" t="s">
+        <v>137</v>
       </c>
       <c r="N57" t="s">
-        <v>52</v>
+        <v>139</v>
+      </c>
+      <c r="O57">
+        <v>13638658298</v>
       </c>
       <c r="R57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C58" t="s">
         <v>79</v>
@@ -2939,59 +2938,50 @@
         <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="F58" t="s">
-        <v>145</v>
-      </c>
-      <c r="K58" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="N58" t="s">
         <v>52</v>
       </c>
-      <c r="O58" t="s">
-        <v>140</v>
-      </c>
       <c r="R58">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="C59" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="F59" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="K59" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="N59" t="s">
-        <v>39</v>
-      </c>
-      <c r="P59" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>64</v>
+        <v>52</v>
+      </c>
+      <c r="O59" t="s">
+        <v>140</v>
       </c>
       <c r="R59">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
         <v>63</v>
@@ -3005,12 +2995,44 @@
       <c r="F60" t="s">
         <v>67</v>
       </c>
+      <c r="K60" t="s">
+        <v>68</v>
+      </c>
       <c r="N60" t="s">
         <v>39</v>
       </c>
+      <c r="P60" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>64</v>
+      </c>
+      <c r="R60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" t="s">
+        <v>63</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" t="s">
+        <v>65</v>
+      </c>
+      <c r="F61" t="s">
+        <v>67</v>
+      </c>
+      <c r="N61" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R61" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
+  <autoFilter ref="A1:R62" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3020,12 +3042,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A67EEF5-ABF4-4CC5-BAC6-126980D50F95}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.08203125" customWidth="1"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>96</v>
       </c>
@@ -3033,7 +3055,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>98</v>
       </c>
@@ -3041,7 +3063,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>100</v>
       </c>
@@ -3049,7 +3071,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>102</v>
       </c>
@@ -3057,7 +3079,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>104</v>
       </c>
@@ -3065,7 +3087,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>106</v>
       </c>
@@ -3073,7 +3095,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>108</v>
       </c>
@@ -3081,7 +3103,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>110</v>
       </c>
@@ -3089,7 +3111,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>112</v>
       </c>
@@ -3097,7 +3119,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>114</v>
       </c>
@@ -3105,7 +3127,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>116</v>
       </c>
@@ -3113,7 +3135,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>118</v>
       </c>
@@ -3121,7 +3143,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>120</v>
       </c>
@@ -3129,7 +3151,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>134</v>
       </c>
@@ -3137,7 +3159,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>123</v>
       </c>
@@ -3145,7 +3167,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>124</v>
       </c>
@@ -3153,7 +3175,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>126</v>
       </c>
@@ -3161,7 +3183,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>128</v>
       </c>
@@ -3169,7 +3191,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>130</v>
       </c>
@@ -3177,7 +3199,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>132</v>
       </c>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TZY_YX\工作\2025\Moze4.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6367B0E6-A218-4865-99CA-53B26ADF3DDE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B6D77E-441A-4A34-A7BE-CA10B21B9A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="25815" windowHeight="15495" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Moze Dict" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="193">
   <si>
     <t>记录类型</t>
   </si>
@@ -694,6 +694,10 @@
   </si>
   <si>
     <t>蔬菜</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>未来城园区食堂</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1773,23 +1777,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
   <dimension ref="A1:R61"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.125" customWidth="1"/>
-    <col min="2" max="2" width="2.625" customWidth="1"/>
+    <col min="1" max="1" width="46.08203125" customWidth="1"/>
+    <col min="2" max="2" width="2.58203125" customWidth="1"/>
     <col min="7" max="7" width="2.25" customWidth="1"/>
-    <col min="8" max="8" width="2.875" customWidth="1"/>
-    <col min="9" max="9" width="4.375" customWidth="1"/>
-    <col min="10" max="10" width="10.875" customWidth="1"/>
-    <col min="11" max="11" width="16.125" customWidth="1"/>
-    <col min="12" max="12" width="11.875" customWidth="1"/>
-    <col min="13" max="13" width="3.125" customWidth="1"/>
-    <col min="14" max="14" width="12.375" customWidth="1"/>
-    <col min="15" max="15" width="16.125" customWidth="1"/>
+    <col min="8" max="8" width="2.83203125" customWidth="1"/>
+    <col min="9" max="9" width="4.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.08203125" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" customWidth="1"/>
+    <col min="13" max="13" width="3.08203125" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" customWidth="1"/>
+    <col min="15" max="15" width="16.08203125" customWidth="1"/>
     <col min="16" max="16" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>74</v>
       </c>
@@ -1845,7 +1849,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -1859,7 +1863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1873,7 +1877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1887,7 +1891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1901,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>157</v>
       </c>
@@ -1915,7 +1919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -1929,7 +1933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>155</v>
       </c>
@@ -1943,7 +1947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>183</v>
       </c>
@@ -1957,7 +1961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>158</v>
       </c>
@@ -1971,7 +1975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>168</v>
       </c>
@@ -1985,7 +1989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>175</v>
       </c>
@@ -1999,7 +2003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>178</v>
       </c>
@@ -2013,7 +2017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>181</v>
       </c>
@@ -2030,7 +2034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>190</v>
       </c>
@@ -2044,7 +2048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>186</v>
       </c>
@@ -2061,7 +2065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>185</v>
       </c>
@@ -2083,7 +2087,7 @@
       <c r="L17" s="12"/>
       <c r="M17" s="13"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -2106,7 +2110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -2129,7 +2133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>161</v>
       </c>
@@ -2155,7 +2159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>160</v>
       </c>
@@ -2178,7 +2182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>163</v>
       </c>
@@ -2195,7 +2199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>156</v>
       </c>
@@ -2212,7 +2216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>164</v>
       </c>
@@ -2232,7 +2236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2249,7 +2253,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2272,7 +2276,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>154</v>
       </c>
@@ -2289,7 +2293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>167</v>
       </c>
@@ -2309,7 +2313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>166</v>
       </c>
@@ -2326,7 +2330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2346,7 +2350,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -2366,7 +2370,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2383,7 +2387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -2400,7 +2404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>95</v>
       </c>
@@ -2414,7 +2418,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -2431,7 +2435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>42</v>
       </c>
@@ -2448,9 +2452,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>192</v>
       </c>
       <c r="C37" t="s">
         <v>79</v>
@@ -2461,11 +2465,8 @@
       <c r="O37" t="s">
         <v>15</v>
       </c>
-      <c r="R37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -2482,7 +2483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>140</v>
       </c>
@@ -2499,7 +2500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -2510,7 +2511,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -2521,7 +2522,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -2535,7 +2536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>91</v>
       </c>
@@ -2549,7 +2550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>172</v>
       </c>
@@ -2575,7 +2576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -2598,7 +2599,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -2621,7 +2622,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>86</v>
       </c>
@@ -2647,7 +2648,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>152</v>
       </c>
@@ -2681,7 +2682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>148</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>72</v>
       </c>
@@ -2733,7 +2734,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>38</v>
       </c>
@@ -2759,7 +2760,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>142</v>
       </c>
@@ -2785,7 +2786,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>180</v>
       </c>
@@ -2814,7 +2815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>179</v>
       </c>
@@ -2843,7 +2844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -2869,7 +2870,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>136</v>
       </c>
@@ -2898,7 +2899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>137</v>
       </c>
@@ -2927,7 +2928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>55</v>
       </c>
@@ -2950,7 +2951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>141</v>
       </c>
@@ -2979,7 +2980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>78</v>
       </c>
@@ -3011,7 +3012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>90</v>
       </c>
@@ -3042,12 +3043,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A67EEF5-ABF4-4CC5-BAC6-126980D50F95}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="1" max="1" width="26.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>96</v>
       </c>
@@ -3055,7 +3056,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>98</v>
       </c>
@@ -3063,7 +3064,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>100</v>
       </c>
@@ -3071,7 +3072,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>102</v>
       </c>
@@ -3079,7 +3080,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>104</v>
       </c>
@@ -3087,7 +3088,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>106</v>
       </c>
@@ -3095,7 +3096,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>108</v>
       </c>
@@ -3103,7 +3104,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>110</v>
       </c>
@@ -3111,7 +3112,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>112</v>
       </c>
@@ -3119,7 +3120,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>114</v>
       </c>
@@ -3127,7 +3128,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>116</v>
       </c>
@@ -3135,7 +3136,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>118</v>
       </c>
@@ -3143,7 +3144,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>120</v>
       </c>
@@ -3151,7 +3152,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>134</v>
       </c>
@@ -3159,7 +3160,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>123</v>
       </c>
@@ -3167,7 +3168,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>124</v>
       </c>
@@ -3175,7 +3176,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>126</v>
       </c>
@@ -3183,7 +3184,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>128</v>
       </c>
@@ -3191,7 +3192,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>130</v>
       </c>
@@ -3199,7 +3200,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>132</v>
       </c>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B6D77E-441A-4A34-A7BE-CA10B21B9A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8383ED88-4722-4A4A-8C14-B599A372D764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="195">
   <si>
     <t>记录类型</t>
   </si>
@@ -698,6 +698,14 @@
   </si>
   <si>
     <t>未来城园区食堂</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>安陆特色粉面馆</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚雄小吃</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1776,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.08203125" customWidth="1"/>
@@ -2065,54 +2073,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>185</v>
+    <row r="17" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>194</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" t="s">
-        <v>187</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>184</v>
-      </c>
-      <c r="K17" t="s">
-        <v>185</v>
-      </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="13"/>
+        <v>79</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="R17" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>185</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="K18" t="s">
-        <v>14</v>
-      </c>
-      <c r="R18">
-        <v>1</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="L18" s="12"/>
+      <c r="M18" s="13"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
         <v>79</v>
@@ -2127,7 +2126,7 @@
         <v>12</v>
       </c>
       <c r="K19" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -2135,7 +2134,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
         <v>79</v>
@@ -2149,11 +2148,8 @@
       <c r="F20" t="s">
         <v>12</v>
       </c>
-      <c r="J20" t="s">
-        <v>19</v>
-      </c>
       <c r="K20" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -2161,7 +2157,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C21" t="s">
         <v>79</v>
@@ -2175,8 +2171,11 @@
       <c r="F21" t="s">
         <v>12</v>
       </c>
+      <c r="J21" t="s">
+        <v>19</v>
+      </c>
       <c r="K21" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -2184,7 +2183,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C22" t="s">
         <v>79</v>
@@ -2192,8 +2191,14 @@
       <c r="D22" t="s">
         <v>159</v>
       </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
       <c r="K22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -2201,7 +2206,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C23" t="s">
         <v>79</v>
@@ -2210,7 +2215,7 @@
         <v>159</v>
       </c>
       <c r="K23" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -2218,7 +2223,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C24" t="s">
         <v>79</v>
@@ -2226,11 +2231,8 @@
       <c r="D24" t="s">
         <v>159</v>
       </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
       <c r="K24" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -2238,24 +2240,27 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="C25" t="s">
         <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
       </c>
       <c r="K25" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
         <v>79</v>
@@ -2266,19 +2271,13 @@
       <c r="E26" t="s">
         <v>11</v>
       </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
-      <c r="J26" t="s">
-        <v>165</v>
-      </c>
       <c r="K26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
         <v>79</v>
@@ -2286,16 +2285,22 @@
       <c r="D27" t="s">
         <v>10</v>
       </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" t="s">
+        <v>165</v>
+      </c>
       <c r="K27" t="s">
-        <v>27</v>
-      </c>
-      <c r="R27">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C28" t="s">
         <v>79</v>
@@ -2303,11 +2308,8 @@
       <c r="D28" t="s">
         <v>10</v>
       </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
       <c r="K28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -2315,7 +2317,7 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C29" t="s">
         <v>79</v>
@@ -2323,8 +2325,11 @@
       <c r="D29" t="s">
         <v>10</v>
       </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
       <c r="K29" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -2332,7 +2337,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
         <v>79</v>
@@ -2340,19 +2345,16 @@
       <c r="D30" t="s">
         <v>10</v>
       </c>
-      <c r="E30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
       <c r="K30" t="s">
-        <v>31</v>
+        <v>147</v>
+      </c>
+      <c r="R30">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
         <v>79</v>
@@ -2363,33 +2365,36 @@
       <c r="E31" t="s">
         <v>11</v>
       </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
       <c r="K31" t="s">
-        <v>33</v>
-      </c>
-      <c r="O31" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
         <v>79</v>
       </c>
+      <c r="D32" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
       <c r="K32" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O32" t="s">
-        <v>40</v>
-      </c>
-      <c r="R32">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
         <v>79</v>
@@ -2398,7 +2403,7 @@
         <v>41</v>
       </c>
       <c r="O33" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -2406,7 +2411,7 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
         <v>79</v>
@@ -2417,10 +2422,13 @@
       <c r="O34" t="s">
         <v>83</v>
       </c>
+      <c r="R34">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
         <v>79</v>
@@ -2431,13 +2439,10 @@
       <c r="O35" t="s">
         <v>83</v>
       </c>
-      <c r="R35">
-        <v>1</v>
-      </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
         <v>79</v>
@@ -2446,7 +2451,7 @@
         <v>41</v>
       </c>
       <c r="O36" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -2454,7 +2459,7 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>192</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
         <v>79</v>
@@ -2463,12 +2468,15 @@
         <v>41</v>
       </c>
       <c r="O37" t="s">
-        <v>15</v>
+        <v>42</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="C38" t="s">
         <v>79</v>
@@ -2477,15 +2485,12 @@
         <v>41</v>
       </c>
       <c r="O38" t="s">
-        <v>43</v>
-      </c>
-      <c r="R38">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
         <v>79</v>
@@ -2494,7 +2499,7 @@
         <v>41</v>
       </c>
       <c r="O39" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -2502,49 +2507,52 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
         <v>79</v>
       </c>
       <c r="K40" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="O40" t="s">
+        <v>140</v>
+      </c>
+      <c r="R40">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
       </c>
       <c r="K41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
         <v>79</v>
       </c>
       <c r="K42" t="s">
-        <v>48</v>
-      </c>
-      <c r="R42">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C43" t="s">
         <v>79</v>
       </c>
       <c r="K43" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="R43">
         <v>1</v>
@@ -2552,25 +2560,13 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
         <v>79</v>
       </c>
-      <c r="D44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>173</v>
-      </c>
       <c r="K44" t="s">
-        <v>174</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -2578,7 +2574,7 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="C45" t="s">
         <v>79</v>
@@ -2590,18 +2586,21 @@
         <v>53</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N45" t="s">
-        <v>81</v>
-      </c>
-      <c r="O45" t="s">
-        <v>94</v>
+        <v>173</v>
+      </c>
+      <c r="K45" t="s">
+        <v>174</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
         <v>79</v>
@@ -2609,22 +2608,22 @@
       <c r="D46" t="s">
         <v>10</v>
       </c>
-      <c r="E46" t="s">
-        <v>35</v>
-      </c>
-      <c r="F46" t="s">
-        <v>69</v>
-      </c>
-      <c r="K46" t="s">
-        <v>84</v>
+      <c r="E46" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="N46" t="s">
-        <v>85</v>
+        <v>81</v>
+      </c>
+      <c r="O46" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C47" t="s">
         <v>79</v>
@@ -2636,72 +2635,69 @@
         <v>35</v>
       </c>
       <c r="F47" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="K47" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N47" t="s">
         <v>85</v>
       </c>
-      <c r="O47" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>152</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D48" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" t="s">
         <v>35</v>
       </c>
-      <c r="F48" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="L48" s="9"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="R48">
-        <v>1</v>
+      <c r="F48" t="s">
+        <v>88</v>
+      </c>
+      <c r="K48" t="s">
+        <v>87</v>
+      </c>
+      <c r="N48" t="s">
+        <v>85</v>
+      </c>
+      <c r="O48" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>148</v>
-      </c>
-      <c r="C49" t="s">
+        <v>152</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="K49" t="s">
-        <v>150</v>
-      </c>
-      <c r="N49" t="s">
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L49" s="9"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="8" t="s">
         <v>139</v>
       </c>
       <c r="R49">
@@ -2710,10 +2706,10 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -2722,21 +2718,21 @@
         <v>35</v>
       </c>
       <c r="F50" t="s">
-        <v>36</v>
-      </c>
-      <c r="J50" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="K50" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="N50" t="s">
-        <v>71</v>
+        <v>139</v>
+      </c>
+      <c r="R50">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C51" t="s">
         <v>79</v>
@@ -2754,7 +2750,7 @@
         <v>37</v>
       </c>
       <c r="K51" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N51" t="s">
         <v>71</v>
@@ -2762,7 +2758,7 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="C52" t="s">
         <v>79</v>
@@ -2780,7 +2776,7 @@
         <v>37</v>
       </c>
       <c r="K52" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="N52" t="s">
         <v>71</v>
@@ -2788,7 +2784,7 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C53" t="s">
         <v>79</v>
@@ -2803,21 +2799,18 @@
         <v>36</v>
       </c>
       <c r="J53" t="s">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="K53" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="N53" t="s">
-        <v>139</v>
-      </c>
-      <c r="R53">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C54" t="s">
         <v>79</v>
@@ -2835,7 +2828,7 @@
         <v>153</v>
       </c>
       <c r="K54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N54" t="s">
         <v>139</v>
@@ -2846,7 +2839,7 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="C55" t="s">
         <v>79</v>
@@ -2855,24 +2848,27 @@
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F55" t="s">
-        <v>66</v>
+        <v>36</v>
+      </c>
+      <c r="J55" t="s">
+        <v>153</v>
       </c>
       <c r="K55" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="N55" t="s">
-        <v>50</v>
-      </c>
-      <c r="O55" s="11" t="s">
-        <v>51</v>
+        <v>139</v>
+      </c>
+      <c r="R55">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="C56" t="s">
         <v>79</v>
@@ -2884,24 +2880,21 @@
         <v>53</v>
       </c>
       <c r="F56" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="K56" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="N56" t="s">
-        <v>139</v>
-      </c>
-      <c r="O56">
-        <v>13297968006</v>
-      </c>
-      <c r="R56">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="O56" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C57" t="s">
         <v>79</v>
@@ -2916,13 +2909,13 @@
         <v>138</v>
       </c>
       <c r="K57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N57" t="s">
         <v>139</v>
       </c>
       <c r="O57">
-        <v>13638658298</v>
+        <v>13297968006</v>
       </c>
       <c r="R57">
         <v>1</v>
@@ -2930,7 +2923,7 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="C58" t="s">
         <v>79</v>
@@ -2942,10 +2935,16 @@
         <v>53</v>
       </c>
       <c r="F58" t="s">
-        <v>54</v>
+        <v>138</v>
+      </c>
+      <c r="K58" t="s">
+        <v>137</v>
       </c>
       <c r="N58" t="s">
-        <v>52</v>
+        <v>139</v>
+      </c>
+      <c r="O58">
+        <v>13638658298</v>
       </c>
       <c r="R58">
         <v>1</v>
@@ -2953,7 +2952,7 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C59" t="s">
         <v>79</v>
@@ -2962,51 +2961,42 @@
         <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="F59" t="s">
-        <v>145</v>
-      </c>
-      <c r="K59" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="N59" t="s">
         <v>52</v>
       </c>
-      <c r="O59" t="s">
-        <v>140</v>
-      </c>
       <c r="R59">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="C60" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="F60" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="K60" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="N60" t="s">
-        <v>39</v>
-      </c>
-      <c r="P60" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>64</v>
+        <v>52</v>
+      </c>
+      <c r="O60" t="s">
+        <v>140</v>
       </c>
       <c r="R60">
         <v>1</v>
@@ -3014,7 +3004,7 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C61" t="s">
         <v>63</v>
@@ -3028,12 +3018,44 @@
       <c r="F61" t="s">
         <v>67</v>
       </c>
+      <c r="K61" t="s">
+        <v>68</v>
+      </c>
       <c r="N61" t="s">
         <v>39</v>
       </c>
+      <c r="P61" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>64</v>
+      </c>
+      <c r="R61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C62" t="s">
+        <v>63</v>
+      </c>
+      <c r="D62" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" t="s">
+        <v>65</v>
+      </c>
+      <c r="F62" t="s">
+        <v>67</v>
+      </c>
+      <c r="N62" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R62" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
+  <autoFilter ref="A1:R63" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8383ED88-4722-4A4A-8C14-B599A372D764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7098D44D-C5D5-4A60-B140-EE99E2727EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="196">
   <si>
     <t>记录类型</t>
   </si>
@@ -685,10 +685,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>小饭馆</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>陈望云</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -706,6 +702,14 @@
   </si>
   <si>
     <t>聚雄小吃</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>川味小饭馆</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>武汉轻工大学</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1784,7 +1788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:R62"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.08203125" customWidth="1"/>
@@ -2044,13 +2048,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" t="s">
         <v>190</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="J15" t="s">
-        <v>191</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2064,7 +2068,7 @@
         <v>79</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="O16" s="14" t="s">
         <v>188</v>
@@ -2075,13 +2079,13 @@
     </row>
     <row r="17" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C17" t="s">
         <v>79</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R17" s="14">
         <v>1</v>
@@ -2394,7 +2398,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s">
         <v>79</v>
@@ -2403,15 +2407,12 @@
         <v>41</v>
       </c>
       <c r="O33" t="s">
-        <v>40</v>
-      </c>
-      <c r="R33">
-        <v>1</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
         <v>79</v>
@@ -2420,7 +2421,7 @@
         <v>41</v>
       </c>
       <c r="O34" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -2428,7 +2429,7 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
         <v>79</v>
@@ -2439,10 +2440,13 @@
       <c r="O35" t="s">
         <v>83</v>
       </c>
+      <c r="R35">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
         <v>79</v>
@@ -2453,13 +2457,10 @@
       <c r="O36" t="s">
         <v>83</v>
       </c>
-      <c r="R36">
-        <v>1</v>
-      </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
         <v>79</v>
@@ -2468,7 +2469,7 @@
         <v>41</v>
       </c>
       <c r="O37" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -2476,7 +2477,7 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>192</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
         <v>79</v>
@@ -2485,12 +2486,15 @@
         <v>41</v>
       </c>
       <c r="O38" t="s">
-        <v>15</v>
+        <v>42</v>
+      </c>
+      <c r="R38">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>191</v>
       </c>
       <c r="C39" t="s">
         <v>79</v>
@@ -2499,15 +2503,12 @@
         <v>41</v>
       </c>
       <c r="O39" t="s">
-        <v>43</v>
-      </c>
-      <c r="R39">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
         <v>79</v>
@@ -2516,7 +2517,7 @@
         <v>41</v>
       </c>
       <c r="O40" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -2524,49 +2525,52 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
       </c>
       <c r="K41" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="O41" t="s">
+        <v>140</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
         <v>79</v>
       </c>
       <c r="K42" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
         <v>79</v>
       </c>
       <c r="K43" t="s">
-        <v>48</v>
-      </c>
-      <c r="R43">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
         <v>79</v>
       </c>
       <c r="K44" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -2574,25 +2578,13 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="C45" t="s">
         <v>79</v>
       </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>173</v>
-      </c>
       <c r="K45" t="s">
-        <v>174</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -2600,7 +2592,7 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="C46" t="s">
         <v>79</v>
@@ -2612,18 +2604,21 @@
         <v>53</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N46" t="s">
-        <v>81</v>
-      </c>
-      <c r="O46" t="s">
-        <v>94</v>
+        <v>173</v>
+      </c>
+      <c r="K46" t="s">
+        <v>174</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R46">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
         <v>79</v>
@@ -2631,22 +2626,22 @@
       <c r="D47" t="s">
         <v>10</v>
       </c>
-      <c r="E47" t="s">
-        <v>35</v>
-      </c>
-      <c r="F47" t="s">
-        <v>69</v>
-      </c>
-      <c r="K47" t="s">
-        <v>84</v>
+      <c r="E47" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="N47" t="s">
-        <v>85</v>
+        <v>81</v>
+      </c>
+      <c r="O47" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
         <v>79</v>
@@ -2658,72 +2653,69 @@
         <v>35</v>
       </c>
       <c r="F48" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="K48" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N48" t="s">
         <v>85</v>
       </c>
-      <c r="O48" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>152</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D49" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" t="s">
         <v>35</v>
       </c>
-      <c r="F49" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="L49" s="9"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="R49">
-        <v>1</v>
+      <c r="F49" t="s">
+        <v>88</v>
+      </c>
+      <c r="K49" t="s">
+        <v>87</v>
+      </c>
+      <c r="N49" t="s">
+        <v>85</v>
+      </c>
+      <c r="O49" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>148</v>
-      </c>
-      <c r="C50" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="K50" t="s">
-        <v>150</v>
-      </c>
-      <c r="N50" t="s">
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L50" s="9"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="8" t="s">
         <v>139</v>
       </c>
       <c r="R50">
@@ -2732,10 +2724,10 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -2744,21 +2736,21 @@
         <v>35</v>
       </c>
       <c r="F51" t="s">
-        <v>36</v>
-      </c>
-      <c r="J51" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="K51" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="N51" t="s">
-        <v>71</v>
+        <v>139</v>
+      </c>
+      <c r="R51">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s">
         <v>79</v>
@@ -2776,7 +2768,7 @@
         <v>37</v>
       </c>
       <c r="K52" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N52" t="s">
         <v>71</v>
@@ -2784,7 +2776,7 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="C53" t="s">
         <v>79</v>
@@ -2802,7 +2794,7 @@
         <v>37</v>
       </c>
       <c r="K53" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="N53" t="s">
         <v>71</v>
@@ -2810,7 +2802,7 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C54" t="s">
         <v>79</v>
@@ -2825,21 +2817,18 @@
         <v>36</v>
       </c>
       <c r="J54" t="s">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="K54" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="N54" t="s">
-        <v>139</v>
-      </c>
-      <c r="R54">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C55" t="s">
         <v>79</v>
@@ -2857,7 +2846,7 @@
         <v>153</v>
       </c>
       <c r="K55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N55" t="s">
         <v>139</v>
@@ -2868,7 +2857,7 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="C56" t="s">
         <v>79</v>
@@ -2877,24 +2866,27 @@
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F56" t="s">
-        <v>66</v>
+        <v>36</v>
+      </c>
+      <c r="J56" t="s">
+        <v>153</v>
       </c>
       <c r="K56" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="N56" t="s">
-        <v>50</v>
-      </c>
-      <c r="O56" s="11" t="s">
-        <v>51</v>
+        <v>139</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="C57" t="s">
         <v>79</v>
@@ -2906,24 +2898,21 @@
         <v>53</v>
       </c>
       <c r="F57" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="K57" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="N57" t="s">
-        <v>139</v>
-      </c>
-      <c r="O57">
-        <v>13297968006</v>
-      </c>
-      <c r="R57">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="O57" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C58" t="s">
         <v>79</v>
@@ -2938,13 +2927,13 @@
         <v>138</v>
       </c>
       <c r="K58" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N58" t="s">
         <v>139</v>
       </c>
       <c r="O58">
-        <v>13638658298</v>
+        <v>13297968006</v>
       </c>
       <c r="R58">
         <v>1</v>
@@ -2952,7 +2941,7 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="C59" t="s">
         <v>79</v>
@@ -2964,10 +2953,16 @@
         <v>53</v>
       </c>
       <c r="F59" t="s">
-        <v>54</v>
+        <v>138</v>
+      </c>
+      <c r="K59" t="s">
+        <v>137</v>
       </c>
       <c r="N59" t="s">
-        <v>52</v>
+        <v>139</v>
+      </c>
+      <c r="O59">
+        <v>13638658298</v>
       </c>
       <c r="R59">
         <v>1</v>
@@ -2975,7 +2970,7 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C60" t="s">
         <v>79</v>
@@ -2984,51 +2979,42 @@
         <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="F60" t="s">
-        <v>145</v>
-      </c>
-      <c r="K60" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="N60" t="s">
         <v>52</v>
       </c>
-      <c r="O60" t="s">
-        <v>140</v>
-      </c>
       <c r="R60">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="C61" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="F61" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="K61" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="N61" t="s">
-        <v>39</v>
-      </c>
-      <c r="P61" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>64</v>
+        <v>52</v>
+      </c>
+      <c r="O61" t="s">
+        <v>140</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -3036,7 +3022,7 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C62" t="s">
         <v>63</v>
@@ -3050,12 +3036,44 @@
       <c r="F62" t="s">
         <v>67</v>
       </c>
+      <c r="K62" t="s">
+        <v>68</v>
+      </c>
       <c r="N62" t="s">
         <v>39</v>
       </c>
+      <c r="P62" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>64</v>
+      </c>
+      <c r="R62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" t="s">
+        <v>63</v>
+      </c>
+      <c r="D63" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" t="s">
+        <v>65</v>
+      </c>
+      <c r="F63" t="s">
+        <v>67</v>
+      </c>
+      <c r="N63" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R63" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
+  <autoFilter ref="A1:R64" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7098D44D-C5D5-4A60-B140-EE99E2727EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3599BE5-3557-46F1-B8C2-F507B33F83C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="195">
   <si>
     <t>记录类型</t>
   </si>
@@ -678,10 +678,6 @@
   </si>
   <si>
     <t>支出</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>正餐</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
@@ -2048,13 +2044,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" t="s">
         <v>189</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="J15" t="s">
-        <v>190</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2068,10 +2064,7 @@
         <v>79</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="O16" s="14" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="R16" s="14">
         <v>1</v>
@@ -2079,13 +2072,13 @@
     </row>
     <row r="17" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C17" t="s">
         <v>79</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R17" s="14">
         <v>1</v>
@@ -2398,7 +2391,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C33" t="s">
         <v>79</v>
@@ -2407,7 +2400,7 @@
         <v>41</v>
       </c>
       <c r="O33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
@@ -2494,7 +2487,7 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C39" t="s">
         <v>79</v>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3599BE5-3557-46F1-B8C2-F507B33F83C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C888C66-4F4B-4698-832B-54E9A79BCD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="196">
   <si>
     <t>记录类型</t>
   </si>
@@ -163,118 +163,396 @@
     <t>兼职</t>
   </si>
   <si>
+    <t>外勤</t>
+  </si>
+  <si>
+    <t>武汉工程大学</t>
+  </si>
+  <si>
+    <t>武汉大学</t>
+  </si>
+  <si>
+    <t>武汉市东湖新技术开发区泽源副食店</t>
+  </si>
+  <si>
+    <t>便邻便利店</t>
+  </si>
+  <si>
+    <t>中商超市珞喻路店</t>
+  </si>
+  <si>
+    <t>中商超市</t>
+  </si>
+  <si>
+    <t>拼多多</t>
+  </si>
+  <si>
+    <t>国网湖北省电力有限公司</t>
+  </si>
+  <si>
+    <t>住</t>
+  </si>
+  <si>
+    <t>海棠苑C4</t>
+  </si>
+  <si>
+    <t>日用&amp;家用</t>
+  </si>
+  <si>
+    <t>居家</t>
+  </si>
+  <si>
+    <t>理发</t>
+  </si>
+  <si>
+    <t>快剪</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>账户</t>
+  </si>
+  <si>
+    <t>币种</t>
+  </si>
+  <si>
+    <t>金额</t>
+  </si>
+  <si>
+    <t>手续费</t>
+  </si>
+  <si>
+    <t>折扣</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>时间</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>个人</t>
+  </si>
+  <si>
+    <t>电费</t>
+  </si>
+  <si>
+    <t>生意</t>
+  </si>
+  <si>
+    <t>1站租车</t>
+  </si>
+  <si>
+    <t>火车</t>
+  </si>
+  <si>
+    <t>武汉纯度餐饮管理有限公司</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼职</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>商家4201007064</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>叮叮充电</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>商家(old)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>超马鲜生</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>宜赞</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>自助服务</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>武汉市武昌区易站电动车维修服务部</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNY</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>馋不二</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>食</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏雪儿生活超市</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
     <t>湖北工业大学</t>
-  </si>
-  <si>
-    <t>外勤</t>
-  </si>
-  <si>
-    <t>武汉工程大学</t>
-  </si>
-  <si>
-    <t>武汉大学</t>
-  </si>
-  <si>
-    <t>武汉市东湖新技术开发区泽源副食店</t>
-  </si>
-  <si>
-    <t>便邻便利店</t>
-  </si>
-  <si>
-    <t>中商超市珞喻路店</t>
-  </si>
-  <si>
-    <t>中商超市</t>
-  </si>
-  <si>
-    <t>拼多多</t>
-  </si>
-  <si>
-    <t>国网湖北省电力有限公司</t>
-  </si>
-  <si>
-    <t>住</t>
-  </si>
-  <si>
-    <t>海棠苑C4</t>
-  </si>
-  <si>
-    <t>日用&amp;家用</t>
-  </si>
-  <si>
-    <t>居家</t>
-  </si>
-  <si>
-    <t>理发</t>
-  </si>
-  <si>
-    <t>快剪</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>账户</t>
-  </si>
-  <si>
-    <t>币种</t>
-  </si>
-  <si>
-    <t>金额</t>
-  </si>
-  <si>
-    <t>手续费</t>
-  </si>
-  <si>
-    <t>折扣</t>
-  </si>
-  <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>时间</t>
-  </si>
-  <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>个人</t>
-  </si>
-  <si>
-    <t>电费</t>
-  </si>
-  <si>
-    <t>生意</t>
-  </si>
-  <si>
-    <t>1站租车</t>
-  </si>
-  <si>
-    <t>火车</t>
-  </si>
-  <si>
-    <t>武汉纯度餐饮管理有限公司</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>兼职</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>商家4201007064</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>叮叮充电</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>商家(old)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>超马鲜生</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁路12306</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>通信&amp;交通</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖北公路客运集团宏基客运站</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>宏基客运站</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>汽车</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>大巴 宏基-李店</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪送</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>抖音</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢亮</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>液化气费</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4KG </t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>琪莉果园湖工草莓园店</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Words</t>
+  </si>
+  <si>
+    <t>FRUIT</t>
+  </si>
+  <si>
+    <t>水果, 果园, 果蔬, 百果园, 鲜果, 果业, 苹果, 香蕉, 红枣, 大枣, 桃子, 水蜜桃, 樱桃, 黄桃, 香梨, 雪梨, 柑橘, 沃柑, 草莓, 甘蔗, 桔子, 沙糖桔, 葡萄, 哈密瓜, 西瓜, 甜瓜, 柚子, 柠檬, 橙子, 菠萝, 凤梨, 榴莲, 山竹, 蓝莓, 荔枝, 龙眼, 椰子, 柿子, 杨梅, 李子, 芒果, 猕猴桃, 火龙果, 百香果, 莲雾, 车厘子, 牛油果, 鳄梨, 芭乐, 番石榴, 菠萝蜜, 桑葚, 枇杷, 杨桃, 无花果, 圣女果, 小番茄, 姑娘果, 西梅, 青枣, 冬枣, 黑布林, 人参果, 释迦, 耙耙柑</t>
+  </si>
+  <si>
+    <t>DRINK</t>
+  </si>
+  <si>
+    <t>可乐, 红牛, 奶茶, 东鹏, 饮料, 汽水, 果汁, 椰汁, 酸奶, 咖啡, 拿铁, 乐虎</t>
+  </si>
+  <si>
+    <t>WATER</t>
+  </si>
+  <si>
+    <t>纯净水, 矿泉水, 农夫山泉, 怡宝, 百岁山, 娃哈哈, 今麦郎</t>
+  </si>
+  <si>
+    <t>SOFTWARE</t>
+  </si>
+  <si>
+    <t>软件, APP, 应用</t>
+  </si>
+  <si>
+    <t>CHARGING</t>
+  </si>
+  <si>
+    <t>特来电, 星星充电, 小桔充电, 国家电网, 电费, 充电, e充电, 云快充, 蔚来, 特斯拉, 超充</t>
+  </si>
+  <si>
+    <t>VEGETABLE</t>
+  </si>
+  <si>
+    <t>青菜, 白菜, 娃娃菜, 菠菜, 生菜, 油麦菜, 韭菜, 芹菜, 香菜, 土豆, 茄子, 豆角, 辣椒, 青椒, 洋葱, 西红柿, 番茄, 黄瓜, 冬瓜, 南瓜, 苦瓜, 丝瓜, 萝卜, 胡萝卜, 藕, 莲藕, 笋, 莴笋, 蘑菇, 香菇, 金针菇, 木耳, 豆芽, 玉米, 红薯, 山药, 芋头</t>
+  </si>
+  <si>
+    <t>BEAN_PRODUCT</t>
+  </si>
+  <si>
+    <t>豆腐, 豆皮, 腐竹, 豆干, 豆腐泡, 素鸡, 千张, 豆卷, 腐皮, 油豆皮, 内脂豆腐, 老豆腐, 嫩豆腐, 冻豆腐, 响铃卷</t>
+  </si>
+  <si>
+    <t>INGREDIENTS</t>
+  </si>
+  <si>
+    <t>馒头, 火腿, 葱, 姜, 蒜, 酱料, 料酒, 白砂糖, 生抽, 老抽, 蒸肉粉, 榨菜, 辣椒酱, 老干妈, 胡椒粉, 火锅底料, 生水饺, 菠菜面条, 面条, 挂面, 红豆, 绿豆, 黄豆</t>
+  </si>
+  <si>
+    <t>PORK</t>
+  </si>
+  <si>
+    <t>猪肉, 扇子骨, 板油, 五花肉, 梅花肉, 瘦肉, 猪蹄膀, 蹄膀, 排骨, 脊骨, 五花, 前蹄, 大肠, 筒子骨, 棒骨, 猪油, 猪蹄</t>
+  </si>
+  <si>
+    <t>POULTRY</t>
+  </si>
+  <si>
+    <t>三黄鸡, 鸡腿, 鸡翅, 鸡胸肉, 老母鸡, 乌鸡, 鸭肉, 鸭腿, 鸭翅, 鸭架, 老鸭</t>
+  </si>
+  <si>
+    <t>BEEF_MUTTON</t>
+  </si>
+  <si>
+    <t>牛肉, 羊肉, 牛排, 肥牛, 羊排, 牛腩, 牛柳, 羊腿, 牛腱</t>
+  </si>
+  <si>
+    <t>SEAFOOD</t>
+  </si>
+  <si>
+    <t>鱼, 虾, 蟹, 贝, 带鱼, 黄鱼, 鲈鱼, 鲫鱼, 草鱼, 基围虾, 皮皮虾, 大闸蟹, 蛤蜊, 生蚝, 鱿鱼, 章鱼, 海带, 紫菜</t>
+  </si>
+  <si>
+    <t>鸡蛋, 土鸡蛋, 生咸鸭蛋, 皮蛋</t>
+  </si>
+  <si>
+    <t>COOKED</t>
+  </si>
+  <si>
+    <t>RICE</t>
+  </si>
+  <si>
+    <t>大米, 五常</t>
+  </si>
+  <si>
+    <t>MEAL</t>
+  </si>
+  <si>
+    <t>三镇民生, 兰州, 丝路, 沙县, 永和四喜, 水煎包, 老乡鸡, 混沌, 馄饨, 牛肉汤, 热干面, 黄蜀郎, 鸡公煲, 小吃, 烧烤, 食堂, 路边摊, 麦香园, 长沙臭豆腐, 东苑一层, 东苑二层, 西区食堂, 包子, 小笼包, 外勤, 板面, 水饺, 猪脚饭, 肠粉, 卤肉饭, 油泼面, 重庆小面, 牛杂粉, 麻辣香锅, 麻辣烫, 煎包, 煎饼, 烧饼, 锅盔, 馕, 土豆鸡蛋饼, 热干面, 牛肉面, 刀削面, 盖浇饭, 炒饭</t>
+  </si>
+  <si>
+    <t>DAILY_NECESSITIES</t>
+  </si>
+  <si>
+    <t>日常用品, 锅, 勺, 刀, 砧板, 擀面杖, 和面棒, 打蛋器, 压汁器, 料理机, 计时器, 切蛋器, 瓶起子, 筷, 碗, 杯, 袋, 瓶, 盒, 壶, 罐, 桶, 纸, 手套, 膜, 布, 洗洁精, 钢丝球, 牙刷, 牙膏, 漱口杯, 洗发水, 沐浴露, 香皂, 鼻毛修剪器, 掏耳勺, 抽纸, 卫生纸, 湿巾, 清凉油, 花露水, 洗衣粉, 洁厕灵, 除锈剂, 清洗剂, 拖把, 扫把, 水桶, 盆, 围裙, 衣架, 晒衣杆, 夹子, 挂钩, 置物架, 凳子垫, 雨伞, 锁, 灯, 电池, 插座, 理线器, 螺丝刀, 卷尺, 润滑油, 胶水</t>
+  </si>
+  <si>
+    <t>SERVER</t>
+  </si>
+  <si>
+    <t>节点, Dler, Dogess</t>
+  </si>
+  <si>
+    <t>BAD_SHOP</t>
+  </si>
+  <si>
+    <t>抖音, 支付宝, 微信, 转账, 扫码, 付款, 商户, 美团, 饿了么, 合并支付, 京东, 拼多多, 淘特, 特价版</t>
+  </si>
+  <si>
+    <t>EGGS</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>水煮花生, 毛豆, 藕夹, 茄盒, 锅包肉, 猪头肉, 卤菜, 凉菜, 熟食, 烧鸡, 烤鸭, 酱牛肉, 熏鱼, 炸带鱼, 炸鱿鱼, 肉丸, 墨鱼丸, 牛肉丸, 鱼丸, 虾滑, 贡丸, 鱿鱼圈, 糍粑, 熟咸鸭蛋,花生米</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国联通</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国移动</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>电话费</t>
+  </si>
+  <si>
+    <t>通信&amp;交通</t>
+  </si>
+  <si>
+    <t>华中农业大学</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>双辉印务荟十店</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳智链物联科技有限公司</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>猛犸</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>购物</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>摄影文印</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>双辉印务荟十店</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>安庆馄饨</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>高德顺风车</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>出租车</t>
+  </si>
+  <si>
+    <t>高德打车</t>
+  </si>
+  <si>
+    <t>滴滴</t>
+  </si>
+  <si>
+    <t>滴滴出行</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>加油</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏婉水果</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>零食顽家</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>永和四喜</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
@@ -282,287 +560,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>自助服务</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>武汉市武昌区易站电动车维修服务部</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNY</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>馋不二</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>食</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏雪儿生活超市</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>湖北工业大学</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁路12306</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>通信&amp;交通</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>湖北公路客运集团宏基客运站</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宏基客运站</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>汽车</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>大巴 宏基-李店</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪送</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>抖音</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>卢亮</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>液化气费</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">4KG </t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>琪莉果园湖工草莓园店</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Words</t>
-  </si>
-  <si>
-    <t>FRUIT</t>
-  </si>
-  <si>
-    <t>水果, 果园, 果蔬, 百果园, 鲜果, 果业, 苹果, 香蕉, 红枣, 大枣, 桃子, 水蜜桃, 樱桃, 黄桃, 香梨, 雪梨, 柑橘, 沃柑, 草莓, 甘蔗, 桔子, 沙糖桔, 葡萄, 哈密瓜, 西瓜, 甜瓜, 柚子, 柠檬, 橙子, 菠萝, 凤梨, 榴莲, 山竹, 蓝莓, 荔枝, 龙眼, 椰子, 柿子, 杨梅, 李子, 芒果, 猕猴桃, 火龙果, 百香果, 莲雾, 车厘子, 牛油果, 鳄梨, 芭乐, 番石榴, 菠萝蜜, 桑葚, 枇杷, 杨桃, 无花果, 圣女果, 小番茄, 姑娘果, 西梅, 青枣, 冬枣, 黑布林, 人参果, 释迦, 耙耙柑</t>
-  </si>
-  <si>
-    <t>DRINK</t>
-  </si>
-  <si>
-    <t>可乐, 红牛, 奶茶, 东鹏, 饮料, 汽水, 果汁, 椰汁, 酸奶, 咖啡, 拿铁, 乐虎</t>
-  </si>
-  <si>
-    <t>WATER</t>
-  </si>
-  <si>
-    <t>纯净水, 矿泉水, 农夫山泉, 怡宝, 百岁山, 娃哈哈, 今麦郎</t>
-  </si>
-  <si>
-    <t>SOFTWARE</t>
-  </si>
-  <si>
-    <t>软件, APP, 应用</t>
-  </si>
-  <si>
-    <t>CHARGING</t>
-  </si>
-  <si>
-    <t>特来电, 星星充电, 小桔充电, 国家电网, 电费, 充电, e充电, 云快充, 蔚来, 特斯拉, 超充</t>
-  </si>
-  <si>
-    <t>VEGETABLE</t>
-  </si>
-  <si>
-    <t>青菜, 白菜, 娃娃菜, 菠菜, 生菜, 油麦菜, 韭菜, 芹菜, 香菜, 土豆, 茄子, 豆角, 辣椒, 青椒, 洋葱, 西红柿, 番茄, 黄瓜, 冬瓜, 南瓜, 苦瓜, 丝瓜, 萝卜, 胡萝卜, 藕, 莲藕, 笋, 莴笋, 蘑菇, 香菇, 金针菇, 木耳, 豆芽, 玉米, 红薯, 山药, 芋头</t>
-  </si>
-  <si>
-    <t>BEAN_PRODUCT</t>
-  </si>
-  <si>
-    <t>豆腐, 豆皮, 腐竹, 豆干, 豆腐泡, 素鸡, 千张, 豆卷, 腐皮, 油豆皮, 内脂豆腐, 老豆腐, 嫩豆腐, 冻豆腐, 响铃卷</t>
-  </si>
-  <si>
-    <t>INGREDIENTS</t>
-  </si>
-  <si>
-    <t>馒头, 火腿, 葱, 姜, 蒜, 酱料, 料酒, 白砂糖, 生抽, 老抽, 蒸肉粉, 榨菜, 辣椒酱, 老干妈, 胡椒粉, 火锅底料, 生水饺, 菠菜面条, 面条, 挂面, 红豆, 绿豆, 黄豆</t>
-  </si>
-  <si>
-    <t>PORK</t>
-  </si>
-  <si>
-    <t>猪肉, 扇子骨, 板油, 五花肉, 梅花肉, 瘦肉, 猪蹄膀, 蹄膀, 排骨, 脊骨, 五花, 前蹄, 大肠, 筒子骨, 棒骨, 猪油, 猪蹄</t>
-  </si>
-  <si>
-    <t>POULTRY</t>
-  </si>
-  <si>
-    <t>三黄鸡, 鸡腿, 鸡翅, 鸡胸肉, 老母鸡, 乌鸡, 鸭肉, 鸭腿, 鸭翅, 鸭架, 老鸭</t>
-  </si>
-  <si>
-    <t>BEEF_MUTTON</t>
-  </si>
-  <si>
-    <t>牛肉, 羊肉, 牛排, 肥牛, 羊排, 牛腩, 牛柳, 羊腿, 牛腱</t>
-  </si>
-  <si>
-    <t>SEAFOOD</t>
-  </si>
-  <si>
-    <t>鱼, 虾, 蟹, 贝, 带鱼, 黄鱼, 鲈鱼, 鲫鱼, 草鱼, 基围虾, 皮皮虾, 大闸蟹, 蛤蜊, 生蚝, 鱿鱼, 章鱼, 海带, 紫菜</t>
-  </si>
-  <si>
-    <t>鸡蛋, 土鸡蛋, 生咸鸭蛋, 皮蛋</t>
-  </si>
-  <si>
-    <t>COOKED</t>
-  </si>
-  <si>
-    <t>RICE</t>
-  </si>
-  <si>
-    <t>大米, 五常</t>
-  </si>
-  <si>
-    <t>MEAL</t>
-  </si>
-  <si>
-    <t>三镇民生, 兰州, 丝路, 沙县, 永和四喜, 水煎包, 老乡鸡, 混沌, 馄饨, 牛肉汤, 热干面, 黄蜀郎, 鸡公煲, 小吃, 烧烤, 食堂, 路边摊, 麦香园, 长沙臭豆腐, 东苑一层, 东苑二层, 西区食堂, 包子, 小笼包, 外勤, 板面, 水饺, 猪脚饭, 肠粉, 卤肉饭, 油泼面, 重庆小面, 牛杂粉, 麻辣香锅, 麻辣烫, 煎包, 煎饼, 烧饼, 锅盔, 馕, 土豆鸡蛋饼, 热干面, 牛肉面, 刀削面, 盖浇饭, 炒饭</t>
-  </si>
-  <si>
-    <t>DAILY_NECESSITIES</t>
-  </si>
-  <si>
-    <t>日常用品, 锅, 勺, 刀, 砧板, 擀面杖, 和面棒, 打蛋器, 压汁器, 料理机, 计时器, 切蛋器, 瓶起子, 筷, 碗, 杯, 袋, 瓶, 盒, 壶, 罐, 桶, 纸, 手套, 膜, 布, 洗洁精, 钢丝球, 牙刷, 牙膏, 漱口杯, 洗发水, 沐浴露, 香皂, 鼻毛修剪器, 掏耳勺, 抽纸, 卫生纸, 湿巾, 清凉油, 花露水, 洗衣粉, 洁厕灵, 除锈剂, 清洗剂, 拖把, 扫把, 水桶, 盆, 围裙, 衣架, 晒衣杆, 夹子, 挂钩, 置物架, 凳子垫, 雨伞, 锁, 灯, 电池, 插座, 理线器, 螺丝刀, 卷尺, 润滑油, 胶水</t>
-  </si>
-  <si>
-    <t>SERVER</t>
-  </si>
-  <si>
-    <t>节点, Dler, Dogess</t>
-  </si>
-  <si>
-    <t>BAD_SHOP</t>
-  </si>
-  <si>
-    <t>抖音, 支付宝, 微信, 转账, 扫码, 付款, 商户, 美团, 饿了么, 合并支付, 京东, 拼多多, 淘特, 特价版</t>
-  </si>
-  <si>
-    <t>EGGS</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>水煮花生, 毛豆, 藕夹, 茄盒, 锅包肉, 猪头肉, 卤菜, 凉菜, 熟食, 烧鸡, 烤鸭, 酱牛肉, 熏鱼, 炸带鱼, 炸鱿鱼, 肉丸, 墨鱼丸, 牛肉丸, 鱼丸, 虾滑, 贡丸, 鱿鱼圈, 糍粑, 熟咸鸭蛋,花生米</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>中国联通</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>中国移动</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>电话费</t>
-  </si>
-  <si>
-    <t>通信&amp;交通</t>
-  </si>
-  <si>
-    <t>华中农业大学</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>双辉印务荟十店</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>深圳智链物联科技有限公司</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>猛犸</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>购物</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>摄影文印</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>双辉印务荟十店</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>安庆馄饨</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>高德顺风车</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>出租车</t>
-  </si>
-  <si>
-    <t>高德打车</t>
-  </si>
-  <si>
-    <t>滴滴</t>
-  </si>
-  <si>
-    <t>滴滴出行</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>加油</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>苏婉水果</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>零食顽家</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>永和四喜</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>宜赞</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>常青麦香园</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -706,6 +703,14 @@
   </si>
   <si>
     <t>武汉轻工大学</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹一</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>华农竹苑</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1784,7 +1789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.08203125" customWidth="1"/>
@@ -1803,13 +1808,13 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1821,13 +1826,13 @@
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>3</v>
@@ -1836,10 +1841,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>5</v>
@@ -1859,13 +1864,13 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1876,7 +1881,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K3" t="s">
         <v>18</v>
@@ -1890,7 +1895,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K4" t="s">
         <v>16</v>
@@ -1904,7 +1909,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -1915,13 +1920,13 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -1929,10 +1934,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K7" t="s">
         <v>29</v>
@@ -1943,13 +1948,13 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -1957,13 +1962,13 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -1971,13 +1976,13 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -1985,13 +1990,13 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" t="s">
         <v>168</v>
-      </c>
-      <c r="C11" t="s">
-        <v>79</v>
-      </c>
-      <c r="K11" t="s">
-        <v>169</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -1999,13 +2004,13 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" t="s">
         <v>175</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="K12" t="s">
-        <v>176</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2013,13 +2018,13 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2027,16 +2032,16 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" t="s">
         <v>181</v>
       </c>
-      <c r="C14" t="s">
-        <v>79</v>
-      </c>
-      <c r="J14" t="s">
-        <v>182</v>
-      </c>
       <c r="K14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -2044,13 +2049,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" t="s">
         <v>188</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="J15" t="s">
-        <v>189</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2058,13 +2063,13 @@
     </row>
     <row r="16" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R16" s="14">
         <v>1</v>
@@ -2072,13 +2077,13 @@
     </row>
     <row r="17" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R17" s="14">
         <v>1</v>
@@ -2086,22 +2091,22 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
       </c>
       <c r="F18" t="s">
+        <v>183</v>
+      </c>
+      <c r="K18" t="s">
         <v>184</v>
-      </c>
-      <c r="K18" t="s">
-        <v>185</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="13"/>
@@ -2111,10 +2116,10 @@
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
@@ -2134,10 +2139,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -2154,13 +2159,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -2172,7 +2177,7 @@
         <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -2180,13 +2185,13 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
@@ -2203,13 +2208,13 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K23" t="s">
         <v>21</v>
@@ -2220,16 +2225,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -2237,13 +2242,13 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
@@ -2260,7 +2265,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -2277,7 +2282,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -2289,7 +2294,7 @@
         <v>12</v>
       </c>
       <c r="J27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K27" t="s">
         <v>26</v>
@@ -2297,10 +2302,10 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -2314,10 +2319,10 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -2334,16 +2339,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
       </c>
       <c r="K30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -2354,7 +2359,7 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -2374,7 +2379,7 @@
         <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2391,30 +2396,30 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" t="s">
         <v>40</v>
       </c>
-      <c r="C34" t="s">
-        <v>79</v>
-      </c>
-      <c r="K34" t="s">
-        <v>41</v>
-      </c>
       <c r="O34" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -2422,47 +2427,47 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O35" t="s">
-        <v>83</v>
-      </c>
-      <c r="R35">
-        <v>1</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O36" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="R36">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K37" t="s">
+        <v>40</v>
+      </c>
+      <c r="O37" t="s">
         <v>41</v>
-      </c>
-      <c r="O37" t="s">
-        <v>83</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -2470,47 +2475,50 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O38" t="s">
-        <v>42</v>
-      </c>
-      <c r="R38">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O39" t="s">
-        <v>15</v>
+        <v>42</v>
+      </c>
+      <c r="R39">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>194</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
       </c>
       <c r="K40" t="s">
-        <v>41</v>
-      </c>
-      <c r="O40" t="s">
-        <v>43</v>
+        <v>195</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -2518,52 +2526,49 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K41" t="s">
-        <v>41</v>
-      </c>
-      <c r="O41" t="s">
-        <v>140</v>
-      </c>
-      <c r="R41">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K43" t="s">
         <v>47</v>
       </c>
+      <c r="R43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K44" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -2571,13 +2576,25 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="K45" t="s">
-        <v>91</v>
+        <v>173</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -2585,59 +2602,56 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="K46" t="s">
-        <v>174</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="R46">
-        <v>1</v>
+        <v>92</v>
+      </c>
+      <c r="N46" t="s">
+        <v>80</v>
+      </c>
+      <c r="O46" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>93</v>
+      <c r="E47" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" t="s">
+        <v>68</v>
+      </c>
+      <c r="K47" t="s">
+        <v>83</v>
       </c>
       <c r="N47" t="s">
-        <v>81</v>
-      </c>
-      <c r="O47" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -2646,70 +2660,73 @@
         <v>35</v>
       </c>
       <c r="F48" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="K48" t="s">
+        <v>86</v>
+      </c>
+      <c r="N48" t="s">
         <v>84</v>
       </c>
-      <c r="N48" t="s">
-        <v>85</v>
+      <c r="O48" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" t="s">
-        <v>79</v>
-      </c>
-      <c r="D49" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F49" t="s">
-        <v>88</v>
-      </c>
-      <c r="K49" t="s">
-        <v>87</v>
-      </c>
-      <c r="N49" t="s">
-        <v>85</v>
-      </c>
-      <c r="O49" t="s">
-        <v>89</v>
+      <c r="F49" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="L49" s="9"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="R49">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>152</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D50" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" t="s">
         <v>35</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" t="s">
+        <v>148</v>
+      </c>
+      <c r="K50" t="s">
         <v>149</v>
       </c>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="L50" s="9"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="8" t="s">
-        <v>139</v>
+      <c r="N50" t="s">
+        <v>138</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -2717,10 +2734,10 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>148</v>
+        <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -2729,24 +2746,24 @@
         <v>35</v>
       </c>
       <c r="F51" t="s">
-        <v>149</v>
+        <v>36</v>
+      </c>
+      <c r="J51" t="s">
+        <v>37</v>
       </c>
       <c r="K51" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="N51" t="s">
-        <v>139</v>
-      </c>
-      <c r="R51">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -2761,18 +2778,18 @@
         <v>37</v>
       </c>
       <c r="K52" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2787,18 +2804,18 @@
         <v>37</v>
       </c>
       <c r="K53" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="N53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="C54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -2810,21 +2827,24 @@
         <v>36</v>
       </c>
       <c r="J54" t="s">
-        <v>37</v>
+        <v>152</v>
       </c>
       <c r="K54" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="N54" t="s">
-        <v>71</v>
+        <v>138</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -2836,13 +2856,13 @@
         <v>36</v>
       </c>
       <c r="J55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K55" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R55">
         <v>1</v>
@@ -2850,57 +2870,57 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F56" t="s">
-        <v>36</v>
-      </c>
-      <c r="J56" t="s">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="K56" t="s">
-        <v>170</v>
+        <v>48</v>
       </c>
       <c r="N56" t="s">
-        <v>139</v>
-      </c>
-      <c r="R56">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="O56" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="E57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F57" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="K57" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="N57" t="s">
-        <v>50</v>
-      </c>
-      <c r="O57" s="11" t="s">
-        <v>51</v>
+        <v>138</v>
+      </c>
+      <c r="O57">
+        <v>13297968006</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
@@ -2908,25 +2928,25 @@
         <v>136</v>
       </c>
       <c r="C58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K58" t="s">
         <v>136</v>
       </c>
       <c r="N58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O58">
-        <v>13297968006</v>
+        <v>13638658298</v>
       </c>
       <c r="R58">
         <v>1</v>
@@ -2934,28 +2954,22 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
       </c>
       <c r="E59" t="s">
+        <v>52</v>
+      </c>
+      <c r="F59" t="s">
         <v>53</v>
       </c>
-      <c r="F59" t="s">
-        <v>138</v>
-      </c>
-      <c r="K59" t="s">
-        <v>137</v>
-      </c>
       <c r="N59" t="s">
-        <v>139</v>
-      </c>
-      <c r="O59">
-        <v>13638658298</v>
+        <v>51</v>
       </c>
       <c r="R59">
         <v>1</v>
@@ -2963,22 +2977,28 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="F60" t="s">
-        <v>54</v>
+        <v>144</v>
+      </c>
+      <c r="K60" t="s">
+        <v>145</v>
       </c>
       <c r="N60" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="O60" t="s">
+        <v>139</v>
       </c>
       <c r="R60">
         <v>1</v>
@@ -2986,28 +3006,31 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="F61" t="s">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="K61" t="s">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="N61" t="s">
-        <v>52</v>
-      </c>
-      <c r="O61" t="s">
-        <v>140</v>
+        <v>39</v>
+      </c>
+      <c r="P61" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>63</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -3015,58 +3038,26 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
       </c>
       <c r="E62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F62" t="s">
-        <v>67</v>
-      </c>
-      <c r="K62" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N62" t="s">
         <v>39</v>
       </c>
-      <c r="P62" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>64</v>
-      </c>
-      <c r="R62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>90</v>
-      </c>
-      <c r="C63" t="s">
-        <v>63</v>
-      </c>
-      <c r="D63" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" t="s">
-        <v>65</v>
-      </c>
-      <c r="F63" t="s">
-        <v>67</v>
-      </c>
-      <c r="N63" t="s">
-        <v>39</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R64" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
+  <autoFilter ref="A1:R63" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3083,162 +3074,162 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C888C66-4F4B-4698-832B-54E9A79BCD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAC34BF-8998-47B5-8E3C-3A8E863E8EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="198">
   <si>
     <t>记录类型</t>
   </si>
@@ -133,12 +133,6 @@
     <t>馋不二零食仓</t>
   </si>
   <si>
-    <t>张志锋13986072562</t>
-  </si>
-  <si>
-    <t>张志锋鱼摊</t>
-  </si>
-  <si>
     <t>春暖花开</t>
   </si>
   <si>
@@ -667,10 +661,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>斯迪姆幼儿园-柏思思</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>李李</t>
   </si>
   <si>
@@ -711,6 +701,26 @@
   </si>
   <si>
     <t>华农竹苑</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>斯迪姆</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>张正国鱼摊</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>张正国</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>斯迪姆美味补给站</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>柏来科技</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1789,7 +1799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:R62"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.08203125" customWidth="1"/>
@@ -1808,13 +1818,13 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1826,13 +1836,13 @@
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>3</v>
@@ -1841,10 +1851,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>5</v>
@@ -1864,13 +1874,13 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1881,7 +1891,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K3" t="s">
         <v>18</v>
@@ -1895,7 +1905,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K4" t="s">
         <v>16</v>
@@ -1909,7 +1919,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -1920,13 +1930,13 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -1934,10 +1944,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K7" t="s">
         <v>29</v>
@@ -1948,13 +1958,13 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -1962,13 +1972,13 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -1976,13 +1986,13 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -1990,13 +2000,13 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2004,13 +2014,13 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2018,13 +2028,13 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2032,16 +2042,16 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -2049,13 +2059,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J15" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2063,13 +2073,13 @@
     </row>
     <row r="16" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="R16" s="14">
         <v>1</v>
@@ -2077,13 +2087,13 @@
     </row>
     <row r="17" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="R17" s="14">
         <v>1</v>
@@ -2091,35 +2101,38 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K18" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="13"/>
+      <c r="R18">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
@@ -2139,10 +2152,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -2159,13 +2172,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -2177,7 +2190,7 @@
         <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -2185,13 +2198,13 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
@@ -2208,13 +2221,13 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K23" t="s">
         <v>21</v>
@@ -2225,16 +2238,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -2242,13 +2255,13 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
@@ -2265,7 +2278,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -2282,7 +2295,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -2294,7 +2307,7 @@
         <v>12</v>
       </c>
       <c r="J27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K27" t="s">
         <v>26</v>
@@ -2302,10 +2315,10 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -2319,10 +2332,10 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -2339,16 +2352,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
       </c>
       <c r="K30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -2356,10 +2369,10 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>195</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -2371,15 +2384,18 @@
         <v>12</v>
       </c>
       <c r="K31" t="s">
-        <v>31</v>
+        <v>194</v>
+      </c>
+      <c r="R31">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2388,38 +2404,38 @@
         <v>11</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O33" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K34" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O34" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -2427,30 +2443,30 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -2458,16 +2474,16 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O37" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -2475,13 +2491,13 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O38" t="s">
         <v>15</v>
@@ -2489,16 +2505,16 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K39" t="s">
+        <v>38</v>
+      </c>
+      <c r="O39" t="s">
         <v>40</v>
-      </c>
-      <c r="O39" t="s">
-        <v>42</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -2506,10 +2522,10 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -2518,7 +2534,7 @@
         <v>11</v>
       </c>
       <c r="K40" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -2526,35 +2542,35 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K42" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R43">
         <v>1</v>
@@ -2562,13 +2578,13 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -2576,25 +2592,25 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K45" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -2602,105 +2618,105 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N46" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F47" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K47" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N47" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F48" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s">
+        <v>84</v>
+      </c>
+      <c r="N48" t="s">
+        <v>82</v>
+      </c>
+      <c r="O48" t="s">
         <v>86</v>
-      </c>
-      <c r="N48" t="s">
-        <v>84</v>
-      </c>
-      <c r="O48" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L49" s="9"/>
       <c r="M49" s="10"/>
       <c r="N49" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R49">
         <v>1</v>
@@ -2708,25 +2724,25 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N50" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -2734,135 +2750,135 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
       </c>
       <c r="E51" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" t="s">
+        <v>34</v>
+      </c>
+      <c r="J51" t="s">
         <v>35</v>
       </c>
-      <c r="F51" t="s">
-        <v>36</v>
-      </c>
-      <c r="J51" t="s">
-        <v>37</v>
-      </c>
       <c r="K51" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C52" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
       </c>
       <c r="E52" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" t="s">
+        <v>34</v>
+      </c>
+      <c r="J52" t="s">
         <v>35</v>
       </c>
-      <c r="F52" t="s">
-        <v>36</v>
-      </c>
-      <c r="J52" t="s">
-        <v>37</v>
-      </c>
       <c r="K52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
       </c>
       <c r="E53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" t="s">
+        <v>34</v>
+      </c>
+      <c r="J53" t="s">
         <v>35</v>
       </c>
-      <c r="F53" t="s">
-        <v>36</v>
-      </c>
-      <c r="J53" t="s">
-        <v>37</v>
-      </c>
       <c r="K53" t="s">
-        <v>142</v>
+        <v>197</v>
       </c>
       <c r="N53" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="R53">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
       </c>
       <c r="E54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" t="s">
+        <v>34</v>
+      </c>
+      <c r="J54" t="s">
         <v>35</v>
       </c>
-      <c r="F54" t="s">
-        <v>36</v>
-      </c>
-      <c r="J54" t="s">
-        <v>152</v>
-      </c>
       <c r="K54" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="N54" t="s">
-        <v>138</v>
-      </c>
-      <c r="R54">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F55" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J55" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K55" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N55" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R55">
         <v>1</v>
@@ -2870,83 +2886,83 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>176</v>
       </c>
       <c r="C56" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="F56" t="s">
-        <v>65</v>
+        <v>34</v>
+      </c>
+      <c r="J56" t="s">
+        <v>150</v>
       </c>
       <c r="K56" t="s">
-        <v>48</v>
+        <v>167</v>
       </c>
       <c r="N56" t="s">
-        <v>49</v>
-      </c>
-      <c r="O56" s="11" t="s">
-        <v>50</v>
+        <v>136</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="E57" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F57" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="K57" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="N57" t="s">
-        <v>138</v>
-      </c>
-      <c r="O57">
-        <v>13297968006</v>
-      </c>
-      <c r="R57">
-        <v>1</v>
+        <v>47</v>
+      </c>
+      <c r="O57" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F58" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K58" t="s">
+        <v>133</v>
+      </c>
+      <c r="N58" t="s">
         <v>136</v>
       </c>
-      <c r="N58" t="s">
-        <v>138</v>
-      </c>
       <c r="O58">
-        <v>13638658298</v>
+        <v>13297968006</v>
       </c>
       <c r="R58">
         <v>1</v>
@@ -2954,22 +2970,28 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="C59" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F59" t="s">
-        <v>53</v>
+        <v>135</v>
+      </c>
+      <c r="K59" t="s">
+        <v>134</v>
       </c>
       <c r="N59" t="s">
-        <v>51</v>
+        <v>136</v>
+      </c>
+      <c r="O59">
+        <v>13638658298</v>
       </c>
       <c r="R59">
         <v>1</v>
@@ -2977,28 +2999,22 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="F60" t="s">
-        <v>144</v>
-      </c>
-      <c r="K60" t="s">
-        <v>145</v>
+        <v>51</v>
       </c>
       <c r="N60" t="s">
-        <v>51</v>
-      </c>
-      <c r="O60" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="R60">
         <v>1</v>
@@ -3006,31 +3022,28 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="F61" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="K61" t="s">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="N61" t="s">
-        <v>39</v>
-      </c>
-      <c r="P61" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>63</v>
+        <v>49</v>
+      </c>
+      <c r="O61" t="s">
+        <v>137</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -3038,26 +3051,58 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C62" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
       </c>
       <c r="E62" t="s">
+        <v>62</v>
+      </c>
+      <c r="F62" t="s">
         <v>64</v>
       </c>
-      <c r="F62" t="s">
-        <v>66</v>
+      <c r="K62" t="s">
+        <v>65</v>
       </c>
       <c r="N62" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="P62" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>61</v>
+      </c>
+      <c r="R62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>87</v>
+      </c>
+      <c r="C63" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" t="s">
+        <v>62</v>
+      </c>
+      <c r="F63" t="s">
+        <v>64</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R63" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
+  <autoFilter ref="A1:R64" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3074,162 +3119,162 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAC34BF-8998-47B5-8E3C-3A8E863E8EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D277ACA7-E861-40AB-AAE6-F6B8D70C5F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -82,9 +82,6 @@
     <t>食材</t>
   </si>
   <si>
-    <t>王记育林</t>
-  </si>
-  <si>
     <t>王记育林干货店</t>
   </si>
   <si>
@@ -721,6 +718,10 @@
   </si>
   <si>
     <t>柏来科技</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>育林</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1818,13 +1819,13 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1836,13 +1837,13 @@
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>3</v>
@@ -1851,10 +1852,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>5</v>
@@ -1874,13 +1875,13 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1888,13 +1889,13 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1902,13 +1903,13 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -1916,13 +1917,13 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -1930,13 +1931,13 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -1944,13 +1945,13 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -1958,13 +1959,13 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -1972,13 +1973,13 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -1986,13 +1987,13 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2000,13 +2001,13 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s">
         <v>165</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
-      </c>
-      <c r="K11" t="s">
-        <v>166</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2014,13 +2015,13 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" t="s">
         <v>172</v>
-      </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="K12" t="s">
-        <v>173</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2028,13 +2029,13 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2042,16 +2043,16 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="J14" t="s">
         <v>178</v>
       </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14" t="s">
-        <v>179</v>
-      </c>
       <c r="K14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -2059,13 +2060,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" t="s">
         <v>184</v>
-      </c>
-      <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15" t="s">
-        <v>185</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2073,13 +2074,13 @@
     </row>
     <row r="16" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R16" s="14">
         <v>1</v>
@@ -2087,13 +2088,13 @@
     </row>
     <row r="17" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R17" s="14">
         <v>1</v>
@@ -2101,22 +2102,22 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="13"/>
@@ -2126,13 +2127,13 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
@@ -2141,7 +2142,7 @@
         <v>12</v>
       </c>
       <c r="K19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -2149,13 +2150,13 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -2164,7 +2165,7 @@
         <v>12</v>
       </c>
       <c r="K20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -2172,13 +2173,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -2187,10 +2188,10 @@
         <v>12</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -2198,13 +2199,13 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
@@ -2213,7 +2214,7 @@
         <v>12</v>
       </c>
       <c r="K22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -2221,16 +2222,16 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -2238,16 +2239,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -2255,19 +2256,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
       </c>
       <c r="K25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -2275,10 +2276,10 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -2287,15 +2288,15 @@
         <v>11</v>
       </c>
       <c r="K26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -2307,24 +2308,24 @@
         <v>12</v>
       </c>
       <c r="J27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
       </c>
       <c r="K28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -2332,10 +2333,10 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -2344,7 +2345,7 @@
         <v>11</v>
       </c>
       <c r="K29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -2352,16 +2353,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
       </c>
       <c r="K30" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -2369,10 +2370,10 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -2384,7 +2385,7 @@
         <v>12</v>
       </c>
       <c r="K31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -2392,10 +2393,10 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -2404,38 +2405,38 @@
         <v>11</v>
       </c>
       <c r="K32" t="s">
+        <v>30</v>
+      </c>
+      <c r="O32" t="s">
         <v>31</v>
-      </c>
-      <c r="O32" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -2443,30 +2444,30 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="K36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
         <v>79</v>
-      </c>
-      <c r="C36" t="s">
-        <v>76</v>
-      </c>
-      <c r="K36" t="s">
-        <v>38</v>
-      </c>
-      <c r="O36" t="s">
-        <v>80</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -2474,16 +2475,16 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
         <v>38</v>
-      </c>
-      <c r="O37" t="s">
-        <v>39</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -2491,30 +2492,30 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -2522,10 +2523,10 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -2534,7 +2535,7 @@
         <v>11</v>
       </c>
       <c r="K40" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -2542,35 +2543,35 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>75</v>
+      </c>
+      <c r="K41" t="s">
         <v>41</v>
-      </c>
-      <c r="C41" t="s">
-        <v>76</v>
-      </c>
-      <c r="K41" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" t="s">
+        <v>75</v>
+      </c>
+      <c r="K42" t="s">
         <v>43</v>
-      </c>
-      <c r="C42" t="s">
-        <v>76</v>
-      </c>
-      <c r="K42" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R43">
         <v>1</v>
@@ -2578,13 +2579,13 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -2592,25 +2593,25 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F45" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="K45" t="s">
         <v>170</v>
       </c>
-      <c r="K45" t="s">
-        <v>171</v>
-      </c>
       <c r="N45" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -2618,105 +2619,105 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F46" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="N46" t="s">
+        <v>77</v>
+      </c>
+      <c r="O46" t="s">
         <v>90</v>
-      </c>
-      <c r="N46" t="s">
-        <v>78</v>
-      </c>
-      <c r="O46" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K47" t="s">
+        <v>80</v>
+      </c>
+      <c r="N47" t="s">
         <v>81</v>
-      </c>
-      <c r="N47" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F48" t="s">
+        <v>84</v>
+      </c>
+      <c r="K48" t="s">
+        <v>83</v>
+      </c>
+      <c r="N48" t="s">
+        <v>81</v>
+      </c>
+      <c r="O48" t="s">
         <v>85</v>
-      </c>
-      <c r="K48" t="s">
-        <v>84</v>
-      </c>
-      <c r="N48" t="s">
-        <v>82</v>
-      </c>
-      <c r="O48" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L49" s="9"/>
       <c r="M49" s="10"/>
       <c r="N49" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R49">
         <v>1</v>
@@ -2724,25 +2725,25 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F50" t="s">
+        <v>145</v>
+      </c>
+      <c r="K50" t="s">
         <v>146</v>
       </c>
-      <c r="K50" t="s">
-        <v>147</v>
-      </c>
       <c r="N50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -2750,80 +2751,80 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
       </c>
       <c r="E51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" t="s">
         <v>33</v>
       </c>
-      <c r="F51" t="s">
+      <c r="J51" t="s">
         <v>34</v>
       </c>
-      <c r="J51" t="s">
-        <v>35</v>
-      </c>
       <c r="K51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
       </c>
       <c r="E52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52" t="s">
         <v>33</v>
       </c>
-      <c r="F52" t="s">
+      <c r="J52" t="s">
         <v>34</v>
       </c>
-      <c r="J52" t="s">
-        <v>35</v>
-      </c>
       <c r="K52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
       </c>
       <c r="E53" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" t="s">
         <v>33</v>
       </c>
-      <c r="F53" t="s">
+      <c r="J53" t="s">
         <v>34</v>
       </c>
-      <c r="J53" t="s">
-        <v>35</v>
-      </c>
       <c r="K53" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R53">
         <v>1</v>
@@ -2831,54 +2832,54 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
       </c>
       <c r="E54" t="s">
+        <v>32</v>
+      </c>
+      <c r="F54" t="s">
         <v>33</v>
       </c>
-      <c r="F54" t="s">
+      <c r="J54" t="s">
         <v>34</v>
       </c>
-      <c r="J54" t="s">
-        <v>35</v>
-      </c>
       <c r="K54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
       </c>
       <c r="E55" t="s">
+        <v>32</v>
+      </c>
+      <c r="F55" t="s">
         <v>33</v>
       </c>
-      <c r="F55" t="s">
-        <v>34</v>
-      </c>
       <c r="J55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N55" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R55">
         <v>1</v>
@@ -2886,28 +2887,28 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
       </c>
       <c r="E56" t="s">
+        <v>32</v>
+      </c>
+      <c r="F56" t="s">
         <v>33</v>
       </c>
-      <c r="F56" t="s">
-        <v>34</v>
-      </c>
       <c r="J56" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K56" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N56" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -2915,51 +2916,51 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="E57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K57" t="s">
+        <v>45</v>
+      </c>
+      <c r="N57" t="s">
         <v>46</v>
       </c>
-      <c r="N57" t="s">
+      <c r="O57" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="O57" s="11" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F58" t="s">
+        <v>134</v>
+      </c>
+      <c r="K58" t="s">
+        <v>132</v>
+      </c>
+      <c r="N58" t="s">
         <v>135</v>
-      </c>
-      <c r="K58" t="s">
-        <v>133</v>
-      </c>
-      <c r="N58" t="s">
-        <v>136</v>
       </c>
       <c r="O58">
         <v>13297968006</v>
@@ -2970,25 +2971,25 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F59" t="s">
+        <v>134</v>
+      </c>
+      <c r="K59" t="s">
+        <v>133</v>
+      </c>
+      <c r="N59" t="s">
         <v>135</v>
-      </c>
-      <c r="K59" t="s">
-        <v>134</v>
-      </c>
-      <c r="N59" t="s">
-        <v>136</v>
       </c>
       <c r="O59">
         <v>13638658298</v>
@@ -2999,22 +3000,22 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
       </c>
       <c r="E60" t="s">
+        <v>49</v>
+      </c>
+      <c r="F60" t="s">
         <v>50</v>
       </c>
-      <c r="F60" t="s">
-        <v>51</v>
-      </c>
       <c r="N60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R60">
         <v>1</v>
@@ -3022,28 +3023,28 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
       </c>
       <c r="E61" t="s">
+        <v>140</v>
+      </c>
+      <c r="F61" t="s">
         <v>141</v>
       </c>
-      <c r="F61" t="s">
+      <c r="K61" t="s">
         <v>142</v>
       </c>
-      <c r="K61" t="s">
-        <v>143</v>
-      </c>
       <c r="N61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O61" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -3051,31 +3052,31 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
       </c>
       <c r="E62" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F62" t="s">
+        <v>63</v>
+      </c>
+      <c r="K62" t="s">
         <v>64</v>
       </c>
-      <c r="K62" t="s">
-        <v>65</v>
-      </c>
       <c r="N62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R62">
         <v>1</v>
@@ -3083,22 +3084,22 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D63" t="s">
         <v>10</v>
       </c>
       <c r="E63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3119,162 +3120,162 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D277ACA7-E861-40AB-AAE6-F6B8D70C5F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF7BF72-954F-4E0B-8B57-700A347E5EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$R$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$S$65</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="201">
   <si>
     <t>记录类型</t>
   </si>
@@ -154,9 +154,6 @@
     <t>兼职</t>
   </si>
   <si>
-    <t>外勤</t>
-  </si>
-  <si>
     <t>武汉工程大学</t>
   </si>
   <si>
@@ -722,6 +719,22 @@
   </si>
   <si>
     <t>育林</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>华中农业大学</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹一</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>华农竹苑</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1800,1310 +1813,1310 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.08203125" customWidth="1"/>
-    <col min="2" max="2" width="2.58203125" customWidth="1"/>
-    <col min="7" max="7" width="2.25" customWidth="1"/>
-    <col min="8" max="8" width="2.83203125" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.08203125" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" customWidth="1"/>
-    <col min="13" max="13" width="3.08203125" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" customWidth="1"/>
-    <col min="15" max="15" width="16.08203125" customWidth="1"/>
-    <col min="16" max="16" width="4.75" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="2.58203125" customWidth="1"/>
+    <col min="8" max="8" width="2.25" customWidth="1"/>
+    <col min="9" max="9" width="2.83203125" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.08203125" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" customWidth="1"/>
+    <col min="14" max="14" width="3.08203125" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" customWidth="1"/>
+    <col min="16" max="16" width="16.08203125" customWidth="1"/>
+    <col min="17" max="17" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K2" t="s">
-        <v>71</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="D3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" t="s">
         <v>17</v>
       </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" t="s">
         <v>15</v>
       </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" t="s">
+        <v>16</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" t="s">
+        <v>71</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>75</v>
       </c>
-      <c r="K5" t="s">
-        <v>16</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" t="s">
+        <v>28</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" t="s">
+        <v>150</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L9" t="s">
+        <v>178</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>153</v>
       </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="K6" t="s">
-        <v>72</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="K7" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" t="s">
-        <v>151</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" t="s">
-        <v>75</v>
-      </c>
-      <c r="K9" t="s">
-        <v>179</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
-      <c r="K10" t="s">
-        <v>154</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" t="s">
+        <v>153</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" t="s">
         <v>164</v>
       </c>
-      <c r="C11" t="s">
-        <v>75</v>
-      </c>
-      <c r="K11" t="s">
-        <v>165</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" t="s">
         <v>171</v>
       </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="S12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" t="s">
         <v>172</v>
       </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>174</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="K13" t="s">
-        <v>173</v>
-      </c>
-      <c r="R13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" t="s">
-        <v>75</v>
-      </c>
-      <c r="J14" t="s">
-        <v>178</v>
+        <v>176</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
       </c>
       <c r="K14" t="s">
         <v>177</v>
       </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L14" t="s">
+        <v>176</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s">
         <v>183</v>
       </c>
-      <c r="C15" t="s">
-        <v>75</v>
-      </c>
-      <c r="J15" t="s">
-        <v>184</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="S15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="S16" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="S17" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>191</v>
+      </c>
+      <c r="D18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" t="s">
         <v>181</v>
       </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="R16" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="R17" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>192</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>11</v>
       </c>
-      <c r="F18" t="s">
-        <v>180</v>
-      </c>
-      <c r="K18" t="s">
-        <v>195</v>
-      </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="13"/>
-      <c r="R18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="G18" t="s">
+        <v>179</v>
+      </c>
+      <c r="L18" t="s">
+        <v>194</v>
+      </c>
+      <c r="M18" s="12"/>
+      <c r="N18" s="13"/>
+      <c r="S18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>197</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
+        <v>196</v>
       </c>
       <c r="D19" t="s">
-        <v>155</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" t="s">
         <v>11</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>12</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>13</v>
       </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
-        <v>75</v>
-      </c>
       <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" t="s">
+        <v>23</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" t="s">
+        <v>12</v>
+      </c>
+      <c r="K21" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" t="s">
+        <v>157</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>155</v>
       </c>
-      <c r="E20" t="s">
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" t="s">
         <v>11</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G22" t="s">
         <v>12</v>
       </c>
-      <c r="K20" t="s">
-        <v>23</v>
-      </c>
-      <c r="R20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="L22" t="s">
+        <v>19</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s">
+        <v>154</v>
+      </c>
+      <c r="L23" t="s">
+        <v>20</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="L24" t="s">
+        <v>151</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>159</v>
+      </c>
+      <c r="D25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" t="s">
+        <v>154</v>
+      </c>
+      <c r="F25" t="s">
         <v>11</v>
       </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="J21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" t="s">
-        <v>158</v>
-      </c>
-      <c r="R21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>156</v>
-      </c>
-      <c r="C22" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" t="s">
-        <v>155</v>
-      </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22" t="s">
-        <v>19</v>
-      </c>
-      <c r="R22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>159</v>
-      </c>
-      <c r="C23" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" t="s">
-        <v>155</v>
-      </c>
-      <c r="K23" t="s">
-        <v>20</v>
-      </c>
-      <c r="R23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" t="s">
-        <v>155</v>
-      </c>
-      <c r="K24" t="s">
-        <v>152</v>
-      </c>
-      <c r="R24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>160</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>155</v>
-      </c>
-      <c r="E25" t="s">
-        <v>11</v>
-      </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>21</v>
       </c>
-      <c r="R25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
-      <c r="C26" t="s">
-        <v>75</v>
-      </c>
       <c r="D26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" t="s">
         <v>10</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>11</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
       <c r="D27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" t="s">
         <v>10</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>11</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>12</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
+        <v>160</v>
+      </c>
+      <c r="L27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="L28" t="s">
+        <v>26</v>
+      </c>
+      <c r="S28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="L29" t="s">
+        <v>27</v>
+      </c>
+      <c r="S29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>161</v>
       </c>
-      <c r="K27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>150</v>
-      </c>
-      <c r="C28" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="D30" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" t="s">
         <v>10</v>
       </c>
-      <c r="K28" t="s">
-        <v>26</v>
-      </c>
-      <c r="R28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>163</v>
-      </c>
-      <c r="C29" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="L30" t="s">
+        <v>142</v>
+      </c>
+      <c r="S30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" t="s">
         <v>10</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F31" t="s">
         <v>11</v>
       </c>
-      <c r="K29" t="s">
-        <v>27</v>
-      </c>
-      <c r="R29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>162</v>
-      </c>
-      <c r="C30" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" t="s">
-        <v>10</v>
-      </c>
-      <c r="K30" t="s">
-        <v>143</v>
-      </c>
-      <c r="R30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>194</v>
-      </c>
-      <c r="C31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>12</v>
       </c>
-      <c r="K31" t="s">
-        <v>193</v>
-      </c>
-      <c r="R31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L31" t="s">
+        <v>192</v>
+      </c>
+      <c r="S31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="C32" t="s">
-        <v>75</v>
-      </c>
       <c r="D32" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" t="s">
         <v>10</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>11</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>30</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>188</v>
+      </c>
+      <c r="D33" t="s">
+        <v>74</v>
+      </c>
+      <c r="P33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" t="s">
+        <v>74</v>
+      </c>
+      <c r="P34" t="s">
+        <v>78</v>
+      </c>
+      <c r="S34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" t="s">
+        <v>74</v>
+      </c>
+      <c r="P35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" t="s">
+        <v>74</v>
+      </c>
+      <c r="P36" t="s">
+        <v>78</v>
+      </c>
+      <c r="S36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" t="s">
+        <v>74</v>
+      </c>
+      <c r="P37" t="s">
+        <v>37</v>
+      </c>
+      <c r="S37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>184</v>
+      </c>
+      <c r="D38" t="s">
+        <v>74</v>
+      </c>
+      <c r="P38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>198</v>
+      </c>
+      <c r="B39" t="s">
+        <v>199</v>
+      </c>
+      <c r="D39" t="s">
+        <v>74</v>
+      </c>
+      <c r="L39" t="s">
+        <v>200</v>
+      </c>
+      <c r="S39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s">
+        <v>74</v>
+      </c>
+      <c r="P40" t="s">
+        <v>38</v>
+      </c>
+      <c r="S40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>189</v>
       </c>
-      <c r="C33" t="s">
-        <v>75</v>
-      </c>
-      <c r="K33" t="s">
-        <v>37</v>
-      </c>
-      <c r="O33" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="D41" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="L41" t="s">
+        <v>190</v>
+      </c>
+      <c r="S41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>74</v>
+      </c>
+      <c r="L42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" t="s">
+        <v>74</v>
+      </c>
+      <c r="L44" t="s">
+        <v>43</v>
+      </c>
+      <c r="S44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" t="s">
+        <v>74</v>
+      </c>
+      <c r="L45" t="s">
+        <v>86</v>
+      </c>
+      <c r="S45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>167</v>
+      </c>
+      <c r="D46" t="s">
+        <v>74</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="L46" t="s">
+        <v>169</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" t="s">
+        <v>74</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="O47" t="s">
+        <v>76</v>
+      </c>
+      <c r="P47" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" t="s">
+        <v>74</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" t="s">
+        <v>64</v>
+      </c>
+      <c r="L48" t="s">
+        <v>79</v>
+      </c>
+      <c r="O48" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" t="s">
+        <v>74</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" t="s">
+        <v>83</v>
+      </c>
+      <c r="L49" t="s">
+        <v>82</v>
+      </c>
+      <c r="O49" t="s">
+        <v>80</v>
+      </c>
+      <c r="P49" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>147</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="M50" s="9"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="S50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G51" t="s">
+        <v>144</v>
+      </c>
+      <c r="L51" t="s">
+        <v>145</v>
+      </c>
+      <c r="O51" t="s">
+        <v>134</v>
+      </c>
+      <c r="S51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" t="s">
+        <v>74</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" t="s">
+        <v>32</v>
+      </c>
+      <c r="G52" t="s">
+        <v>33</v>
+      </c>
+      <c r="K52" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52" t="s">
+        <v>68</v>
+      </c>
+      <c r="O52" t="s">
         <v>66</v>
       </c>
-      <c r="C34" t="s">
-        <v>75</v>
-      </c>
-      <c r="K34" t="s">
-        <v>37</v>
-      </c>
-      <c r="O34" t="s">
-        <v>79</v>
-      </c>
-      <c r="R34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" t="s">
-        <v>75</v>
-      </c>
-      <c r="K35" t="s">
-        <v>37</v>
-      </c>
-      <c r="O35" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" t="s">
-        <v>75</v>
-      </c>
-      <c r="K36" t="s">
-        <v>37</v>
-      </c>
-      <c r="O36" t="s">
-        <v>79</v>
-      </c>
-      <c r="R36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
-      <c r="K37" t="s">
-        <v>37</v>
-      </c>
-      <c r="O37" t="s">
-        <v>38</v>
-      </c>
-      <c r="R37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>185</v>
-      </c>
-      <c r="C38" t="s">
-        <v>75</v>
-      </c>
-      <c r="K38" t="s">
-        <v>37</v>
-      </c>
-      <c r="O38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C39" t="s">
-        <v>75</v>
-      </c>
-      <c r="K39" t="s">
-        <v>37</v>
-      </c>
-      <c r="O39" t="s">
-        <v>39</v>
-      </c>
-      <c r="R39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>190</v>
-      </c>
-      <c r="C40" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40" t="s">
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53" t="s">
         <v>10</v>
       </c>
-      <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="K40" t="s">
-        <v>191</v>
-      </c>
-      <c r="R40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" t="s">
-        <v>75</v>
-      </c>
-      <c r="K41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" t="s">
-        <v>75</v>
-      </c>
-      <c r="K42" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" t="s">
-        <v>75</v>
-      </c>
-      <c r="K43" t="s">
-        <v>44</v>
-      </c>
-      <c r="R43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" t="s">
-        <v>75</v>
-      </c>
-      <c r="K44" t="s">
-        <v>87</v>
-      </c>
-      <c r="R44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>168</v>
-      </c>
-      <c r="C45" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="F53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G53" t="s">
+        <v>33</v>
+      </c>
+      <c r="K53" t="s">
+        <v>34</v>
+      </c>
+      <c r="L53" t="s">
+        <v>72</v>
+      </c>
+      <c r="O53" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>195</v>
+      </c>
+      <c r="D54" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="K45" t="s">
-        <v>170</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="F54" t="s">
+        <v>32</v>
+      </c>
+      <c r="G54" t="s">
+        <v>33</v>
+      </c>
+      <c r="K54" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54" t="s">
+        <v>195</v>
+      </c>
+      <c r="O54" t="s">
+        <v>66</v>
+      </c>
+      <c r="S54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55" t="s">
         <v>10</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="N46" t="s">
-        <v>77</v>
-      </c>
-      <c r="O46" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="F55" t="s">
         <v>32</v>
       </c>
-      <c r="F47" t="s">
-        <v>65</v>
-      </c>
-      <c r="K47" t="s">
-        <v>80</v>
-      </c>
-      <c r="N47" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
-        <v>32</v>
-      </c>
-      <c r="F48" t="s">
-        <v>84</v>
-      </c>
-      <c r="K48" t="s">
-        <v>83</v>
-      </c>
-      <c r="N48" t="s">
-        <v>81</v>
-      </c>
-      <c r="O48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>148</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="L49" s="9"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="R49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>144</v>
-      </c>
-      <c r="C50" t="s">
-        <v>59</v>
-      </c>
-      <c r="D50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" t="s">
-        <v>32</v>
-      </c>
-      <c r="F50" t="s">
-        <v>145</v>
-      </c>
-      <c r="K50" t="s">
-        <v>146</v>
-      </c>
-      <c r="N50" t="s">
-        <v>135</v>
-      </c>
-      <c r="R50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>68</v>
-      </c>
-      <c r="C51" t="s">
-        <v>75</v>
-      </c>
-      <c r="D51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" t="s">
-        <v>32</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G55" t="s">
         <v>33</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K55" t="s">
         <v>34</v>
       </c>
-      <c r="K51" t="s">
-        <v>69</v>
-      </c>
-      <c r="N51" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>35</v>
-      </c>
-      <c r="C52" t="s">
-        <v>75</v>
-      </c>
-      <c r="D52" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" t="s">
-        <v>32</v>
-      </c>
-      <c r="F52" t="s">
-        <v>33</v>
-      </c>
-      <c r="J52" t="s">
-        <v>34</v>
-      </c>
-      <c r="K52" t="s">
-        <v>73</v>
-      </c>
-      <c r="N52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C53" t="s">
-        <v>75</v>
-      </c>
-      <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>32</v>
-      </c>
-      <c r="F53" t="s">
-        <v>33</v>
-      </c>
-      <c r="J53" t="s">
-        <v>34</v>
-      </c>
-      <c r="K53" t="s">
-        <v>196</v>
-      </c>
-      <c r="N53" t="s">
-        <v>67</v>
-      </c>
-      <c r="R53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="L55" t="s">
         <v>138</v>
       </c>
-      <c r="C54" t="s">
-        <v>75</v>
-      </c>
-      <c r="D54" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" t="s">
-        <v>32</v>
-      </c>
-      <c r="F54" t="s">
-        <v>33</v>
-      </c>
-      <c r="J54" t="s">
-        <v>34</v>
-      </c>
-      <c r="K54" t="s">
-        <v>139</v>
-      </c>
-      <c r="N54" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>176</v>
-      </c>
-      <c r="C55" t="s">
-        <v>75</v>
-      </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" t="s">
-        <v>32</v>
-      </c>
-      <c r="F55" t="s">
-        <v>33</v>
-      </c>
-      <c r="J55" t="s">
-        <v>149</v>
-      </c>
-      <c r="K55" t="s">
-        <v>167</v>
-      </c>
-      <c r="N55" t="s">
-        <v>135</v>
-      </c>
-      <c r="R55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="O55" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>175</v>
       </c>
-      <c r="C56" t="s">
-        <v>75</v>
-      </c>
       <c r="D56" t="s">
+        <v>74</v>
+      </c>
+      <c r="E56" t="s">
         <v>10</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>32</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>33</v>
       </c>
-      <c r="J56" t="s">
-        <v>149</v>
-      </c>
       <c r="K56" t="s">
+        <v>148</v>
+      </c>
+      <c r="L56" t="s">
         <v>166</v>
       </c>
-      <c r="N56" t="s">
+      <c r="O56" t="s">
+        <v>134</v>
+      </c>
+      <c r="S56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" t="s">
+        <v>74</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s">
+        <v>32</v>
+      </c>
+      <c r="G57" t="s">
+        <v>33</v>
+      </c>
+      <c r="K57" t="s">
+        <v>148</v>
+      </c>
+      <c r="L57" t="s">
+        <v>165</v>
+      </c>
+      <c r="O57" t="s">
+        <v>134</v>
+      </c>
+      <c r="S57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" t="s">
+        <v>74</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
+        <v>48</v>
+      </c>
+      <c r="G58" t="s">
+        <v>61</v>
+      </c>
+      <c r="L58" t="s">
+        <v>44</v>
+      </c>
+      <c r="O58" t="s">
+        <v>45</v>
+      </c>
+      <c r="P58" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>131</v>
+      </c>
+      <c r="D59" t="s">
+        <v>74</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" t="s">
+        <v>48</v>
+      </c>
+      <c r="G59" t="s">
+        <v>133</v>
+      </c>
+      <c r="L59" t="s">
+        <v>131</v>
+      </c>
+      <c r="O59" t="s">
+        <v>134</v>
+      </c>
+      <c r="P59">
+        <v>13297968006</v>
+      </c>
+      <c r="S59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>132</v>
+      </c>
+      <c r="D60" t="s">
+        <v>74</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" t="s">
+        <v>133</v>
+      </c>
+      <c r="L60" t="s">
+        <v>132</v>
+      </c>
+      <c r="O60" t="s">
+        <v>134</v>
+      </c>
+      <c r="P60">
+        <v>13638658298</v>
+      </c>
+      <c r="S60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>50</v>
+      </c>
+      <c r="D61" t="s">
+        <v>74</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G61" t="s">
+        <v>49</v>
+      </c>
+      <c r="O61" t="s">
+        <v>47</v>
+      </c>
+      <c r="S61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>136</v>
+      </c>
+      <c r="D62" t="s">
+        <v>74</v>
+      </c>
+      <c r="E62" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
+        <v>139</v>
+      </c>
+      <c r="G62" t="s">
+        <v>140</v>
+      </c>
+      <c r="L62" t="s">
+        <v>141</v>
+      </c>
+      <c r="O62" t="s">
+        <v>47</v>
+      </c>
+      <c r="P62" t="s">
         <v>135</v>
       </c>
-      <c r="R56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>45</v>
-      </c>
-      <c r="C57" t="s">
-        <v>75</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="S62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>73</v>
+      </c>
+      <c r="D63" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" t="s">
         <v>10</v>
       </c>
-      <c r="E57" t="s">
-        <v>49</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="F63" t="s">
+        <v>60</v>
+      </c>
+      <c r="G63" t="s">
         <v>62</v>
       </c>
-      <c r="K57" t="s">
-        <v>45</v>
-      </c>
-      <c r="N57" t="s">
-        <v>46</v>
-      </c>
-      <c r="O57" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>132</v>
-      </c>
-      <c r="C58" t="s">
-        <v>75</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="L63" t="s">
+        <v>63</v>
+      </c>
+      <c r="O63" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>59</v>
+      </c>
+      <c r="R63" t="s">
+        <v>59</v>
+      </c>
+      <c r="S63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>85</v>
+      </c>
+      <c r="D64" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" t="s">
         <v>10</v>
       </c>
-      <c r="E58" t="s">
-        <v>49</v>
-      </c>
-      <c r="F58" t="s">
-        <v>134</v>
-      </c>
-      <c r="K58" t="s">
-        <v>132</v>
-      </c>
-      <c r="N58" t="s">
-        <v>135</v>
-      </c>
-      <c r="O58">
-        <v>13297968006</v>
-      </c>
-      <c r="R58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59" t="s">
-        <v>75</v>
-      </c>
-      <c r="D59" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" t="s">
-        <v>49</v>
-      </c>
-      <c r="F59" t="s">
-        <v>134</v>
-      </c>
-      <c r="K59" t="s">
-        <v>133</v>
-      </c>
-      <c r="N59" t="s">
-        <v>135</v>
-      </c>
-      <c r="O59">
-        <v>13638658298</v>
-      </c>
-      <c r="R59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>51</v>
-      </c>
-      <c r="C60" t="s">
-        <v>75</v>
-      </c>
-      <c r="D60" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" t="s">
-        <v>49</v>
-      </c>
-      <c r="F60" t="s">
-        <v>50</v>
-      </c>
-      <c r="N60" t="s">
-        <v>48</v>
-      </c>
-      <c r="R60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>137</v>
-      </c>
-      <c r="C61" t="s">
-        <v>75</v>
-      </c>
-      <c r="D61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" t="s">
-        <v>140</v>
-      </c>
-      <c r="F61" t="s">
-        <v>141</v>
-      </c>
-      <c r="K61" t="s">
-        <v>142</v>
-      </c>
-      <c r="N61" t="s">
-        <v>48</v>
-      </c>
-      <c r="O61" t="s">
-        <v>136</v>
-      </c>
-      <c r="R61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" t="s">
-        <v>59</v>
-      </c>
-      <c r="D62" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" t="s">
-        <v>61</v>
-      </c>
-      <c r="F62" t="s">
-        <v>63</v>
-      </c>
-      <c r="K62" t="s">
-        <v>64</v>
-      </c>
-      <c r="N62" t="s">
+      <c r="F64" t="s">
+        <v>60</v>
+      </c>
+      <c r="G64" t="s">
+        <v>62</v>
+      </c>
+      <c r="O64" t="s">
         <v>36</v>
       </c>
-      <c r="P62" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>60</v>
-      </c>
-      <c r="R62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>86</v>
-      </c>
-      <c r="C63" t="s">
-        <v>59</v>
-      </c>
-      <c r="D63" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" t="s">
-        <v>61</v>
-      </c>
-      <c r="F63" t="s">
-        <v>63</v>
-      </c>
-      <c r="N63" t="s">
-        <v>36</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R64" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
+  <autoFilter ref="A1:S65" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3120,162 +3133,162 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF7BF72-954F-4E0B-8B57-700A347E5EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F3FD56-3383-49C5-A1AF-88D0466D6B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="207">
   <si>
     <t>记录类型</t>
   </si>
@@ -287,10 +287,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>夏雪儿生活超市</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>湖北工业大学</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -690,6 +686,38 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
+    <t>斯迪姆</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>张正国鱼摊</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>张正国</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>斯迪姆美味补给站</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>柏来科技</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>育林</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>华中农业大学</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
     <t>竹一</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -698,43 +726,39 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>斯迪姆</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>张正国鱼摊</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>张正国</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>斯迪姆美味补给站</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>柏来科技</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>育林</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>商品</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>华中农业大学</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>竹一</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>华农竹苑</t>
+    <t>食</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>武汉工程大学</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖北工业大学</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖工东苑</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>东苑</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>武汉工程大学</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>中南民族大学</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>中心食堂</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>民大中心食堂</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1817,8 +1841,8 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.08203125" customWidth="1"/>
-    <col min="2" max="2" width="9.25" customWidth="1"/>
-    <col min="3" max="3" width="2.58203125" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" customWidth="1"/>
     <col min="8" max="8" width="2.25" customWidth="1"/>
     <col min="9" max="9" width="2.83203125" customWidth="1"/>
     <col min="10" max="10" width="4.33203125" customWidth="1"/>
@@ -1836,7 +1860,7 @@
         <v>69</v>
       </c>
       <c r="B1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>51</v>
@@ -1948,7 +1972,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
         <v>74</v>
@@ -1976,13 +2000,13 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
         <v>74</v>
       </c>
       <c r="L8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S8">
         <v>1</v>
@@ -1990,13 +2014,13 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D9" t="s">
         <v>74</v>
       </c>
       <c r="L9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S9">
         <v>1</v>
@@ -2004,13 +2028,13 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D10" t="s">
         <v>74</v>
       </c>
       <c r="L10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S10">
         <v>1</v>
@@ -2018,13 +2042,13 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" t="s">
         <v>163</v>
-      </c>
-      <c r="D11" t="s">
-        <v>74</v>
-      </c>
-      <c r="L11" t="s">
-        <v>164</v>
       </c>
       <c r="S11">
         <v>1</v>
@@ -2032,13 +2056,13 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" t="s">
         <v>170</v>
-      </c>
-      <c r="D12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L12" t="s">
-        <v>171</v>
       </c>
       <c r="S12">
         <v>1</v>
@@ -2046,13 +2070,13 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D13" t="s">
         <v>74</v>
       </c>
       <c r="L13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S13">
         <v>1</v>
@@ -2060,16 +2084,16 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" t="s">
         <v>176</v>
       </c>
-      <c r="D14" t="s">
-        <v>74</v>
-      </c>
-      <c r="K14" t="s">
-        <v>177</v>
-      </c>
       <c r="L14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S14">
         <v>1</v>
@@ -2077,13 +2101,13 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s">
         <v>182</v>
-      </c>
-      <c r="D15" t="s">
-        <v>74</v>
-      </c>
-      <c r="K15" t="s">
-        <v>183</v>
       </c>
       <c r="S15">
         <v>1</v>
@@ -2091,13 +2115,13 @@
     </row>
     <row r="16" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D16" t="s">
         <v>74</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S16" s="14">
         <v>1</v>
@@ -2105,13 +2129,13 @@
     </row>
     <row r="17" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D17" t="s">
         <v>74</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S17" s="14">
         <v>1</v>
@@ -2119,22 +2143,22 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
         <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L18" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M18" s="12"/>
       <c r="N18" s="13"/>
@@ -2144,13 +2168,13 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D19" t="s">
         <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -2173,7 +2197,7 @@
         <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -2190,13 +2214,13 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D21" t="s">
         <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F21" t="s">
         <v>11</v>
@@ -2208,7 +2232,7 @@
         <v>18</v>
       </c>
       <c r="L21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S21">
         <v>1</v>
@@ -2216,13 +2240,13 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
         <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
@@ -2239,13 +2263,13 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D23" t="s">
         <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L23" t="s">
         <v>20</v>
@@ -2256,16 +2280,16 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D24" t="s">
         <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S24">
         <v>1</v>
@@ -2273,13 +2297,13 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D25" t="s">
         <v>74</v>
       </c>
       <c r="E25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
@@ -2325,7 +2349,7 @@
         <v>12</v>
       </c>
       <c r="K27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L27" t="s">
         <v>25</v>
@@ -2333,7 +2357,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D28" t="s">
         <v>74</v>
@@ -2350,7 +2374,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D29" t="s">
         <v>74</v>
@@ -2370,7 +2394,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D30" t="s">
         <v>74</v>
@@ -2379,7 +2403,7 @@
         <v>10</v>
       </c>
       <c r="L30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S30">
         <v>1</v>
@@ -2387,7 +2411,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D31" t="s">
         <v>74</v>
@@ -2402,7 +2426,7 @@
         <v>12</v>
       </c>
       <c r="L31" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="S31">
         <v>1</v>
@@ -2430,13 +2454,13 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D33" t="s">
         <v>74</v>
       </c>
       <c r="P33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
@@ -2447,7 +2471,7 @@
         <v>74</v>
       </c>
       <c r="P34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S34">
         <v>1</v>
@@ -2455,35 +2479,53 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D35" t="s">
         <v>74</v>
       </c>
       <c r="P35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>204</v>
+      </c>
+      <c r="B36" t="s">
+        <v>205</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
       </c>
-      <c r="P36" t="s">
-        <v>78</v>
-      </c>
-      <c r="S36">
-        <v>1</v>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L36" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>199</v>
+      </c>
+      <c r="B37" t="s">
+        <v>203</v>
       </c>
       <c r="D37" t="s">
         <v>74</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="L37" t="s">
+        <v>203</v>
       </c>
       <c r="P37" t="s">
         <v>37</v>
@@ -2494,7 +2536,7 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D38" t="s">
         <v>74</v>
@@ -2505,30 +2547,51 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" t="s">
+        <v>202</v>
+      </c>
+      <c r="D39" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="L39" t="s">
+        <v>201</v>
+      </c>
+      <c r="O39" t="s">
         <v>198</v>
       </c>
-      <c r="B39" t="s">
-        <v>199</v>
-      </c>
-      <c r="D39" t="s">
-        <v>74</v>
-      </c>
-      <c r="L39" t="s">
+      <c r="P39" t="s">
         <v>200</v>
-      </c>
-      <c r="S39">
-        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>195</v>
+      </c>
+      <c r="B40" t="s">
+        <v>196</v>
       </c>
       <c r="D40" t="s">
         <v>74</v>
       </c>
-      <c r="P40" t="s">
-        <v>38</v>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="L40" t="s">
+        <v>197</v>
+      </c>
+      <c r="O40" t="s">
+        <v>198</v>
       </c>
       <c r="S40">
         <v>1</v>
@@ -2536,19 +2599,13 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
         <v>74</v>
       </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>11</v>
-      </c>
-      <c r="L41" t="s">
-        <v>190</v>
+      <c r="P41" t="s">
+        <v>38</v>
       </c>
       <c r="S41">
         <v>1</v>
@@ -2592,13 +2649,13 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
         <v>74</v>
       </c>
       <c r="L45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S45">
         <v>1</v>
@@ -2606,7 +2663,7 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D46" t="s">
         <v>74</v>
@@ -2618,10 +2675,10 @@
         <v>48</v>
       </c>
       <c r="G46" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L46" t="s">
         <v>168</v>
-      </c>
-      <c r="L46" t="s">
-        <v>169</v>
       </c>
       <c r="O46" s="4" t="s">
         <v>47</v>
@@ -2632,7 +2689,7 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D47" t="s">
         <v>74</v>
@@ -2644,18 +2701,18 @@
         <v>48</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O47" t="s">
         <v>76</v>
       </c>
       <c r="P47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D48" t="s">
         <v>74</v>
@@ -2670,15 +2727,15 @@
         <v>64</v>
       </c>
       <c r="L48" t="s">
+        <v>78</v>
+      </c>
+      <c r="O48" t="s">
         <v>79</v>
-      </c>
-      <c r="O48" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D49" t="s">
         <v>74</v>
@@ -2690,21 +2747,21 @@
         <v>32</v>
       </c>
       <c r="G49" t="s">
+        <v>82</v>
+      </c>
+      <c r="L49" t="s">
+        <v>81</v>
+      </c>
+      <c r="O49" t="s">
+        <v>79</v>
+      </c>
+      <c r="P49" t="s">
         <v>83</v>
-      </c>
-      <c r="L49" t="s">
-        <v>82</v>
-      </c>
-      <c r="O49" t="s">
-        <v>80</v>
-      </c>
-      <c r="P49" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>58</v>
@@ -2716,7 +2773,7 @@
         <v>32</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
@@ -2725,12 +2782,12 @@
         <v>59</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M50" s="9"/>
       <c r="N50" s="10"/>
       <c r="O50" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S50">
         <v>1</v>
@@ -2738,7 +2795,7 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D51" t="s">
         <v>58</v>
@@ -2750,13 +2807,13 @@
         <v>32</v>
       </c>
       <c r="G51" t="s">
+        <v>143</v>
+      </c>
+      <c r="L51" t="s">
         <v>144</v>
       </c>
-      <c r="L51" t="s">
-        <v>145</v>
-      </c>
       <c r="O51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S51">
         <v>1</v>
@@ -2816,7 +2873,7 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D54" t="s">
         <v>74</v>
@@ -2834,7 +2891,7 @@
         <v>34</v>
       </c>
       <c r="L54" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O54" t="s">
         <v>66</v>
@@ -2845,7 +2902,7 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D55" t="s">
         <v>74</v>
@@ -2863,7 +2920,7 @@
         <v>34</v>
       </c>
       <c r="L55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O55" t="s">
         <v>66</v>
@@ -2871,7 +2928,7 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D56" t="s">
         <v>74</v>
@@ -2886,13 +2943,13 @@
         <v>33</v>
       </c>
       <c r="K56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S56">
         <v>1</v>
@@ -2900,7 +2957,7 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
         <v>74</v>
@@ -2915,13 +2972,13 @@
         <v>33</v>
       </c>
       <c r="K57" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S57">
         <v>1</v>
@@ -2955,7 +3012,7 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D59" t="s">
         <v>74</v>
@@ -2967,13 +3024,13 @@
         <v>48</v>
       </c>
       <c r="G59" t="s">
+        <v>132</v>
+      </c>
+      <c r="L59" t="s">
+        <v>130</v>
+      </c>
+      <c r="O59" t="s">
         <v>133</v>
-      </c>
-      <c r="L59" t="s">
-        <v>131</v>
-      </c>
-      <c r="O59" t="s">
-        <v>134</v>
       </c>
       <c r="P59">
         <v>13297968006</v>
@@ -2984,7 +3041,7 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D60" t="s">
         <v>74</v>
@@ -2996,13 +3053,13 @@
         <v>48</v>
       </c>
       <c r="G60" t="s">
+        <v>132</v>
+      </c>
+      <c r="L60" t="s">
+        <v>131</v>
+      </c>
+      <c r="O60" t="s">
         <v>133</v>
-      </c>
-      <c r="L60" t="s">
-        <v>132</v>
-      </c>
-      <c r="O60" t="s">
-        <v>134</v>
       </c>
       <c r="P60">
         <v>13638658298</v>
@@ -3036,7 +3093,7 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D62" t="s">
         <v>74</v>
@@ -3045,19 +3102,19 @@
         <v>10</v>
       </c>
       <c r="F62" t="s">
+        <v>138</v>
+      </c>
+      <c r="G62" t="s">
         <v>139</v>
       </c>
-      <c r="G62" t="s">
+      <c r="L62" t="s">
         <v>140</v>
-      </c>
-      <c r="L62" t="s">
-        <v>141</v>
       </c>
       <c r="O62" t="s">
         <v>47</v>
       </c>
       <c r="P62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S62">
         <v>1</v>
@@ -3097,7 +3154,7 @@
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D64" t="s">
         <v>58</v>
@@ -3133,162 +3190,162 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TZY_YX\工作\2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F3FD56-3383-49C5-A1AF-88D0466D6B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F1FB2C-92D5-4BFC-90C2-5EEC96DB94DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="25815" windowHeight="15495" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Moze Dict" sheetId="1" r:id="rId1"/>
     <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$S$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$S$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="213">
   <si>
     <t>记录类型</t>
   </si>
@@ -722,10 +722,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>华农竹苑</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>食</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -738,10 +734,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>湖工东苑</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>东苑</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -759,6 +751,38 @@
   </si>
   <si>
     <t>民大中心食堂</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>东三一楼</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>武汉职业技术学院</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>武职食堂</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>武汉职业技术大学</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>未来城园区食堂</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖工西区食堂</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖工东苑食堂</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>华农竹苑食堂</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1837,25 +1861,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:S64"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S65"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="46.08203125" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" customWidth="1"/>
+    <col min="1" max="1" width="46.125" customWidth="1"/>
+    <col min="2" max="2" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="7.125" customWidth="1"/>
     <col min="8" max="8" width="2.25" customWidth="1"/>
-    <col min="9" max="9" width="2.83203125" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.08203125" customWidth="1"/>
-    <col min="13" max="13" width="11.83203125" customWidth="1"/>
-    <col min="14" max="14" width="3.08203125" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" customWidth="1"/>
-    <col min="16" max="16" width="16.08203125" customWidth="1"/>
+    <col min="9" max="9" width="2.875" customWidth="1"/>
+    <col min="10" max="10" width="4.375" customWidth="1"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="13" max="13" width="11.875" customWidth="1"/>
+    <col min="14" max="14" width="3.125" customWidth="1"/>
+    <col min="15" max="15" width="12.375" customWidth="1"/>
+    <col min="16" max="16" width="16.125" customWidth="1"/>
     <col min="17" max="17" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>69</v>
       </c>
@@ -1914,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1928,7 +1952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1942,7 +1966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1956,7 +1980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1970,7 +1994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -1984,7 +2008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -1998,7 +2022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -2012,7 +2036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>177</v>
       </c>
@@ -2026,7 +2050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>152</v>
       </c>
@@ -2040,7 +2064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -2054,7 +2078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>169</v>
       </c>
@@ -2068,7 +2092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>172</v>
       </c>
@@ -2082,7 +2106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>175</v>
       </c>
@@ -2099,7 +2123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>181</v>
       </c>
@@ -2113,7 +2137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>179</v>
       </c>
@@ -2127,7 +2151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>185</v>
       </c>
@@ -2141,7 +2165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>188</v>
       </c>
@@ -2166,7 +2190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>193</v>
       </c>
@@ -2189,7 +2213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2212,7 +2236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>155</v>
       </c>
@@ -2238,7 +2262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>154</v>
       </c>
@@ -2261,7 +2285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>157</v>
       </c>
@@ -2278,7 +2302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -2295,7 +2319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>158</v>
       </c>
@@ -2315,7 +2339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2332,7 +2356,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2355,7 +2379,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>148</v>
       </c>
@@ -2372,7 +2396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>161</v>
       </c>
@@ -2392,7 +2416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>160</v>
       </c>
@@ -2409,7 +2433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>190</v>
       </c>
@@ -2432,7 +2456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -2452,48 +2476,78 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>187</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s">
         <v>74</v>
       </c>
       <c r="P33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>198</v>
+      </c>
+      <c r="B34" t="s">
+        <v>201</v>
       </c>
       <c r="D34" t="s">
         <v>74</v>
       </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="L34" t="s">
+        <v>201</v>
+      </c>
+      <c r="O34" t="s">
+        <v>76</v>
+      </c>
       <c r="P34" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="S34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>206</v>
+      </c>
+      <c r="B35" t="s">
+        <v>205</v>
       </c>
       <c r="D35" t="s">
         <v>74</v>
       </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="L35" t="s">
+        <v>207</v>
+      </c>
+      <c r="O35" t="s">
+        <v>76</v>
+      </c>
       <c r="P35" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B36" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -2505,15 +2559,18 @@
         <v>11</v>
       </c>
       <c r="L36" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+      <c r="O36" t="s">
+        <v>76</v>
+      </c>
+      <c r="P36" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>199</v>
-      </c>
-      <c r="B37" t="s">
-        <v>203</v>
+        <v>65</v>
       </c>
       <c r="D37" t="s">
         <v>74</v>
@@ -2525,32 +2582,50 @@
         <v>11</v>
       </c>
       <c r="L37" t="s">
-        <v>203</v>
+        <v>210</v>
+      </c>
+      <c r="O37" t="s">
+        <v>76</v>
       </c>
       <c r="P37" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="S37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>183</v>
       </c>
+      <c r="B38" t="s">
+        <v>209</v>
+      </c>
       <c r="D38" t="s">
         <v>74</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="L38" t="s">
+        <v>209</v>
+      </c>
+      <c r="O38" t="s">
+        <v>76</v>
       </c>
       <c r="P38" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D39" t="s">
         <v>74</v>
@@ -2562,21 +2637,21 @@
         <v>11</v>
       </c>
       <c r="L39" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="O39" t="s">
-        <v>198</v>
-      </c>
-      <c r="P39" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+      <c r="S39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B40" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D40" t="s">
         <v>74</v>
@@ -2588,16 +2663,13 @@
         <v>11</v>
       </c>
       <c r="L40" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="O40" t="s">
-        <v>198</v>
-      </c>
-      <c r="S40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>38</v>
       </c>
@@ -2611,85 +2683,70 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>187</v>
+      </c>
+      <c r="D42" t="s">
+        <v>74</v>
+      </c>
+      <c r="P42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>39</v>
       </c>
-      <c r="D42" t="s">
-        <v>74</v>
-      </c>
-      <c r="L42" t="s">
+      <c r="D43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L43" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>41</v>
       </c>
-      <c r="D43" t="s">
-        <v>74</v>
-      </c>
-      <c r="L43" t="s">
+      <c r="D44" t="s">
+        <v>74</v>
+      </c>
+      <c r="L44" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>43</v>
       </c>
-      <c r="D44" t="s">
-        <v>74</v>
-      </c>
-      <c r="L44" t="s">
+      <c r="D45" t="s">
+        <v>74</v>
+      </c>
+      <c r="L45" t="s">
         <v>43</v>
       </c>
-      <c r="S44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="S45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>85</v>
       </c>
-      <c r="D45" t="s">
-        <v>74</v>
-      </c>
-      <c r="L45" t="s">
+      <c r="D46" t="s">
+        <v>74</v>
+      </c>
+      <c r="L46" t="s">
         <v>85</v>
       </c>
-      <c r="S45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="S46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>166</v>
-      </c>
-      <c r="D46" t="s">
-        <v>74</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="L46" t="s">
-        <v>168</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="S46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>86</v>
       </c>
       <c r="D47" t="s">
         <v>74</v>
@@ -2701,18 +2758,21 @@
         <v>48</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="O47" t="s">
-        <v>76</v>
-      </c>
-      <c r="P47" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+      <c r="L47" t="s">
+        <v>168</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D48" t="s">
         <v>74</v>
@@ -2720,22 +2780,22 @@
       <c r="E48" t="s">
         <v>10</v>
       </c>
-      <c r="F48" t="s">
-        <v>32</v>
-      </c>
-      <c r="G48" t="s">
-        <v>64</v>
-      </c>
-      <c r="L48" t="s">
+      <c r="F48" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="O48" t="s">
+        <v>76</v>
+      </c>
+      <c r="P48" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>78</v>
-      </c>
-      <c r="O48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>80</v>
       </c>
       <c r="D49" t="s">
         <v>74</v>
@@ -2747,84 +2807,81 @@
         <v>32</v>
       </c>
       <c r="G49" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="L49" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O49" t="s">
         <v>79</v>
       </c>
-      <c r="P49" t="s">
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>80</v>
+      </c>
+      <c r="D50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" t="s">
+        <v>82</v>
+      </c>
+      <c r="L50" t="s">
+        <v>81</v>
+      </c>
+      <c r="O50" t="s">
+        <v>79</v>
+      </c>
+      <c r="P50" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
         <v>146</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D51" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F51" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G51" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8" t="s">
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="L50" s="8" t="s">
+      <c r="L51" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="M50" s="9"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="8" t="s">
+      <c r="M51" s="9"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="S50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="S51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>142</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>58</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" t="s">
-        <v>32</v>
-      </c>
-      <c r="G51" t="s">
-        <v>143</v>
-      </c>
-      <c r="L51" t="s">
-        <v>144</v>
-      </c>
-      <c r="O51" t="s">
-        <v>133</v>
-      </c>
-      <c r="S51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" t="s">
-        <v>74</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
@@ -2833,21 +2890,21 @@
         <v>32</v>
       </c>
       <c r="G52" t="s">
-        <v>33</v>
-      </c>
-      <c r="K52" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="L52" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
       <c r="O52" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="S52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D53" t="s">
         <v>74</v>
@@ -2865,15 +2922,15 @@
         <v>34</v>
       </c>
       <c r="L53" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O53" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="D54" t="s">
         <v>74</v>
@@ -2891,18 +2948,15 @@
         <v>34</v>
       </c>
       <c r="L54" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="O54" t="s">
         <v>66</v>
       </c>
-      <c r="S54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D55" t="s">
         <v>74</v>
@@ -2920,15 +2974,18 @@
         <v>34</v>
       </c>
       <c r="L55" t="s">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="O55" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="D56" t="s">
         <v>74</v>
@@ -2943,21 +3000,18 @@
         <v>33</v>
       </c>
       <c r="K56" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="L56" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="O56" t="s">
-        <v>133</v>
-      </c>
-      <c r="S56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D57" t="s">
         <v>74</v>
@@ -2975,7 +3029,7 @@
         <v>147</v>
       </c>
       <c r="L57" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O57" t="s">
         <v>133</v>
@@ -2984,9 +3038,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>44</v>
+        <v>173</v>
       </c>
       <c r="D58" t="s">
         <v>74</v>
@@ -2995,24 +3049,27 @@
         <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G58" t="s">
-        <v>61</v>
+        <v>33</v>
+      </c>
+      <c r="K58" t="s">
+        <v>147</v>
       </c>
       <c r="L58" t="s">
+        <v>164</v>
+      </c>
+      <c r="O58" t="s">
+        <v>133</v>
+      </c>
+      <c r="S58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>44</v>
-      </c>
-      <c r="O58" t="s">
-        <v>45</v>
-      </c>
-      <c r="P58" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>130</v>
       </c>
       <c r="D59" t="s">
         <v>74</v>
@@ -3024,24 +3081,21 @@
         <v>48</v>
       </c>
       <c r="G59" t="s">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="L59" t="s">
+        <v>44</v>
+      </c>
+      <c r="O59" t="s">
+        <v>45</v>
+      </c>
+      <c r="P59" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>130</v>
-      </c>
-      <c r="O59" t="s">
-        <v>133</v>
-      </c>
-      <c r="P59">
-        <v>13297968006</v>
-      </c>
-      <c r="S59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>131</v>
       </c>
       <c r="D60" t="s">
         <v>74</v>
@@ -3056,21 +3110,21 @@
         <v>132</v>
       </c>
       <c r="L60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O60" t="s">
         <v>133</v>
       </c>
       <c r="P60">
-        <v>13638658298</v>
+        <v>13297968006</v>
       </c>
       <c r="S60">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="D61" t="s">
         <v>74</v>
@@ -3082,18 +3136,24 @@
         <v>48</v>
       </c>
       <c r="G61" t="s">
-        <v>49</v>
+        <v>132</v>
+      </c>
+      <c r="L61" t="s">
+        <v>131</v>
       </c>
       <c r="O61" t="s">
-        <v>47</v>
+        <v>133</v>
+      </c>
+      <c r="P61">
+        <v>13638658298</v>
       </c>
       <c r="S61">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="D62" t="s">
         <v>74</v>
@@ -3102,59 +3162,50 @@
         <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="G62" t="s">
-        <v>139</v>
-      </c>
-      <c r="L62" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="O62" t="s">
         <v>47</v>
       </c>
-      <c r="P62" t="s">
-        <v>134</v>
-      </c>
       <c r="S62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="G63" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="L63" t="s">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="O63" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>59</v>
-      </c>
-      <c r="R63" t="s">
-        <v>59</v>
+        <v>47</v>
+      </c>
+      <c r="P63" t="s">
+        <v>134</v>
       </c>
       <c r="S63">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D64" t="s">
         <v>58</v>
@@ -3168,12 +3219,44 @@
       <c r="G64" t="s">
         <v>62</v>
       </c>
+      <c r="L64" t="s">
+        <v>63</v>
+      </c>
       <c r="O64" t="s">
         <v>36</v>
       </c>
+      <c r="Q64" t="s">
+        <v>59</v>
+      </c>
+      <c r="R64" t="s">
+        <v>59</v>
+      </c>
+      <c r="S64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>84</v>
+      </c>
+      <c r="D65" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>60</v>
+      </c>
+      <c r="G65" t="s">
+        <v>62</v>
+      </c>
+      <c r="O65" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S65" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
+  <autoFilter ref="A1:S66" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3183,12 +3266,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A67EEF5-ABF4-4CC5-BAC6-126980D50F95}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.08203125" customWidth="1"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>90</v>
       </c>
@@ -3196,7 +3279,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>92</v>
       </c>
@@ -3204,7 +3287,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>94</v>
       </c>
@@ -3212,7 +3295,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>96</v>
       </c>
@@ -3220,7 +3303,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>98</v>
       </c>
@@ -3228,7 +3311,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>100</v>
       </c>
@@ -3236,7 +3319,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>102</v>
       </c>
@@ -3244,7 +3327,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>104</v>
       </c>
@@ -3252,7 +3335,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>106</v>
       </c>
@@ -3260,7 +3343,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>108</v>
       </c>
@@ -3268,7 +3351,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>110</v>
       </c>
@@ -3276,7 +3359,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>112</v>
       </c>
@@ -3284,7 +3367,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>114</v>
       </c>
@@ -3292,7 +3375,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>128</v>
       </c>
@@ -3300,7 +3383,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>117</v>
       </c>
@@ -3308,7 +3391,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>118</v>
       </c>
@@ -3316,7 +3399,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>120</v>
       </c>
@@ -3324,7 +3407,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>122</v>
       </c>
@@ -3332,7 +3415,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>124</v>
       </c>
@@ -3340,7 +3423,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>126</v>
       </c>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TZY_YX\工作\2025\Moze4.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F1FB2C-92D5-4BFC-90C2-5EEC96DB94DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD13DDD-72AE-488E-9F6B-8105D6EA5FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="25815" windowHeight="15495" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Moze Dict" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="214">
   <si>
     <t>记录类型</t>
   </si>
@@ -783,6 +783,10 @@
   </si>
   <si>
     <t>华农竹苑食堂</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#外勤 </t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1862,24 +1866,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
   <dimension ref="A1:S65"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.125" customWidth="1"/>
-    <col min="2" max="2" width="12.625" customWidth="1"/>
-    <col min="3" max="3" width="7.125" customWidth="1"/>
+    <col min="1" max="1" width="46.08203125" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.08203125" customWidth="1"/>
     <col min="8" max="8" width="2.25" customWidth="1"/>
-    <col min="9" max="9" width="2.875" customWidth="1"/>
-    <col min="10" max="10" width="4.375" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
-    <col min="12" max="12" width="16.125" customWidth="1"/>
-    <col min="13" max="13" width="11.875" customWidth="1"/>
-    <col min="14" max="14" width="3.125" customWidth="1"/>
-    <col min="15" max="15" width="12.375" customWidth="1"/>
-    <col min="16" max="16" width="16.125" customWidth="1"/>
+    <col min="9" max="9" width="2.83203125" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.08203125" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" customWidth="1"/>
+    <col min="14" max="14" width="3.08203125" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" customWidth="1"/>
+    <col min="16" max="16" width="16.08203125" customWidth="1"/>
     <col min="17" max="17" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>69</v>
       </c>
@@ -1938,7 +1942,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1952,7 +1956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1966,7 +1970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1980,7 +1984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1994,7 +1998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -2008,7 +2012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -2022,7 +2026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -2036,7 +2040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>177</v>
       </c>
@@ -2050,7 +2054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>152</v>
       </c>
@@ -2064,7 +2068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -2078,7 +2082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>169</v>
       </c>
@@ -2092,7 +2096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>172</v>
       </c>
@@ -2106,7 +2110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>175</v>
       </c>
@@ -2123,7 +2127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>181</v>
       </c>
@@ -2137,7 +2141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>179</v>
       </c>
@@ -2151,7 +2155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>185</v>
       </c>
@@ -2165,7 +2169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>188</v>
       </c>
@@ -2190,7 +2194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>193</v>
       </c>
@@ -2213,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2236,7 +2240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>155</v>
       </c>
@@ -2262,7 +2266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>154</v>
       </c>
@@ -2285,7 +2289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>157</v>
       </c>
@@ -2302,7 +2306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -2319,7 +2323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>158</v>
       </c>
@@ -2339,7 +2343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2356,7 +2360,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2379,7 +2383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>148</v>
       </c>
@@ -2396,7 +2400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>161</v>
       </c>
@@ -2416,7 +2420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>160</v>
       </c>
@@ -2433,7 +2437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>190</v>
       </c>
@@ -2456,7 +2460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -2476,7 +2480,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -2487,7 +2491,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>198</v>
       </c>
@@ -2512,11 +2516,14 @@
       <c r="P34" t="s">
         <v>37</v>
       </c>
+      <c r="Q34" t="s">
+        <v>213</v>
+      </c>
       <c r="S34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>206</v>
       </c>
@@ -2541,8 +2548,11 @@
       <c r="P35" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="Q35" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>199</v>
       </c>
@@ -2567,8 +2577,11 @@
       <c r="P36" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="Q36" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -2590,11 +2603,14 @@
       <c r="P37" t="s">
         <v>77</v>
       </c>
+      <c r="Q37" t="s">
+        <v>213</v>
+      </c>
       <c r="S37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>183</v>
       </c>
@@ -2619,8 +2635,11 @@
       <c r="P38" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="Q38" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>195</v>
       </c>
@@ -2646,7 +2665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>202</v>
       </c>
@@ -2669,7 +2688,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>38</v>
       </c>
@@ -2683,7 +2702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>187</v>
       </c>
@@ -2694,7 +2713,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -2705,7 +2724,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>41</v>
       </c>
@@ -2716,7 +2735,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -2730,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -2744,7 +2763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>166</v>
       </c>
@@ -2770,7 +2789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>86</v>
       </c>
@@ -2793,7 +2812,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>78</v>
       </c>
@@ -2816,7 +2835,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>80</v>
       </c>
@@ -2842,7 +2861,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -2876,7 +2895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>142</v>
       </c>
@@ -2902,7 +2921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>67</v>
       </c>
@@ -2928,7 +2947,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>35</v>
       </c>
@@ -2954,7 +2973,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>192</v>
       </c>
@@ -2983,7 +3002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>136</v>
       </c>
@@ -3009,7 +3028,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>174</v>
       </c>
@@ -3038,7 +3057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>173</v>
       </c>
@@ -3067,7 +3086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>44</v>
       </c>
@@ -3093,7 +3112,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>130</v>
       </c>
@@ -3122,7 +3141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>131</v>
       </c>
@@ -3151,7 +3170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -3174,7 +3193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>135</v>
       </c>
@@ -3203,7 +3222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -3235,7 +3254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>84</v>
       </c>
@@ -3266,12 +3285,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A67EEF5-ABF4-4CC5-BAC6-126980D50F95}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="1" max="1" width="26.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>90</v>
       </c>
@@ -3279,7 +3298,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>92</v>
       </c>
@@ -3287,7 +3306,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>94</v>
       </c>
@@ -3295,7 +3314,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>96</v>
       </c>
@@ -3303,7 +3322,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>98</v>
       </c>
@@ -3311,7 +3330,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>100</v>
       </c>
@@ -3319,7 +3338,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>102</v>
       </c>
@@ -3327,7 +3346,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>104</v>
       </c>
@@ -3335,7 +3354,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>106</v>
       </c>
@@ -3343,7 +3362,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>108</v>
       </c>
@@ -3351,7 +3370,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>110</v>
       </c>
@@ -3359,7 +3378,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>112</v>
       </c>
@@ -3367,7 +3386,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>114</v>
       </c>
@@ -3375,7 +3394,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>128</v>
       </c>
@@ -3383,7 +3402,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>117</v>
       </c>
@@ -3391,7 +3410,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>118</v>
       </c>
@@ -3399,7 +3418,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>120</v>
       </c>
@@ -3407,7 +3426,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>122</v>
       </c>
@@ -3415,7 +3434,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>124</v>
       </c>
@@ -3423,7 +3442,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>126</v>
       </c>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD13DDD-72AE-488E-9F6B-8105D6EA5FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1381C87-E7CD-468B-BA87-E6A2C0B660CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -619,14 +619,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>拉州拉面</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>拉州|丝路</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>中国石油|中石油</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -787,6 +779,14 @@
   </si>
   <si>
     <t xml:space="preserve">#外勤 </t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>兰州|丝路</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>兰州拉面</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1888,7 +1888,7 @@
         <v>69</v>
       </c>
       <c r="B1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>51</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
         <v>74</v>
       </c>
       <c r="L9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S9">
         <v>1</v>
@@ -2098,13 +2098,13 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="D13" t="s">
         <v>74</v>
       </c>
       <c r="L13" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="S13">
         <v>1</v>
@@ -2112,16 +2112,16 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D14" t="s">
         <v>74</v>
       </c>
       <c r="K14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S14">
         <v>1</v>
@@ -2129,13 +2129,13 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D15" t="s">
         <v>74</v>
       </c>
       <c r="K15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S15">
         <v>1</v>
@@ -2143,13 +2143,13 @@
     </row>
     <row r="16" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D16" t="s">
         <v>74</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="S16" s="14">
         <v>1</v>
@@ -2157,13 +2157,13 @@
     </row>
     <row r="17" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D17" t="s">
         <v>74</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="S17" s="14">
         <v>1</v>
@@ -2171,22 +2171,22 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D18" t="s">
         <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M18" s="12"/>
       <c r="N18" s="13"/>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
         <v>74</v>
@@ -2439,7 +2439,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D31" t="s">
         <v>74</v>
@@ -2454,7 +2454,7 @@
         <v>12</v>
       </c>
       <c r="L31" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="S31">
         <v>1</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D34" t="s">
         <v>74</v>
@@ -2508,7 +2508,7 @@
         <v>11</v>
       </c>
       <c r="L34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="O34" t="s">
         <v>76</v>
@@ -2517,7 +2517,7 @@
         <v>37</v>
       </c>
       <c r="Q34" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="S34">
         <v>1</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B35" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D35" t="s">
         <v>74</v>
@@ -2540,24 +2540,24 @@
         <v>11</v>
       </c>
       <c r="L35" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O35" t="s">
         <v>76</v>
       </c>
       <c r="P35" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q35" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -2569,16 +2569,16 @@
         <v>11</v>
       </c>
       <c r="L36" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O36" t="s">
         <v>76</v>
       </c>
       <c r="P36" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Q36" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
@@ -2595,7 +2595,7 @@
         <v>11</v>
       </c>
       <c r="L37" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O37" t="s">
         <v>76</v>
@@ -2604,7 +2604,7 @@
         <v>77</v>
       </c>
       <c r="Q37" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="S37">
         <v>1</v>
@@ -2612,10 +2612,10 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B38" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D38" t="s">
         <v>74</v>
@@ -2627,7 +2627,7 @@
         <v>11</v>
       </c>
       <c r="L38" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O38" t="s">
         <v>76</v>
@@ -2636,15 +2636,15 @@
         <v>14</v>
       </c>
       <c r="Q38" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D39" t="s">
         <v>74</v>
@@ -2656,10 +2656,10 @@
         <v>11</v>
       </c>
       <c r="L39" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="S39">
         <v>1</v>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D40" t="s">
         <v>74</v>
@@ -2682,7 +2682,7 @@
         <v>11</v>
       </c>
       <c r="L40" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O40" t="s">
         <v>76</v>
@@ -2704,13 +2704,13 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
         <v>74</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
@@ -2975,7 +2975,7 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D55" t="s">
         <v>74</v>
@@ -2993,7 +2993,7 @@
         <v>34</v>
       </c>
       <c r="L55" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O55" t="s">
         <v>66</v>
@@ -3030,7 +3030,7 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D57" t="s">
         <v>74</v>
@@ -3059,7 +3059,7 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D58" t="s">
         <v>74</v>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1381C87-E7CD-468B-BA87-E6A2C0B660CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE814A8-E534-4BF9-B174-C79C3798B851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="217">
   <si>
     <t>记录类型</t>
   </si>
@@ -787,6 +787,18 @@
   </si>
   <si>
     <t>兰州拉面</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>拼多多</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>返利回馈</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>返利</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1865,7 +1877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB1C259-84E7-4725-A96D-25208E398E8B}">
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.08203125" customWidth="1"/>
@@ -3254,7 +3266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>84</v>
       </c>
@@ -3272,6 +3284,32 @@
       </c>
       <c r="O65" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>214</v>
+      </c>
+      <c r="D66" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" t="s">
+        <v>215</v>
+      </c>
+      <c r="F66" t="s">
+        <v>215</v>
+      </c>
+      <c r="G66" t="s">
+        <v>215</v>
+      </c>
+      <c r="L66" t="s">
+        <v>214</v>
+      </c>
+      <c r="O66" t="s">
+        <v>216</v>
+      </c>
+      <c r="S66">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE814A8-E534-4BF9-B174-C79C3798B851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89453140-72A1-4333-A819-8E37CAD41477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62C99D20-D431-4D03-8833-D8088AE0D5DF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="218">
   <si>
     <t>记录类型</t>
   </si>
@@ -799,6 +799,10 @@
   </si>
   <si>
     <t>返利</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>打开拼多多|现金红包|领更多现金红包</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -3288,7 +3292,7 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D66" t="s">
         <v>58</v>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F5947C-60B4-494A-8085-CF4D6EEA956E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2EA71F-68DA-4FBB-8904-FF09A089EA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="212">
   <si>
     <t>商家(old)</t>
   </si>
@@ -668,6 +668,10 @@
   </si>
   <si>
     <t>食材</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>淘宝闪购</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1167,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S72"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.58203125" style="14" customWidth="1"/>
@@ -2710,27 +2714,28 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="D58" t="s">
         <v>20</v>
       </c>
+      <c r="E58" t="s">
+        <v>30</v>
+      </c>
       <c r="L58" t="s">
-        <v>19</v>
-      </c>
-      <c r="S58">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="O58"/>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D59" t="s">
         <v>20</v>
       </c>
       <c r="L59" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="S59">
         <v>1</v>
@@ -2738,13 +2743,13 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D60" t="s">
         <v>20</v>
       </c>
       <c r="L60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S60">
         <v>1</v>
@@ -2752,13 +2757,13 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D61" t="s">
         <v>20</v>
       </c>
       <c r="L61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S61">
         <v>1</v>
@@ -2766,13 +2771,13 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D62" t="s">
         <v>20</v>
       </c>
       <c r="L62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S62">
         <v>1</v>
@@ -2780,13 +2785,13 @@
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D63" t="s">
         <v>20</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="S63">
         <v>1</v>
@@ -2794,13 +2799,13 @@
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D64" t="s">
         <v>20</v>
       </c>
       <c r="L64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S64">
         <v>1</v>
@@ -2808,13 +2813,13 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D65" t="s">
         <v>20</v>
       </c>
       <c r="L65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S65">
         <v>1</v>
@@ -2822,13 +2827,13 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="S66">
         <v>1</v>
@@ -2836,49 +2841,49 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
       </c>
       <c r="L67" t="s">
-        <v>96</v>
+        <v>33</v>
+      </c>
+      <c r="S67">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
       </c>
       <c r="L68" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
       </c>
       <c r="L69" t="s">
-        <v>99</v>
-      </c>
-      <c r="S69">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D70" t="s">
         <v>20</v>
       </c>
       <c r="L70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S70">
         <v>1</v>
@@ -2886,16 +2891,13 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
       </c>
-      <c r="P71" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>77</v>
+      <c r="L71" t="s">
+        <v>100</v>
       </c>
       <c r="S71">
         <v>1</v>
@@ -2903,15 +2905,32 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>93</v>
+      </c>
+      <c r="D72" t="s">
+        <v>20</v>
+      </c>
+      <c r="P72" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>77</v>
+      </c>
+      <c r="S72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>94</v>
       </c>
-      <c r="D72" t="s">
-        <v>20</v>
-      </c>
-      <c r="P72" t="s">
+      <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="P73" t="s">
         <v>94</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="Q73" t="s">
         <v>77</v>
       </c>
     </row>

--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DC646E-CEC7-446C-AE1E-F4ABA49D53AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90FFC7E-10A7-4983-9B2E-85E4240696A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Moze Dict" sheetId="1" r:id="rId1"/>
-    <sheet name="KeyWords" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moze Dict'!$A$1:$S$74</definedName>
@@ -24,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="180">
   <si>
     <t>商家(old)</t>
   </si>
@@ -95,592 +94,483 @@
     <t>饮食</t>
   </si>
   <si>
+    <t>食</t>
+  </si>
+  <si>
+    <t>湖工东苑水果店</t>
+  </si>
+  <si>
+    <t>湖北工业大学</t>
+  </si>
+  <si>
+    <t>苏婉水果</t>
+  </si>
+  <si>
+    <t>食材</t>
+  </si>
+  <si>
+    <t>豆制品|豆腐|豆香聚</t>
+  </si>
+  <si>
+    <t>豆制品</t>
+  </si>
+  <si>
+    <t>康福豆腐店</t>
+  </si>
+  <si>
+    <t>康福路家禽批发零售</t>
+  </si>
+  <si>
+    <t>禽肉</t>
+  </si>
+  <si>
+    <t>育林</t>
+  </si>
+  <si>
+    <t>王记育林干货店</t>
+  </si>
+  <si>
+    <t>王姐</t>
+  </si>
+  <si>
+    <t>王姐干货店</t>
+  </si>
+  <si>
+    <t>丁静静|山东老面馒头</t>
+  </si>
+  <si>
+    <t>山东老面馒头</t>
+  </si>
+  <si>
+    <t>张正国</t>
+  </si>
+  <si>
+    <t>张正国鱼摊</t>
+  </si>
+  <si>
+    <t>北方馒头</t>
+  </si>
+  <si>
+    <t>常青麦香园</t>
+  </si>
+  <si>
+    <t>沙县</t>
+  </si>
+  <si>
+    <t>沙县小吃</t>
+  </si>
+  <si>
+    <t>兰州|丝路</t>
+  </si>
+  <si>
+    <t>兰州拉面</t>
+  </si>
+  <si>
+    <t>李李</t>
+  </si>
+  <si>
+    <t>川味小饭馆</t>
+  </si>
+  <si>
+    <t>聚雄小吃</t>
+  </si>
+  <si>
+    <t>安陆特色粉面馆</t>
+  </si>
+  <si>
+    <t>斯迪姆</t>
+  </si>
+  <si>
+    <t>斯迪姆美味补给站</t>
+  </si>
+  <si>
+    <t>生烫牛杂</t>
+  </si>
+  <si>
+    <t>生烫牛杂粉</t>
+  </si>
+  <si>
+    <t>永和四喜</t>
+  </si>
+  <si>
+    <t>黄蜀郎</t>
+  </si>
+  <si>
+    <t>黄蜀郎鸡公煲</t>
+  </si>
+  <si>
+    <t>彩凤小吃店</t>
+  </si>
+  <si>
+    <t>安庆馄饨|安庆混沌</t>
+  </si>
+  <si>
+    <t>安庆馄饨</t>
+  </si>
+  <si>
+    <t>春暖花开</t>
+  </si>
+  <si>
+    <t>路边摊</t>
+  </si>
+  <si>
+    <t>广水包粑</t>
+  </si>
+  <si>
+    <t>武汉工程大学</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#外勤 </t>
+  </si>
+  <si>
+    <t>武汉职业技术学院</t>
+  </si>
+  <si>
+    <t>东三一楼</t>
+  </si>
+  <si>
+    <t>武职食堂</t>
+  </si>
+  <si>
+    <t>武汉职业技术大学</t>
+  </si>
+  <si>
+    <t>东苑</t>
+  </si>
+  <si>
+    <t>湖工东苑食堂</t>
+  </si>
+  <si>
+    <t>西苑</t>
+  </si>
+  <si>
+    <t>湖工西苑食堂</t>
+  </si>
+  <si>
+    <t>武汉纯度餐饮管理有限公司</t>
+  </si>
+  <si>
+    <t>湖工西区食堂</t>
+  </si>
+  <si>
+    <t>未来城园区食堂</t>
+  </si>
+  <si>
+    <t>中南民族大学</t>
+  </si>
+  <si>
+    <t>华中农业大学</t>
+  </si>
+  <si>
+    <t>竹一</t>
+  </si>
+  <si>
+    <t>华农竹苑食堂</t>
+  </si>
+  <si>
+    <t>中心食堂</t>
+  </si>
+  <si>
+    <t>民大中心食堂</t>
+  </si>
+  <si>
+    <t>莘子苑食堂</t>
+  </si>
+  <si>
+    <t>武汉理工大学</t>
+  </si>
+  <si>
+    <t>中国邮政</t>
+  </si>
+  <si>
+    <t>居家</t>
+  </si>
+  <si>
+    <t>快递邮政</t>
+  </si>
+  <si>
+    <t>邮政</t>
+  </si>
+  <si>
+    <t>日用&amp;家用</t>
+  </si>
+  <si>
+    <t>卢亮</t>
+  </si>
+  <si>
+    <t>液化气费</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4KG </t>
+  </si>
+  <si>
+    <t>铁路12306</t>
+  </si>
+  <si>
+    <t>交通</t>
+  </si>
+  <si>
+    <t>火车</t>
+  </si>
+  <si>
+    <t>通信&amp;交通</t>
+  </si>
+  <si>
+    <t>湖北公路客运集团宏基客运站</t>
+  </si>
+  <si>
+    <t>汽车</t>
+  </si>
+  <si>
+    <t>宏基客运站</t>
+  </si>
+  <si>
+    <t>大巴 宏基-李店</t>
+  </si>
+  <si>
+    <t>滴滴出行</t>
+  </si>
+  <si>
+    <t>出租车</t>
+  </si>
+  <si>
+    <t>滴滴</t>
+  </si>
+  <si>
+    <t>高德顺风车</t>
+  </si>
+  <si>
+    <t>高德打车</t>
+  </si>
+  <si>
+    <t>商家4201007064</t>
+  </si>
+  <si>
+    <t>加油充电</t>
+  </si>
+  <si>
+    <t>充电</t>
+  </si>
+  <si>
+    <t>叮叮充电</t>
+  </si>
+  <si>
+    <t>兼职</t>
+  </si>
+  <si>
+    <t>自助服务平台</t>
+  </si>
+  <si>
+    <t>自助服务</t>
+  </si>
+  <si>
+    <t>柏来科技</t>
+  </si>
+  <si>
+    <t>深圳智链物联科技有限公司</t>
+  </si>
+  <si>
+    <t>猛犸</t>
+  </si>
+  <si>
+    <t>中石化|中国石化</t>
+  </si>
+  <si>
+    <t>加油</t>
+  </si>
+  <si>
+    <t>中国石华</t>
+  </si>
+  <si>
+    <t>中国石油|中石油</t>
+  </si>
+  <si>
+    <t>中国石油</t>
+  </si>
+  <si>
+    <t>国网湖北省电力有限公司</t>
+  </si>
+  <si>
+    <t>电费</t>
+  </si>
+  <si>
+    <t>住</t>
+  </si>
+  <si>
+    <t>海棠苑C4</t>
+  </si>
+  <si>
+    <t>武汉供电公司</t>
+  </si>
+  <si>
+    <t>电费-我家</t>
+  </si>
+  <si>
+    <t>中国联通</t>
+  </si>
+  <si>
+    <t>电话费</t>
+  </si>
+  <si>
+    <t>中国移动</t>
+  </si>
+  <si>
+    <t>快剪</t>
+  </si>
+  <si>
+    <t>理发</t>
+  </si>
+  <si>
+    <t>双辉印务荟十店</t>
+  </si>
+  <si>
+    <t>购物</t>
+  </si>
+  <si>
+    <t>摄影文印</t>
+  </si>
+  <si>
+    <t>武汉市武昌区易站电动车维修服务部</t>
+  </si>
+  <si>
+    <t>个人</t>
+  </si>
+  <si>
+    <t>生意</t>
+  </si>
+  <si>
+    <t>1站租车</t>
+  </si>
+  <si>
+    <t>闪送</t>
+  </si>
+  <si>
+    <t>打开拼多多|现金红包|领更多现金红包</t>
+  </si>
+  <si>
+    <t>返利回馈</t>
+  </si>
+  <si>
+    <t>拼多多</t>
+  </si>
+  <si>
+    <t>返利</t>
+  </si>
+  <si>
+    <t>三镇民生</t>
+  </si>
+  <si>
+    <t>老乡鸡</t>
+  </si>
+  <si>
+    <t>F7023</t>
+  </si>
+  <si>
+    <t>应收款项</t>
+  </si>
+  <si>
+    <t>报账</t>
+  </si>
+  <si>
+    <t>停车费</t>
+  </si>
+  <si>
+    <t>#费用报销</t>
+  </si>
+  <si>
+    <t>天之逸</t>
+  </si>
+  <si>
+    <t>^(.*?)(?:停车收费|停车场|停车费|停车平台)?$</t>
+  </si>
+  <si>
+    <t>\1</t>
+  </si>
+  <si>
+    <t>淘宝闪购</t>
+  </si>
+  <si>
+    <t>超马鲜生</t>
+  </si>
+  <si>
+    <t>好的生鲜</t>
+  </si>
+  <si>
+    <t>好又鲜</t>
+  </si>
+  <si>
+    <t>悦森活</t>
+  </si>
+  <si>
+    <t>宜赞</t>
+  </si>
+  <si>
+    <t>馋不二</t>
+  </si>
+  <si>
+    <t>馋不二零食仓</t>
+  </si>
+  <si>
+    <t>零食顽家</t>
+  </si>
+  <si>
+    <t>零食很忙</t>
+  </si>
+  <si>
+    <t>沃尔玛</t>
+  </si>
+  <si>
+    <t>武汉市东湖新技术开发区泽源副食店</t>
+  </si>
+  <si>
+    <t>便邻便利店</t>
+  </si>
+  <si>
+    <t>中商超市珞喻路店</t>
+  </si>
+  <si>
+    <t>中商超市</t>
+  </si>
+  <si>
+    <t>抖音</t>
+  </si>
+  <si>
+    <t>武汉大学</t>
+  </si>
+  <si>
+    <t>武汉轻工大学</t>
+  </si>
+  <si>
     <t>饮料水果</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>饮料</t>
-  </si>
-  <si>
-    <t>食</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>水果</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔬菜</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜜雪冰城</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>琪莉果园湖工草莓园店</t>
-  </si>
-  <si>
-    <t xml:space="preserve">饮料水果 </t>
-  </si>
-  <si>
-    <t>水果</t>
-  </si>
-  <si>
-    <t>湖工东苑水果店</t>
-  </si>
-  <si>
-    <t>湖北工业大学</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>苏婉水果</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>陈望云</t>
-  </si>
-  <si>
-    <t>食材</t>
-  </si>
-  <si>
-    <t>蔬菜</t>
-  </si>
-  <si>
-    <t>豆制品|豆腐|豆香聚</t>
-  </si>
-  <si>
-    <t>豆制品</t>
-  </si>
-  <si>
-    <t>康福豆腐店</t>
-  </si>
-  <si>
-    <t>康福路家禽批发零售</t>
-  </si>
-  <si>
-    <t>禽肉</t>
-  </si>
-  <si>
-    <t>育林</t>
-  </si>
-  <si>
-    <t>王记育林干货店</t>
-  </si>
-  <si>
-    <t>王姐</t>
-  </si>
-  <si>
-    <t>王姐干货店</t>
-  </si>
-  <si>
-    <t>丁静静|山东老面馒头</t>
-  </si>
-  <si>
-    <t>山东老面馒头</t>
-  </si>
-  <si>
-    <t>张正国</t>
-  </si>
-  <si>
-    <t>张正国鱼摊</t>
-  </si>
-  <si>
-    <t>北方馒头</t>
-  </si>
-  <si>
-    <t>常青麦香园</t>
-  </si>
-  <si>
-    <t>沙县</t>
-  </si>
-  <si>
-    <t>沙县小吃</t>
-  </si>
-  <si>
-    <t>兰州|丝路</t>
-  </si>
-  <si>
-    <t>兰州拉面</t>
-  </si>
-  <si>
-    <t>李李</t>
-  </si>
-  <si>
-    <t>川味小饭馆</t>
-  </si>
-  <si>
-    <t>聚雄小吃</t>
-  </si>
-  <si>
-    <t>安陆特色粉面馆</t>
-  </si>
-  <si>
-    <t>斯迪姆</t>
-  </si>
-  <si>
-    <t>斯迪姆美味补给站</t>
-  </si>
-  <si>
-    <t>生烫牛杂</t>
-  </si>
-  <si>
-    <t>生烫牛杂粉</t>
-  </si>
-  <si>
-    <t>永和四喜</t>
-  </si>
-  <si>
-    <t>黄蜀郎</t>
-  </si>
-  <si>
-    <t>黄蜀郎鸡公煲</t>
-  </si>
-  <si>
-    <t>彩凤小吃店</t>
-  </si>
-  <si>
-    <t>安庆馄饨|安庆混沌</t>
-  </si>
-  <si>
-    <t>安庆馄饨</t>
-  </si>
-  <si>
-    <t>春暖花开</t>
-  </si>
-  <si>
-    <t>路边摊</t>
-  </si>
-  <si>
-    <t>广水包粑</t>
-  </si>
-  <si>
-    <t>武汉工程大学</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#外勤 </t>
-  </si>
-  <si>
-    <t>武汉职业技术学院</t>
-  </si>
-  <si>
-    <t>东三一楼</t>
-  </si>
-  <si>
-    <t>武职食堂</t>
-  </si>
-  <si>
-    <t>武汉职业技术大学</t>
-  </si>
-  <si>
-    <t>东苑</t>
-  </si>
-  <si>
-    <t>湖工东苑食堂</t>
-  </si>
-  <si>
-    <t>西苑</t>
-  </si>
-  <si>
-    <t>湖工西苑食堂</t>
-  </si>
-  <si>
-    <t>武汉纯度餐饮管理有限公司</t>
-  </si>
-  <si>
-    <t>湖工西区食堂</t>
-  </si>
-  <si>
-    <t>未来城园区食堂</t>
-  </si>
-  <si>
-    <t>中南民族大学</t>
-  </si>
-  <si>
-    <t>华中农业大学</t>
-  </si>
-  <si>
-    <t>竹一</t>
-  </si>
-  <si>
-    <t>华农竹苑食堂</t>
-  </si>
-  <si>
-    <t>中心食堂</t>
-  </si>
-  <si>
-    <t>民大中心食堂</t>
-  </si>
-  <si>
-    <t>莘子苑食堂</t>
-  </si>
-  <si>
-    <t>武汉理工大学</t>
-  </si>
-  <si>
-    <t>中国邮政</t>
-  </si>
-  <si>
-    <t>居家</t>
-  </si>
-  <si>
-    <t>快递邮政</t>
-  </si>
-  <si>
-    <t>邮政</t>
-  </si>
-  <si>
-    <t>日用&amp;家用</t>
-  </si>
-  <si>
-    <t>卢亮</t>
-  </si>
-  <si>
-    <t>液化气费</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4KG </t>
-  </si>
-  <si>
-    <t>铁路12306</t>
-  </si>
-  <si>
-    <t>交通</t>
-  </si>
-  <si>
-    <t>火车</t>
-  </si>
-  <si>
-    <t>通信&amp;交通</t>
-  </si>
-  <si>
-    <t>湖北公路客运集团宏基客运站</t>
-  </si>
-  <si>
-    <t>汽车</t>
-  </si>
-  <si>
-    <t>宏基客运站</t>
-  </si>
-  <si>
-    <t>大巴 宏基-李店</t>
-  </si>
-  <si>
-    <t>滴滴出行</t>
-  </si>
-  <si>
-    <t>出租车</t>
-  </si>
-  <si>
-    <t>滴滴</t>
-  </si>
-  <si>
-    <t>高德顺风车</t>
-  </si>
-  <si>
-    <t>高德打车</t>
-  </si>
-  <si>
-    <t>商家4201007064</t>
-  </si>
-  <si>
-    <t>加油充电</t>
-  </si>
-  <si>
-    <t>充电</t>
-  </si>
-  <si>
-    <t>叮叮充电</t>
-  </si>
-  <si>
-    <t>兼职</t>
-  </si>
-  <si>
-    <t>自助服务平台</t>
-  </si>
-  <si>
-    <t>自助服务</t>
-  </si>
-  <si>
-    <t>柏来科技</t>
-  </si>
-  <si>
-    <t>深圳智链物联科技有限公司</t>
-  </si>
-  <si>
-    <t>猛犸</t>
-  </si>
-  <si>
-    <t>中石化|中国石化</t>
-  </si>
-  <si>
-    <t>加油</t>
-  </si>
-  <si>
-    <t>中国石华</t>
-  </si>
-  <si>
-    <t>中国石油|中石油</t>
-  </si>
-  <si>
-    <t>中国石油</t>
-  </si>
-  <si>
-    <t>国网湖北省电力有限公司</t>
-  </si>
-  <si>
-    <t>电费</t>
-  </si>
-  <si>
-    <t>住</t>
-  </si>
-  <si>
-    <t>海棠苑C4</t>
-  </si>
-  <si>
-    <t>武汉供电公司</t>
-  </si>
-  <si>
-    <t>电费-我家</t>
-  </si>
-  <si>
-    <t>中国联通</t>
-  </si>
-  <si>
-    <t>电话费</t>
-  </si>
-  <si>
-    <t>中国移动</t>
-  </si>
-  <si>
-    <t>快剪</t>
-  </si>
-  <si>
-    <t>理发</t>
-  </si>
-  <si>
-    <t>双辉印务荟十店</t>
-  </si>
-  <si>
-    <t>购物</t>
-  </si>
-  <si>
-    <t>摄影文印</t>
-  </si>
-  <si>
-    <t>武汉市武昌区易站电动车维修服务部</t>
-  </si>
-  <si>
-    <t>个人</t>
-  </si>
-  <si>
-    <t>生意</t>
-  </si>
-  <si>
-    <t>1站租车</t>
-  </si>
-  <si>
-    <t>闪送</t>
-  </si>
-  <si>
-    <t>打开拼多多|现金红包|领更多现金红包</t>
-  </si>
-  <si>
-    <t>返利回馈</t>
-  </si>
-  <si>
-    <t>拼多多</t>
-  </si>
-  <si>
-    <t>返利</t>
-  </si>
-  <si>
-    <t>三镇民生</t>
-  </si>
-  <si>
-    <t>老乡鸡</t>
-  </si>
-  <si>
-    <t>F7023</t>
-  </si>
-  <si>
-    <t>应收款项</t>
-  </si>
-  <si>
-    <t>报账</t>
-  </si>
-  <si>
-    <t>停车费</t>
-  </si>
-  <si>
-    <t>#费用报销</t>
-  </si>
-  <si>
-    <t>天之逸</t>
-  </si>
-  <si>
-    <t>^(.*?)(?:停车收费|停车场|停车费|停车平台)?$</t>
-  </si>
-  <si>
-    <t>\1</t>
-  </si>
-  <si>
-    <t>淘宝闪购</t>
-  </si>
-  <si>
-    <t>超马鲜生</t>
-  </si>
-  <si>
-    <t>好的生鲜</t>
-  </si>
-  <si>
-    <t>好又鲜</t>
-  </si>
-  <si>
-    <t>悦森活</t>
-  </si>
-  <si>
-    <t>宜赞</t>
-  </si>
-  <si>
-    <t>馋不二</t>
-  </si>
-  <si>
-    <t>馋不二零食仓</t>
-  </si>
-  <si>
-    <t>零食顽家</t>
-  </si>
-  <si>
-    <t>零食很忙</t>
-  </si>
-  <si>
-    <t>沃尔玛</t>
-  </si>
-  <si>
-    <t>武汉市东湖新技术开发区泽源副食店</t>
-  </si>
-  <si>
-    <t>便邻便利店</t>
-  </si>
-  <si>
-    <t>中商超市珞喻路店</t>
-  </si>
-  <si>
-    <t>中商超市</t>
-  </si>
-  <si>
-    <t>抖音</t>
-  </si>
-  <si>
-    <t>武汉大学</t>
-  </si>
-  <si>
-    <t>武汉轻工大学</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Words</t>
-  </si>
-  <si>
-    <t>FRUIT</t>
-  </si>
-  <si>
-    <t>水果, 果园, 果蔬, 百果园, 鲜果, 果业, 苹果, 香蕉, 红枣, 大枣, 桃子, 水蜜桃, 樱桃, 黄桃, 香梨, 雪梨, 柑橘, 沃柑, 草莓, 甘蔗, 桔子, 沙糖桔, 葡萄, 哈密瓜, 西瓜, 甜瓜, 柚子, 柠檬, 橙子, 菠萝, 凤梨, 榴莲, 山竹, 蓝莓, 荔枝, 龙眼, 椰子, 柿子, 杨梅, 李子, 芒果, 猕猴桃, 火龙果, 百香果, 莲雾, 车厘子, 牛油果, 鳄梨, 芭乐, 番石榴, 菠萝蜜, 桑葚, 枇杷, 杨桃, 无花果, 圣女果, 小番茄, 姑娘果, 西梅, 青枣, 冬枣, 黑布林, 人参果, 释迦, 耙耙柑</t>
-  </si>
-  <si>
-    <t>DRINK</t>
-  </si>
-  <si>
-    <t>可乐, 红牛, 奶茶, 东鹏, 饮料, 汽水, 果汁, 椰汁, 酸奶, 咖啡, 拿铁, 乐虎</t>
-  </si>
-  <si>
-    <t>WATER</t>
-  </si>
-  <si>
-    <t>纯净水, 矿泉水, 农夫山泉, 怡宝, 百岁山, 娃哈哈, 今麦郎</t>
-  </si>
-  <si>
-    <t>SOFTWARE</t>
-  </si>
-  <si>
-    <t>软件, APP, 应用</t>
-  </si>
-  <si>
-    <t>CHARGING</t>
-  </si>
-  <si>
-    <t>特来电, 星星充电, 小桔充电, 国家电网, 电费, 充电, e充电, 云快充, 蔚来, 特斯拉, 超充</t>
-  </si>
-  <si>
-    <t>VEGETABLE</t>
-  </si>
-  <si>
-    <t>青菜, 白菜, 娃娃菜, 菠菜, 生菜, 油麦菜, 韭菜, 芹菜, 香菜, 土豆, 茄子, 豆角, 辣椒, 青椒, 洋葱, 西红柿, 番茄, 黄瓜, 冬瓜, 南瓜, 苦瓜, 丝瓜, 萝卜, 胡萝卜, 藕, 莲藕, 笋, 莴笋, 蘑菇, 香菇, 金针菇, 木耳, 豆芽, 玉米, 红薯, 山药, 芋头</t>
-  </si>
-  <si>
-    <t>BEAN_PRODUCT</t>
-  </si>
-  <si>
-    <t>豆腐, 豆皮, 腐竹, 豆干, 豆腐泡, 素鸡, 千张, 豆卷, 腐皮, 油豆皮, 内脂豆腐, 老豆腐, 嫩豆腐, 冻豆腐, 响铃卷</t>
-  </si>
-  <si>
-    <t>INGREDIENTS</t>
-  </si>
-  <si>
-    <t>馒头, 火腿, 葱, 姜, 蒜, 酱料, 料酒, 白砂糖, 生抽, 老抽, 蒸肉粉, 榨菜, 辣椒酱, 老干妈, 胡椒粉, 火锅底料, 生水饺, 菠菜面条, 面条, 挂面, 红豆, 绿豆, 黄豆</t>
-  </si>
-  <si>
-    <t>PORK</t>
-  </si>
-  <si>
-    <t>猪肉, 扇子骨, 板油, 五花肉, 梅花肉, 瘦肉, 猪蹄膀, 蹄膀, 排骨, 脊骨, 五花, 前蹄, 大肠, 筒子骨, 棒骨, 猪油, 猪蹄</t>
-  </si>
-  <si>
-    <t>POULTRY</t>
-  </si>
-  <si>
-    <t>三黄鸡, 鸡腿, 鸡翅, 鸡胸肉, 老母鸡, 乌鸡, 鸭肉, 鸭腿, 鸭翅, 鸭架, 老鸭</t>
-  </si>
-  <si>
-    <t>BEEF_MUTTON</t>
-  </si>
-  <si>
-    <t>牛肉, 羊肉, 牛排, 肥牛, 羊排, 牛腩, 牛柳, 羊腿, 牛腱</t>
-  </si>
-  <si>
-    <t>SEAFOOD</t>
-  </si>
-  <si>
-    <t>鱼, 虾, 蟹, 贝, 带鱼, 黄鱼, 鲈鱼, 鲫鱼, 草鱼, 基围虾, 皮皮虾, 大闸蟹, 蛤蜊, 生蚝, 鱿鱼, 章鱼, 海带, 紫菜</t>
-  </si>
-  <si>
-    <t>EGGS</t>
-  </si>
-  <si>
-    <t>鸡蛋, 土鸡蛋, 生咸鸭蛋, 皮蛋</t>
-  </si>
-  <si>
-    <t>COOKED</t>
-  </si>
-  <si>
-    <t>水煮花生, 毛豆, 藕夹, 茄盒, 锅包肉, 猪头肉, 卤菜, 凉菜, 熟食, 烧鸡, 烤鸭, 酱牛肉, 熏鱼, 炸带鱼, 炸鱿鱼, 肉丸, 墨鱼丸, 牛肉丸, 鱼丸, 虾滑, 贡丸, 鱿鱼圈, 糍粑, 熟咸鸭蛋,花生米</t>
-  </si>
-  <si>
-    <t>RICE</t>
-  </si>
-  <si>
-    <t>大米, 五常</t>
-  </si>
-  <si>
-    <t>MEAL</t>
-  </si>
-  <si>
-    <t>三镇民生, 兰州, 丝路, 沙县, 永和四喜, 水煎包, 老乡鸡, 混沌, 馄饨, 牛肉汤, 热干面, 黄蜀郎, 鸡公煲, 小吃, 烧烤, 食堂, 路边摊, 麦香园, 长沙臭豆腐, 东苑一层, 东苑二层, 西区食堂, 包子, 小笼包, 外勤, 板面, 水饺, 猪脚饭, 肠粉, 卤肉饭, 油泼面, 重庆小面, 牛杂粉, 麻辣香锅, 麻辣烫, 煎包, 煎饼, 烧饼, 锅盔, 馕, 土豆鸡蛋饼, 热干面, 牛肉面, 刀削面, 盖浇饭, 炒饭</t>
-  </si>
-  <si>
-    <t>DAILY_NECESSITIES</t>
-  </si>
-  <si>
-    <t>日常用品, 锅, 勺, 刀, 砧板, 擀面杖, 和面棒, 打蛋器, 压汁器, 料理机, 计时器, 切蛋器, 瓶起子, 筷, 碗, 杯, 袋, 瓶, 盒, 壶, 罐, 桶, 纸, 手套, 膜, 布, 洗洁精, 钢丝球, 牙刷, 牙膏, 漱口杯, 洗发水, 沐浴露, 香皂, 鼻毛修剪器, 掏耳勺, 抽纸, 卫生纸, 湿巾, 清凉油, 花露水, 洗衣粉, 洁厕灵, 除锈剂, 清洗剂, 拖把, 扫把, 水桶, 盆, 围裙, 衣架, 晒衣杆, 夹子, 挂钩, 置物架, 凳子垫, 雨伞, 锁, 灯, 电池, 插座, 理线器, 螺丝刀, 卷尺, 润滑油, 胶水</t>
-  </si>
-  <si>
-    <t>SERVER</t>
-  </si>
-  <si>
-    <t>节点, Dler, Dogess</t>
-  </si>
-  <si>
-    <t>BAD_SHOP</t>
-  </si>
-  <si>
-    <t>抖音, 支付宝, 微信, 转账, 扫码, 付款, 商户, 美团, 饿了么, 合并支付, 京东, 拼多多, 淘特, 特价版</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -690,7 +580,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -700,12 +590,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -713,12 +605,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -746,7 +633,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -791,21 +678,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -813,7 +685,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -829,11 +701,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -851,6 +718,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1069,19 +939,20 @@
   <dimension ref="A1:S74"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.75" style="13" customWidth="1"/>
-    <col min="2" max="2" width="12.58203125" style="13" customWidth="1"/>
-    <col min="3" max="3" width="7.08203125" style="13" customWidth="1"/>
-    <col min="8" max="8" width="2.25" style="13" customWidth="1"/>
-    <col min="9" max="9" width="2.83203125" style="13" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" style="13" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" style="13" customWidth="1"/>
-    <col min="12" max="12" width="16.08203125" style="13" customWidth="1"/>
-    <col min="13" max="13" width="11.83203125" style="13" customWidth="1"/>
-    <col min="14" max="14" width="3.08203125" style="13" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" style="13" customWidth="1"/>
-    <col min="16" max="16" width="16.08203125" style="13" customWidth="1"/>
-    <col min="17" max="17" width="11.33203125" style="13" customWidth="1"/>
+    <col min="1" max="1" width="38.75" style="10" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="7.08203125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="28.83203125" customWidth="1"/>
+    <col min="8" max="8" width="2.25" style="10" customWidth="1"/>
+    <col min="9" max="9" width="2.83203125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="16.08203125" style="10" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="3.08203125" style="10" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" style="10" customWidth="1"/>
+    <col min="16" max="16" width="16.08203125" style="10" customWidth="1"/>
+    <col min="17" max="17" width="11.33203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -1144,8 +1015,8 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>19</v>
+      <c r="A2" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -1156,101 +1027,101 @@
       <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
+      <c r="G2" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="L2" t="s">
         <v>19</v>
       </c>
       <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" t="s">
         <v>25</v>
       </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="L4" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="O4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
         <v>27</v>
       </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" t="s">
-        <v>34</v>
+      <c r="K5" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S5">
         <v>1</v>
@@ -1258,7 +1129,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -1270,16 +1141,16 @@
         <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="O6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S6">
         <v>1</v>
@@ -1287,7 +1158,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1299,21 +1170,21 @@
         <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="O7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
@@ -1325,13 +1196,13 @@
         <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="O8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S8">
         <v>1</v>
@@ -1339,7 +1210,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
@@ -1351,13 +1222,13 @@
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="O9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S9">
         <v>1</v>
@@ -1365,7 +1236,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
         <v>20</v>
@@ -1377,13 +1248,13 @@
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L10" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S10">
         <v>1</v>
@@ -1391,7 +1262,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
         <v>20</v>
@@ -1403,13 +1274,13 @@
         <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="O11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S11">
         <v>1</v>
@@ -1417,7 +1288,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
@@ -1429,19 +1300,19 @@
         <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L12" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P12"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
@@ -1453,10 +1324,10 @@
         <v>22</v>
       </c>
       <c r="L13" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="O13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P13"/>
       <c r="S13">
@@ -1465,7 +1336,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
@@ -1477,10 +1348,10 @@
         <v>22</v>
       </c>
       <c r="L14" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P14"/>
       <c r="S14">
@@ -1489,7 +1360,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
@@ -1501,10 +1372,10 @@
         <v>22</v>
       </c>
       <c r="L15" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="O15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P15"/>
       <c r="S15">
@@ -1513,7 +1384,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -1525,10 +1396,10 @@
         <v>22</v>
       </c>
       <c r="L16" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="O16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P16"/>
       <c r="S16">
@@ -1537,7 +1408,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
@@ -1549,10 +1420,10 @@
         <v>22</v>
       </c>
       <c r="L17" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="O17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S17">
         <v>1</v>
@@ -1560,7 +1431,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
         <v>20</v>
@@ -1572,12 +1443,12 @@
         <v>22</v>
       </c>
       <c r="L18" t="s">
-        <v>59</v>
-      </c>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+        <v>52</v>
+      </c>
+      <c r="M18" s="8"/>
+      <c r="N18" s="9"/>
       <c r="O18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P18"/>
       <c r="S18">
@@ -1586,7 +1457,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
         <v>20</v>
@@ -1598,10 +1469,10 @@
         <v>22</v>
       </c>
       <c r="L19" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="O19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P19"/>
       <c r="S19">
@@ -1610,7 +1481,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
         <v>20</v>
@@ -1622,10 +1493,10 @@
         <v>22</v>
       </c>
       <c r="L20" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="O20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P20"/>
       <c r="S20">
@@ -1634,7 +1505,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
         <v>20</v>
@@ -1646,10 +1517,10 @@
         <v>22</v>
       </c>
       <c r="L21" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="O21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P21"/>
       <c r="S21">
@@ -1658,7 +1529,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
         <v>20</v>
@@ -1670,10 +1541,10 @@
         <v>22</v>
       </c>
       <c r="L22" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="O22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P22"/>
       <c r="S22">
@@ -1682,7 +1553,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
@@ -1694,10 +1565,10 @@
         <v>22</v>
       </c>
       <c r="L23" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="O23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P23"/>
       <c r="S23">
@@ -1706,7 +1577,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
         <v>20</v>
@@ -1718,21 +1589,21 @@
         <v>22</v>
       </c>
       <c r="L24" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="O24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P24" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>
@@ -1744,16 +1615,16 @@
         <v>22</v>
       </c>
       <c r="L25" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="O25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P25" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="Q25" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="S25">
         <v>1</v>
@@ -1761,10 +1632,10 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
         <v>20</v>
@@ -1776,16 +1647,16 @@
         <v>22</v>
       </c>
       <c r="L26" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="O26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P26" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Q26" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="S26">
         <v>1</v>
@@ -1793,10 +1664,10 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
@@ -1808,24 +1679,24 @@
         <v>22</v>
       </c>
       <c r="L27" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O27" t="s">
+        <v>23</v>
+      </c>
+      <c r="P27" t="s">
         <v>25</v>
       </c>
-      <c r="P27" t="s">
-        <v>30</v>
-      </c>
       <c r="Q27" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
         <v>20</v>
@@ -1837,21 +1708,21 @@
         <v>22</v>
       </c>
       <c r="L28" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="O28" t="s">
+        <v>23</v>
+      </c>
+      <c r="P28" t="s">
         <v>25</v>
       </c>
-      <c r="P28" t="s">
-        <v>30</v>
-      </c>
       <c r="Q28" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
         <v>20</v>
@@ -1863,16 +1734,16 @@
         <v>22</v>
       </c>
       <c r="L29" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="O29" t="s">
+        <v>23</v>
+      </c>
+      <c r="P29" t="s">
         <v>25</v>
       </c>
-      <c r="P29" t="s">
-        <v>30</v>
-      </c>
       <c r="Q29" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="S29">
         <v>1</v>
@@ -1880,10 +1751,10 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
         <v>20</v>
@@ -1895,24 +1766,24 @@
         <v>22</v>
       </c>
       <c r="L30" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O30" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P30" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="Q30" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
         <v>20</v>
@@ -1924,10 +1795,10 @@
         <v>22</v>
       </c>
       <c r="L31" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="O31" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S31">
         <v>1</v>
@@ -1935,10 +1806,10 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
         <v>20</v>
@@ -1950,18 +1821,18 @@
         <v>22</v>
       </c>
       <c r="L32" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="O32" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s">
         <v>20</v>
@@ -1973,21 +1844,21 @@
         <v>22</v>
       </c>
       <c r="L33" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="O33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P33" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="Q33" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
         <v>20</v>
@@ -1996,16 +1867,16 @@
         <v>21</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L34" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="S34">
         <v>1</v>
@@ -2013,7 +1884,7 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
         <v>20</v>
@@ -2022,21 +1893,21 @@
         <v>21</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="O35" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P35" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
         <v>20</v>
@@ -2045,21 +1916,21 @@
         <v>21</v>
       </c>
       <c r="F36" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G36" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="L36" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="O36" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
         <v>20</v>
@@ -2068,48 +1939,48 @@
         <v>21</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L37" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="O37" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="P37" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M38" s="9"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="8" t="s">
+      <c r="D38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5" t="s">
         <v>103</v>
+      </c>
+      <c r="M38" s="6"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="S38">
         <v>1</v>
@@ -2117,7 +1988,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D39" t="s">
         <v>20</v>
@@ -2126,16 +1997,16 @@
         <v>21</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G39" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L39" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="O39" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="S39">
         <v>1</v>
@@ -2143,7 +2014,7 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
         <v>20</v>
@@ -2152,24 +2023,24 @@
         <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K40" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L40" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="O40" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D41" t="s">
         <v>20</v>
@@ -2178,24 +2049,24 @@
         <v>21</v>
       </c>
       <c r="F41" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K41" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L41" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="O41" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
         <v>20</v>
@@ -2204,19 +2075,19 @@
         <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G42" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K42" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L42" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="O42" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="S42">
         <v>1</v>
@@ -2224,7 +2095,7 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
         <v>20</v>
@@ -2233,24 +2104,24 @@
         <v>21</v>
       </c>
       <c r="F43" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G43" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K43" t="s">
+        <v>108</v>
+      </c>
+      <c r="L43" t="s">
         <v>115</v>
       </c>
-      <c r="L43" t="s">
-        <v>122</v>
-      </c>
       <c r="O43" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D44" t="s">
         <v>20</v>
@@ -2259,19 +2130,19 @@
         <v>21</v>
       </c>
       <c r="F44" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G44" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K44" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="L44" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="O44" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="S44">
         <v>1</v>
@@ -2279,7 +2150,7 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
         <v>20</v>
@@ -2288,19 +2159,19 @@
         <v>21</v>
       </c>
       <c r="F45" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G45" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K45" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="L45" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="O45" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="S45">
         <v>1</v>
@@ -2308,7 +2179,7 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D46" t="s">
         <v>20</v>
@@ -2317,27 +2188,27 @@
         <v>21</v>
       </c>
       <c r="F46" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G46" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="L46" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="O46" t="s">
-        <v>130</v>
-      </c>
-      <c r="P46" s="10" t="s">
-        <v>131</v>
+        <v>123</v>
+      </c>
+      <c r="P46" s="7" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B47" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D47" t="s">
         <v>20</v>
@@ -2346,24 +2217,24 @@
         <v>21</v>
       </c>
       <c r="F47" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G47" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="L47" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="O47" t="s">
-        <v>130</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>131</v>
+        <v>123</v>
+      </c>
+      <c r="P47" s="7" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D48" t="s">
         <v>20</v>
@@ -2372,16 +2243,16 @@
         <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G48" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="L48" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="O48" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="P48">
         <v>13297968006</v>
@@ -2392,7 +2263,7 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D49" t="s">
         <v>20</v>
@@ -2401,16 +2272,16 @@
         <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G49" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="L49" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="O49" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="P49">
         <v>13638658298</v>
@@ -2421,7 +2292,7 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D50" t="s">
         <v>20</v>
@@ -2430,13 +2301,13 @@
         <v>21</v>
       </c>
       <c r="F50" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G50" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="O50" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="S50">
         <v>1</v>
@@ -2444,7 +2315,7 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D51" t="s">
         <v>20</v>
@@ -2453,19 +2324,19 @@
         <v>21</v>
       </c>
       <c r="F51" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G51" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="L51" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="O51" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="S51">
         <v>1</v>
@@ -2473,7 +2344,7 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D52" t="s">
         <v>20</v>
@@ -2482,16 +2353,16 @@
         <v>21</v>
       </c>
       <c r="F52" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G52" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L52" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="O52" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="Q52"/>
       <c r="S52">
@@ -2500,7 +2371,7 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
         <v>20</v>
@@ -2509,36 +2380,36 @@
         <v>21</v>
       </c>
       <c r="F53" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G53" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="O53" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
         <v>20</v>
       </c>
       <c r="E54" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F54" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G54" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="L54" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="O54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="S54">
         <v>1</v>
@@ -2546,7 +2417,7 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D55" t="s">
         <v>20</v>
@@ -2558,10 +2429,10 @@
         <v>22</v>
       </c>
       <c r="L55" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="O55" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S55">
         <v>1</v>
@@ -2569,7 +2440,7 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D56" t="s">
         <v>20</v>
@@ -2581,10 +2452,10 @@
         <v>22</v>
       </c>
       <c r="L56" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="O56" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S56">
         <v>1</v>
@@ -2593,31 +2464,31 @@
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D57" t="s">
         <v>20</v>
       </c>
       <c r="E57" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F57" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G57" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="K57" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="L57"/>
       <c r="O57"/>
       <c r="P57"/>
       <c r="Q57" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="R57" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="S57">
         <v>1</v>
@@ -2625,14 +2496,14 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="K58"/>
       <c r="L58" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="O58"/>
       <c r="P58"/>
@@ -2643,7 +2514,7 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D59" t="s">
         <v>20</v>
@@ -2652,19 +2523,19 @@
         <v>21</v>
       </c>
       <c r="L59" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="O59"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
         <v>20</v>
       </c>
       <c r="L60" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="S60">
         <v>1</v>
@@ -2672,13 +2543,13 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D61" t="s">
         <v>20</v>
       </c>
       <c r="L61" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="S61">
         <v>1</v>
@@ -2686,13 +2557,13 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D62" t="s">
         <v>20</v>
       </c>
       <c r="L62" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="S62">
         <v>1</v>
@@ -2700,13 +2571,13 @@
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D63" t="s">
         <v>20</v>
       </c>
       <c r="L63" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="S63">
         <v>1</v>
@@ -2714,13 +2585,13 @@
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D64" t="s">
         <v>20</v>
       </c>
       <c r="L64" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="S64">
         <v>1</v>
@@ -2728,13 +2599,13 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D65" t="s">
         <v>20</v>
       </c>
       <c r="L65" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="S65">
         <v>1</v>
@@ -2742,13 +2613,13 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="S66">
         <v>1</v>
@@ -2756,13 +2627,13 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
       </c>
       <c r="L67" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="S67">
         <v>1</v>
@@ -2770,13 +2641,13 @@
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
       </c>
       <c r="L68" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="S68">
         <v>1</v>
@@ -2784,35 +2655,35 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
       </c>
       <c r="L69" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D70" t="s">
         <v>20</v>
       </c>
       <c r="L70" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
       </c>
       <c r="L71" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="S71">
         <v>1</v>
@@ -2820,13 +2691,13 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D72" t="s">
         <v>20</v>
       </c>
       <c r="L72" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="S72">
         <v>1</v>
@@ -2834,16 +2705,16 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D73" t="s">
         <v>20</v>
       </c>
       <c r="P73" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="Q73" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="S73">
         <v>1</v>
@@ -2851,195 +2722,21 @@
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D74" t="s">
         <v>20</v>
       </c>
       <c r="P74" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="Q74" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S74" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.08203125" style="13" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Moze Dict.xlsx
+++ b/Moze Dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\天之逸2025\Moze4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90FFC7E-10A7-4983-9B2E-85E4240696A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C16DDF-0B1A-4294-BE0D-AAD6CEC2DA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -484,9 +484,6 @@
     <t>^(.*?)(?:停车收费|停车场|停车费|停车平台)?$</t>
   </si>
   <si>
-    <t>\1</t>
-  </si>
-  <si>
     <t>淘宝闪购</t>
   </si>
   <si>
@@ -570,6 +567,10 @@
   </si>
   <si>
     <t>陈望云</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>\1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1016,7 +1017,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -1028,10 +1029,10 @@
         <v>22</v>
       </c>
       <c r="G2" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>172</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>173</v>
       </c>
       <c r="L2" t="s">
         <v>19</v>
@@ -1045,7 +1046,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
@@ -1057,10 +1058,10 @@
         <v>22</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -1074,7 +1075,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
@@ -1086,10 +1087,10 @@
         <v>22</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -1103,7 +1104,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
@@ -1118,7 +1119,7 @@
         <v>27</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O5" t="s">
         <v>23</v>
@@ -2502,11 +2503,11 @@
         <v>146</v>
       </c>
       <c r="K58"/>
-      <c r="L58" t="s">
-        <v>153</v>
-      </c>
+      <c r="L58"/>
       <c r="O58"/>
-      <c r="P58"/>
+      <c r="P58" s="12" t="s">
+        <v>179</v>
+      </c>
       <c r="Q58"/>
       <c r="S58">
         <v>1</v>
@@ -2514,7 +2515,7 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D59" t="s">
         <v>20</v>
@@ -2523,19 +2524,19 @@
         <v>21</v>
       </c>
       <c r="L59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O59"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D60" t="s">
         <v>20</v>
       </c>
       <c r="L60" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="S60">
         <v>1</v>
@@ -2543,13 +2544,13 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D61" t="s">
         <v>20</v>
       </c>
       <c r="L61" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S61">
         <v>1</v>
@@ -2557,13 +2558,13 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D62" t="s">
         <v>20</v>
       </c>
       <c r="L62" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S62">
         <v>1</v>
@@ -2571,13 +2572,13 @@
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D63" t="s">
         <v>20</v>
       </c>
       <c r="L63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="S63">
         <v>1</v>
@@ -2585,13 +2586,13 @@
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D64" t="s">
         <v>20</v>
       </c>
       <c r="L64" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S64">
         <v>1</v>
@@ -2599,13 +2600,13 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="L65" t="s">
         <v>160</v>
-      </c>
-      <c r="D65" t="s">
-        <v>20</v>
-      </c>
-      <c r="L65" t="s">
-        <v>161</v>
       </c>
       <c r="S65">
         <v>1</v>
@@ -2613,13 +2614,13 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S66">
         <v>1</v>
@@ -2627,13 +2628,13 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
       </c>
       <c r="L67" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="S67">
         <v>1</v>
@@ -2641,13 +2642,13 @@
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
       </c>
       <c r="L68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S68">
         <v>1</v>
@@ -2655,24 +2656,24 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>164</v>
+      </c>
+      <c r="D69" t="s">
+        <v>20</v>
+      </c>
+      <c r="L69" t="s">
         <v>165</v>
-      </c>
-      <c r="D69" t="s">
-        <v>20</v>
-      </c>
-      <c r="L69" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>166</v>
+      </c>
+      <c r="D70" t="s">
+        <v>20</v>
+      </c>
+      <c r="L70" t="s">
         <v>167</v>
-      </c>
-      <c r="D70" t="s">
-        <v>20</v>
-      </c>
-      <c r="L70" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
@@ -2691,13 +2692,13 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D72" t="s">
         <v>20</v>
       </c>
       <c r="L72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S72">
         <v>1</v>
@@ -2705,13 +2706,13 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D73" t="s">
         <v>20</v>
       </c>
       <c r="P73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q73" t="s">
         <v>65</v>
@@ -2722,13 +2723,13 @@
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D74" t="s">
         <v>20</v>
       </c>
       <c r="P74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q74" t="s">
         <v>65</v>
